--- a/apps/api/data/excel_templates/universities.xlsx
+++ b/apps/api/data/excel_templates/universities.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB37AEA-05CE-E048-B0C0-8A1A61876143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE590D08-25E7-5243-9729-F216247796EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="universities" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">universities!$A$1:$Q$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="416">
   <si>
     <t>name</t>
   </si>
@@ -74,13 +74,1263 @@
   </si>
   <si>
     <t>postgraduates</t>
+  </si>
+  <si>
+    <t>Harvard University</t>
+  </si>
+  <si>
+    <t>Private Research University</t>
+  </si>
+  <si>
+    <t>World prestigious university. Ivy League, highly selective.</t>
+  </si>
+  <si>
+    <t>Stanford University</t>
+  </si>
+  <si>
+    <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
+  </si>
+  <si>
+    <t>University of Cambridge</t>
+  </si>
+  <si>
+    <t>Public Research University</t>
+  </si>
+  <si>
+    <t>World prestigious university. Russell Group.</t>
+  </si>
+  <si>
+    <t>Massachusetts Institute of Technology (MIT)</t>
+  </si>
+  <si>
+    <t>World prestigious university. Highly selective.</t>
+  </si>
+  <si>
+    <t>University of California, Berkeley</t>
+  </si>
+  <si>
+    <t>World prestigious university. Public Ivy League, highly selective.</t>
+  </si>
+  <si>
+    <t>Princeton University</t>
+  </si>
+  <si>
+    <t>University of Oxford</t>
+  </si>
+  <si>
+    <t>Columbia University</t>
+  </si>
+  <si>
+    <t>California Institute of Technology</t>
+  </si>
+  <si>
+    <t>University of Chicago</t>
+  </si>
+  <si>
+    <t>World prestigious university. Highly selective. Hidden Ivy League.</t>
+  </si>
+  <si>
+    <t>Yale University</t>
+  </si>
+  <si>
+    <t>University of California, Los Angeles</t>
+  </si>
+  <si>
+    <t>World prestigious university. Public Ivy League.</t>
+  </si>
+  <si>
+    <t>University of Washington</t>
+  </si>
+  <si>
+    <t>World-renowned university, public Ivy League</t>
+  </si>
+  <si>
+    <t>Cornell University</t>
+  </si>
+  <si>
+    <t>University of California, San Diego</t>
+  </si>
+  <si>
+    <t>University College London</t>
+  </si>
+  <si>
+    <t>University of Pennsylvania</t>
+  </si>
+  <si>
+    <t>Johns Hopkins University</t>
+  </si>
+  <si>
+    <t>Swiss Federal Institute of Technology Zurich</t>
+  </si>
+  <si>
+    <t>World prestigious university</t>
+  </si>
+  <si>
+    <t>Washington University in St. Louis</t>
+  </si>
+  <si>
+    <t>University of California, San Francisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> N/A (UCSF does not offer undergraduate programs)</t>
+  </si>
+  <si>
+    <t>World-renowned university</t>
+  </si>
+  <si>
+    <t>Northwestern University</t>
+  </si>
+  <si>
+    <t>University of Toronto</t>
+  </si>
+  <si>
+    <t>World prestigious university. U15 Group.</t>
+  </si>
+  <si>
+    <t>The University of Tokyo</t>
+  </si>
+  <si>
+    <t>World prestigious university. Imperial university.</t>
+  </si>
+  <si>
+    <t>University of Michigan-Ann Arbor</t>
+  </si>
+  <si>
+    <t>Duke University</t>
+  </si>
+  <si>
+    <t>Imperial College London</t>
+  </si>
+  <si>
+    <t>University of Wisconsin - Madison</t>
+  </si>
+  <si>
+    <t>New York University</t>
+  </si>
+  <si>
+    <t>World-renowned university. Highly selective.</t>
+  </si>
+  <si>
+    <t>University of Copenhagen</t>
+  </si>
+  <si>
+    <t>University of British Columbia</t>
+  </si>
+  <si>
+    <t>World-renowned university. U15 Group.</t>
+  </si>
+  <si>
+    <t>The University of Edinburgh</t>
+  </si>
+  <si>
+    <t>World-renowned university. Russell Group.</t>
+  </si>
+  <si>
+    <t>University of North Carolina at Chapel Hill</t>
+  </si>
+  <si>
+    <t>University of Minnesota, Twin Cities</t>
+  </si>
+  <si>
+    <t>Kyoto University</t>
+  </si>
+  <si>
+    <t>World-renowned university. Imperial university.</t>
+  </si>
+  <si>
+    <t>Rockefeller University</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> N/A (Rockefeller is a graduate-only institution)</t>
+  </si>
+  <si>
+    <t>Focused on Biomedical Sciences</t>
+  </si>
+  <si>
+    <t>University of Illinois at Urbana-Champaign</t>
+  </si>
+  <si>
+    <t>The University of Manchester</t>
+  </si>
+  <si>
+    <t>The University of Melbourne</t>
+  </si>
+  <si>
+    <t>World-renowned university. Group of Eight (Go8).</t>
+  </si>
+  <si>
+    <t>Pierre and Marie Curie University - Paris 6</t>
+  </si>
+  <si>
+    <t>40,000 (for Sorbonne University)</t>
+  </si>
+  <si>
+    <t>Elite university in France. World-renowned university.</t>
+  </si>
+  <si>
+    <t>University of Paris-Sud (Paris 11)</t>
+  </si>
+  <si>
+    <t>Elite university in France</t>
+  </si>
+  <si>
+    <t>Heidelberg University</t>
+  </si>
+  <si>
+    <t>World-renowned university. Elite university in Germany.</t>
+  </si>
+  <si>
+    <t>University of Colorado at Boulder</t>
+  </si>
+  <si>
+    <t>Public Ivy League</t>
+  </si>
+  <si>
+    <t>Karolinska Institute</t>
+  </si>
+  <si>
+    <t>Public Medical University</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> N/A (focuses primarily on graduate programs in medical and life sciences)</t>
+  </si>
+  <si>
+    <t>University of California, Santa Barbara</t>
+  </si>
+  <si>
+    <t>King's College London</t>
+  </si>
+  <si>
+    <t>Utrecht University</t>
+  </si>
+  <si>
+    <t>The University of Texas Southwestern Medical Center at Dallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> N/A (medical institution)</t>
+  </si>
+  <si>
+    <t>Known for Medical Sciences, Healthcare and Research</t>
+  </si>
+  <si>
+    <t>Tsinghua University</t>
+  </si>
+  <si>
+    <t>World prestigious university. C9 League.</t>
+  </si>
+  <si>
+    <t>Technical University Munich</t>
+  </si>
+  <si>
+    <t>The University of Texas at Austin</t>
+  </si>
+  <si>
+    <t>Vanderbilt University</t>
+  </si>
+  <si>
+    <t>Highly selective. Hidden Ivy League.</t>
+  </si>
+  <si>
+    <t>University of Maryland, College Park</t>
+  </si>
+  <si>
+    <t>University of Southern California</t>
+  </si>
+  <si>
+    <t>The University of Queensland</t>
+  </si>
+  <si>
+    <t>Group of Eight (Go8)</t>
+  </si>
+  <si>
+    <t>University of Helsinki</t>
+  </si>
+  <si>
+    <t>Known for Medical Sciences, Humanities and Social Sciences</t>
+  </si>
+  <si>
+    <t>University of Munich</t>
+  </si>
+  <si>
+    <t>University of Zurich</t>
+  </si>
+  <si>
+    <t>University of Groningen</t>
+  </si>
+  <si>
+    <t>Known for Life Sciences, Arts and Social Sciences</t>
+  </si>
+  <si>
+    <t>University of Geneva</t>
+  </si>
+  <si>
+    <t>Known for International Relations, Social Sciences and Law</t>
+  </si>
+  <si>
+    <t>University of Bristol</t>
+  </si>
+  <si>
+    <t>Russell Group</t>
+  </si>
+  <si>
+    <t>University of Oslo</t>
+  </si>
+  <si>
+    <t>Known for Humanities, Natural Sciences and Social Sciences</t>
+  </si>
+  <si>
+    <t>Uppsala University</t>
+  </si>
+  <si>
+    <t>Known for Humanities, Life Sciences and Social Sciences</t>
+  </si>
+  <si>
+    <t>University of California, Irvine</t>
+  </si>
+  <si>
+    <t>Aarhus University</t>
+  </si>
+  <si>
+    <t>Known for Humanities, Business and Natural Sciences</t>
+  </si>
+  <si>
+    <t>McMaster University</t>
+  </si>
+  <si>
+    <t>U15 Group</t>
+  </si>
+  <si>
+    <t>McGill University</t>
+  </si>
+  <si>
+    <t>University of Pittsburgh, Pittsburgh Campus</t>
+  </si>
+  <si>
+    <t>École Normale Supérieure - Paris</t>
+  </si>
+  <si>
+    <t>Ghent University</t>
+  </si>
+  <si>
+    <t>Known for Medical Sciences, Engineering and Life Sciences</t>
+  </si>
+  <si>
+    <t>Mayo Medical School</t>
+  </si>
+  <si>
+    <t>Private Medical School</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> N/A (graduate-only institution)</t>
+  </si>
+  <si>
+    <t>Known for Medical Education and Clinical Research</t>
+  </si>
+  <si>
+    <t>Peking University</t>
+  </si>
+  <si>
+    <t>Erasmus University</t>
+  </si>
+  <si>
+    <t>Known for Social Sciences, Business and Medical Sciences</t>
+  </si>
+  <si>
+    <t>Rice University</t>
+  </si>
+  <si>
+    <t>Stockholm University</t>
+  </si>
+  <si>
+    <t>Swiss Federal Institute of Technology Lausanne</t>
+  </si>
+  <si>
+    <t>Purdue University - West Lafayette</t>
+  </si>
+  <si>
+    <t>Monash University</t>
+  </si>
+  <si>
+    <t>Rutgers, The State University of New Jersey - New Brunswick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Ivy League
+</t>
+  </si>
+  <si>
+    <t>Boston University</t>
+  </si>
+  <si>
+    <t>Carnegie Mellon University</t>
+  </si>
+  <si>
+    <t>The Ohio State University - Columbus</t>
+  </si>
+  <si>
+    <t>University of Sydney</t>
+  </si>
+  <si>
+    <t>Nagoya University</t>
+  </si>
+  <si>
+    <t>Georgia Institute of Technology</t>
+  </si>
+  <si>
+    <t>World-renowned university, public Ivy League, highly selective.</t>
+  </si>
+  <si>
+    <t>Pennsylvania State University - University Park</t>
+  </si>
+  <si>
+    <t>University of California, Davis</t>
+  </si>
+  <si>
+    <t>Leiden University</t>
+  </si>
+  <si>
+    <t>University of Florida</t>
+  </si>
+  <si>
+    <t>KU Leuven</t>
+  </si>
+  <si>
+    <t>National University of Singapore</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>The University of Western Australia</t>
+  </si>
+  <si>
+    <t>Moscow State University</t>
+  </si>
+  <si>
+    <t>World-renowned university. Elite university in Russia.</t>
+  </si>
+  <si>
+    <t>University of Basel</t>
+  </si>
+  <si>
+    <t>Known for Medical Sciences, Life Sciences and Humanities</t>
+  </si>
+  <si>
+    <t>University of Göttingen</t>
+  </si>
+  <si>
+    <t>Elite university in Germany</t>
+  </si>
+  <si>
+    <t>The Australian National University</t>
+  </si>
+  <si>
+    <t>University of California, Santa Cruz</t>
+  </si>
+  <si>
+    <t>Known for Social Sciences, Natural Sciences and Arts</t>
+  </si>
+  <si>
+    <t>Cardiff University</t>
+  </si>
+  <si>
+    <t>University of Arizona</t>
+  </si>
+  <si>
+    <t>UNI-000001</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UNI-000002</t>
+  </si>
+  <si>
+    <t>UNI-000003</t>
+  </si>
+  <si>
+    <t>UNI-000004</t>
+  </si>
+  <si>
+    <t>UNI-000005</t>
+  </si>
+  <si>
+    <t>UNI-000006</t>
+  </si>
+  <si>
+    <t>UNI-000007</t>
+  </si>
+  <si>
+    <t>UNI-000008</t>
+  </si>
+  <si>
+    <t>UNI-000009</t>
+  </si>
+  <si>
+    <t>UNI-000010</t>
+  </si>
+  <si>
+    <t>UNI-000011</t>
+  </si>
+  <si>
+    <t>UNI-000012</t>
+  </si>
+  <si>
+    <t>UNI-000013</t>
+  </si>
+  <si>
+    <t>UNI-000014</t>
+  </si>
+  <si>
+    <t>UNI-000015</t>
+  </si>
+  <si>
+    <t>UNI-000016</t>
+  </si>
+  <si>
+    <t>UNI-000017</t>
+  </si>
+  <si>
+    <t>UNI-000018</t>
+  </si>
+  <si>
+    <t>UNI-000019</t>
+  </si>
+  <si>
+    <t>UNI-000020</t>
+  </si>
+  <si>
+    <t>UNI-000021</t>
+  </si>
+  <si>
+    <t>UNI-000022</t>
+  </si>
+  <si>
+    <t>UNI-000023</t>
+  </si>
+  <si>
+    <t>UNI-000024</t>
+  </si>
+  <si>
+    <t>UNI-000025</t>
+  </si>
+  <si>
+    <t>UNI-000026</t>
+  </si>
+  <si>
+    <t>UNI-000027</t>
+  </si>
+  <si>
+    <t>UNI-000028</t>
+  </si>
+  <si>
+    <t>UNI-000029</t>
+  </si>
+  <si>
+    <t>UNI-000030</t>
+  </si>
+  <si>
+    <t>UNI-000031</t>
+  </si>
+  <si>
+    <t>UNI-000032</t>
+  </si>
+  <si>
+    <t>UNI-000033</t>
+  </si>
+  <si>
+    <t>UNI-000034</t>
+  </si>
+  <si>
+    <t>UNI-000035</t>
+  </si>
+  <si>
+    <t>UNI-000036</t>
+  </si>
+  <si>
+    <t>UNI-000037</t>
+  </si>
+  <si>
+    <t>UNI-000038</t>
+  </si>
+  <si>
+    <t>UNI-000039</t>
+  </si>
+  <si>
+    <t>UNI-000040</t>
+  </si>
+  <si>
+    <t>UNI-000041</t>
+  </si>
+  <si>
+    <t>UNI-000042</t>
+  </si>
+  <si>
+    <t>UNI-000043</t>
+  </si>
+  <si>
+    <t>UNI-000044</t>
+  </si>
+  <si>
+    <t>UNI-000045</t>
+  </si>
+  <si>
+    <t>UNI-000046</t>
+  </si>
+  <si>
+    <t>UNI-000047</t>
+  </si>
+  <si>
+    <t>UNI-000048</t>
+  </si>
+  <si>
+    <t>UNI-000049</t>
+  </si>
+  <si>
+    <t>UNI-000050</t>
+  </si>
+  <si>
+    <t>UNI-000051</t>
+  </si>
+  <si>
+    <t>UNI-000052</t>
+  </si>
+  <si>
+    <t>UNI-000053</t>
+  </si>
+  <si>
+    <t>UNI-000054</t>
+  </si>
+  <si>
+    <t>UNI-000055</t>
+  </si>
+  <si>
+    <t>UNI-000056</t>
+  </si>
+  <si>
+    <t>UNI-000057</t>
+  </si>
+  <si>
+    <t>UNI-000058</t>
+  </si>
+  <si>
+    <t>UNI-000059</t>
+  </si>
+  <si>
+    <t>UNI-000060</t>
+  </si>
+  <si>
+    <t>UNI-000061</t>
+  </si>
+  <si>
+    <t>UNI-000062</t>
+  </si>
+  <si>
+    <t>UNI-000063</t>
+  </si>
+  <si>
+    <t>UNI-000064</t>
+  </si>
+  <si>
+    <t>UNI-000065</t>
+  </si>
+  <si>
+    <t>UNI-000066</t>
+  </si>
+  <si>
+    <t>UNI-000067</t>
+  </si>
+  <si>
+    <t>UNI-000068</t>
+  </si>
+  <si>
+    <t>UNI-000069</t>
+  </si>
+  <si>
+    <t>UNI-000070</t>
+  </si>
+  <si>
+    <t>UNI-000071</t>
+  </si>
+  <si>
+    <t>UNI-000072</t>
+  </si>
+  <si>
+    <t>UNI-000073</t>
+  </si>
+  <si>
+    <t>UNI-000074</t>
+  </si>
+  <si>
+    <t>UNI-000075</t>
+  </si>
+  <si>
+    <t>UNI-000076</t>
+  </si>
+  <si>
+    <t>UNI-000077</t>
+  </si>
+  <si>
+    <t>UNI-000078</t>
+  </si>
+  <si>
+    <t>UNI-000079</t>
+  </si>
+  <si>
+    <t>UNI-000080</t>
+  </si>
+  <si>
+    <t>UNI-000081</t>
+  </si>
+  <si>
+    <t>UNI-000082</t>
+  </si>
+  <si>
+    <t>UNI-000083</t>
+  </si>
+  <si>
+    <t>UNI-000084</t>
+  </si>
+  <si>
+    <t>UNI-000085</t>
+  </si>
+  <si>
+    <t>UNI-000086</t>
+  </si>
+  <si>
+    <t>UNI-000087</t>
+  </si>
+  <si>
+    <t>UNI-000088</t>
+  </si>
+  <si>
+    <t>UNI-000089</t>
+  </si>
+  <si>
+    <t>UNI-000090</t>
+  </si>
+  <si>
+    <t>UNI-000091</t>
+  </si>
+  <si>
+    <t>UNI-000092</t>
+  </si>
+  <si>
+    <t>UNI-000093</t>
+  </si>
+  <si>
+    <t>UNI-000094</t>
+  </si>
+  <si>
+    <t>UNI-000095</t>
+  </si>
+  <si>
+    <t>UNI-000096</t>
+  </si>
+  <si>
+    <t>UNI-000097</t>
+  </si>
+  <si>
+    <t>UNI-000098</t>
+  </si>
+  <si>
+    <t>UNI-000099</t>
+  </si>
+  <si>
+    <t>Eidgenössische Technische Hochschule Zürich</t>
+  </si>
+  <si>
+    <t>東京大学</t>
+  </si>
+  <si>
+    <t>Københavns Universitet</t>
+  </si>
+  <si>
+    <t>京都大学</t>
+  </si>
+  <si>
+    <t>Prifysgol Caerdydd</t>
+  </si>
+  <si>
+    <t>Georg-August-Universität Göttingen</t>
+  </si>
+  <si>
+    <t>Universität Basel</t>
+  </si>
+  <si>
+    <t>Московский государственный университет имени М. В. Ломоносова</t>
+  </si>
+  <si>
+    <t>Katholieke Universiteit Leuven</t>
+  </si>
+  <si>
+    <t>Universiteit Leiden</t>
+  </si>
+  <si>
+    <t>The Pennsylvania State University</t>
+  </si>
+  <si>
+    <t>名古屋大学</t>
+  </si>
+  <si>
+    <t>The University of Sydney</t>
+  </si>
+  <si>
+    <t>The Ohio State University</t>
+  </si>
+  <si>
+    <t>Rutgers, The State University of New Jersey–New Brunswick</t>
+  </si>
+  <si>
+    <t>Purdue University</t>
+  </si>
+  <si>
+    <t>École polytechnique fédérale de Lausanne (EPFL)</t>
+  </si>
+  <si>
+    <t>Stockholms universitet</t>
+  </si>
+  <si>
+    <t>Erasmus Universiteit Rotterdam</t>
+  </si>
+  <si>
+    <t>北京大学</t>
+  </si>
+  <si>
+    <t>Universiteit Gent</t>
+  </si>
+  <si>
+    <t>École normale supérieure</t>
+  </si>
+  <si>
+    <t>University of Pittsburgh</t>
+  </si>
+  <si>
+    <t>Université McGill</t>
+  </si>
+  <si>
+    <t>Aarhus Universitet</t>
+  </si>
+  <si>
+    <t>Uppsala universitet</t>
+  </si>
+  <si>
+    <t>Universitetet i Oslo</t>
+  </si>
+  <si>
+    <t>Université de Genève</t>
+  </si>
+  <si>
+    <t>Rijksuniversiteit Groningen</t>
+  </si>
+  <si>
+    <t>Universität Zürich</t>
+  </si>
+  <si>
+    <t>Ludwig-Maximilians-Universität München</t>
+  </si>
+  <si>
+    <t>Helsingin yliopisto</t>
+  </si>
+  <si>
+    <t>Technische Universität München</t>
+  </si>
+  <si>
+    <t>清华大学</t>
+  </si>
+  <si>
+    <t>Universiteit Utrecht</t>
+  </si>
+  <si>
+    <t>Karolinska Institutet</t>
+  </si>
+  <si>
+    <t>University of Colorado Boulder</t>
+  </si>
+  <si>
+    <t>Ruprecht-Karls-Universität Heidelberg</t>
+  </si>
+  <si>
+    <t>Université Paris-Sud (Paris XI)</t>
+  </si>
+  <si>
+    <t>Université Pierre-et-Marie-Curie (Paris VI)</t>
+  </si>
+  <si>
+    <t>King Saud University</t>
+  </si>
+  <si>
+    <t>Leading public university in Saudi Arabia. Flagship institution with strong research programs and broad academic offerings.</t>
+  </si>
+  <si>
+    <t>UNI-000100</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="178"/>
+      </rPr>
+      <t>جامعة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="178"/>
+      </rPr>
+      <t>الملك</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="178"/>
+      </rPr>
+      <t>سعود</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Riyadh</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Tucson,Arizona</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Cardiff,Wales</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Santa Cruz,California</t>
+  </si>
+  <si>
+    <t>Canberra</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Göttingen</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Moscow</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>Perth,Western Australia</t>
+  </si>
+  <si>
+    <t>Leuven</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Gainesville,Florida</t>
+  </si>
+  <si>
+    <t>Leiden</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Davis,California</t>
+  </si>
+  <si>
+    <t>University Park,Pennsylvania</t>
+  </si>
+  <si>
+    <t>Atlanta,Georgia</t>
+  </si>
+  <si>
+    <t>Nagoya,Aichi</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Sydney,New South Wales</t>
+  </si>
+  <si>
+    <t>Columbus,Ohio</t>
+  </si>
+  <si>
+    <t>Pittsburgh,Pennsylvania</t>
+  </si>
+  <si>
+    <t>Boston,Massachusetts</t>
+  </si>
+  <si>
+    <t>New Brunswick,New Jersey</t>
+  </si>
+  <si>
+    <t>Melbourne,Victoria</t>
+  </si>
+  <si>
+    <t>West Lafayette,Indiana</t>
+  </si>
+  <si>
+    <t>Lausanne</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Houston,Texas</t>
+  </si>
+  <si>
+    <t>Rotterdam</t>
+  </si>
+  <si>
+    <t>Beijing</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Rochester,Minnesota</t>
+  </si>
+  <si>
+    <t>Ghent</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Montreal,Quebec</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Hamilton,Ontario</t>
+  </si>
+  <si>
+    <t>Aarhus</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Irvine,California</t>
+  </si>
+  <si>
+    <t>Uppsala</t>
+  </si>
+  <si>
+    <t>Oslo</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Bristol,England</t>
+  </si>
+  <si>
+    <t>Geneva</t>
+  </si>
+  <si>
+    <t>Groningen</t>
+  </si>
+  <si>
+    <t>Zurich</t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t>Helsinki</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Brisbane,Queensland</t>
+  </si>
+  <si>
+    <t>Los Angeles,California</t>
+  </si>
+  <si>
+    <t>College Park,Maryland</t>
+  </si>
+  <si>
+    <t>Nashville,Tennessee</t>
+  </si>
+  <si>
+    <t>Austin,Texas</t>
+  </si>
+  <si>
+    <t>Dallas,Texas</t>
+  </si>
+  <si>
+    <t>Utrecht</t>
+  </si>
+  <si>
+    <t>London,England</t>
+  </si>
+  <si>
+    <t>Santa Barbara,California</t>
+  </si>
+  <si>
+    <t>Boulder,Colorado</t>
+  </si>
+  <si>
+    <t>Heidelberg,Baden-Württemberg</t>
+  </si>
+  <si>
+    <t>Orsay</t>
+  </si>
+  <si>
+    <t>Manchester,England</t>
+  </si>
+  <si>
+    <t>Urbana and Champaign,Illinois</t>
+  </si>
+  <si>
+    <t>New York City,New York</t>
+  </si>
+  <si>
+    <t>Kyoto</t>
+  </si>
+  <si>
+    <t>Minneapolis,Minnesota</t>
+  </si>
+  <si>
+    <t>Chapel Hill,North Carolina</t>
+  </si>
+  <si>
+    <t>Edinburgh,Scotland</t>
+  </si>
+  <si>
+    <t>Vancouver,British Columbia</t>
+  </si>
+  <si>
+    <t>Copenhagen</t>
+  </si>
+  <si>
+    <t>Madison,Wisconsin</t>
+  </si>
+  <si>
+    <t>Durham,North Carolina</t>
+  </si>
+  <si>
+    <t>Ann Arbor,Michigan</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Toronto,Ontario</t>
+  </si>
+  <si>
+    <t>Evanston,Illinois</t>
+  </si>
+  <si>
+    <t>San Francisco,California</t>
+  </si>
+  <si>
+    <t>St. Louis,Missouri</t>
+  </si>
+  <si>
+    <t>Baltimore,Maryland</t>
+  </si>
+  <si>
+    <t>Philadelphia,Pennsylvania</t>
+  </si>
+  <si>
+    <t>San Diego,California</t>
+  </si>
+  <si>
+    <t>Ithaca,New York</t>
+  </si>
+  <si>
+    <t>Seattle,Washington</t>
+  </si>
+  <si>
+    <t>New Haven,Connecticut</t>
+  </si>
+  <si>
+    <t>Chicago,Illinois</t>
+  </si>
+  <si>
+    <t>Pasadena,California</t>
+  </si>
+  <si>
+    <t>Oxford,England</t>
+  </si>
+  <si>
+    <t>Princeton,New Jersey</t>
+  </si>
+  <si>
+    <t>Berkeley,California</t>
+  </si>
+  <si>
+    <t>Cambridge,Massachusetts</t>
+  </si>
+  <si>
+    <t>Cambridge,England</t>
+  </si>
+  <si>
+    <t>Stanford,California</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,21 +1341,45 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="178"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -120,15 +1394,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -426,69 +1717,3573 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="17" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="I2" s="2">
+        <v>20000</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2">
+        <v>1636</v>
+      </c>
+      <c r="P2" s="2">
+        <v>7000</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I3" s="2">
+        <v>15000</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>1885</v>
+      </c>
+      <c r="P3" s="2">
+        <v>7000</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="I4" s="2">
+        <v>24000</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4">
+        <v>1209</v>
+      </c>
+      <c r="P4" s="2">
+        <v>12000</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="I5" s="2">
+        <v>11500</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5">
+        <v>1861</v>
+      </c>
+      <c r="P5" s="2">
+        <v>4500</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I6" s="2">
+        <v>42000</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6">
+        <v>1868</v>
+      </c>
+      <c r="P6" s="2">
+        <v>31000</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8000</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7">
+        <v>1746</v>
+      </c>
+      <c r="P7" s="2">
+        <v>5300</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I8" s="2">
+        <v>24000</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8">
+        <v>1096</v>
+      </c>
+      <c r="P8" s="2">
+        <v>12000</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I9" s="2">
+        <v>31000</v>
+      </c>
+      <c r="L9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9">
+        <v>1754</v>
+      </c>
+      <c r="P9" s="2">
+        <v>8200</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2200</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10">
+        <v>1891</v>
+      </c>
+      <c r="P10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="I11" s="2">
+        <v>17000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11">
+        <v>1890</v>
+      </c>
+      <c r="P11" s="2">
+        <v>6800</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="I12" s="2">
+        <v>13000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12">
+        <v>1701</v>
+      </c>
+      <c r="P12" s="2">
+        <v>6100</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I13" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13">
+        <v>1919</v>
+      </c>
+      <c r="P13" s="2">
+        <v>31000</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="I14" s="2">
+        <v>54000</v>
+      </c>
+      <c r="L14" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14">
+        <v>1861</v>
+      </c>
+      <c r="P14" s="2">
+        <v>32000</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="I15" s="2">
+        <v>23000</v>
+      </c>
+      <c r="L15" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15">
+        <v>1865</v>
+      </c>
+      <c r="P15" s="2">
+        <v>15000</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I16" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L16" t="s">
+        <v>41</v>
+      </c>
+      <c r="M16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16">
+        <v>1903</v>
+      </c>
+      <c r="P16" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I17" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L17" t="s">
+        <v>42</v>
+      </c>
+      <c r="M17" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17">
+        <v>1826</v>
+      </c>
+      <c r="P17" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="I18" s="2">
+        <v>25000</v>
+      </c>
+      <c r="L18" t="s">
+        <v>43</v>
+      </c>
+      <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18">
+        <v>1740</v>
+      </c>
+      <c r="P18" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I19" s="2">
+        <v>24000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N19">
+        <v>1876</v>
+      </c>
+      <c r="P19" s="2">
+        <v>6000</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H20" t="s">
+        <v>369</v>
+      </c>
+      <c r="I20" s="2">
+        <v>20000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>269</v>
+      </c>
+      <c r="M20" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20">
+        <v>1855</v>
+      </c>
+      <c r="P20" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I21" s="2">
+        <v>15000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>47</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21">
+        <v>1853</v>
+      </c>
+      <c r="P21" s="2">
+        <v>8000</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I22" s="2">
+        <v>3000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>48</v>
+      </c>
+      <c r="M22" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22">
+        <v>1864</v>
+      </c>
+      <c r="P22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="I23" s="2">
+        <v>21000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>51</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23">
+        <v>1851</v>
+      </c>
+      <c r="P23" s="2">
+        <v>8000</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="I24" s="2">
+        <v>90000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24">
+        <v>1827</v>
+      </c>
+      <c r="P24" s="2">
+        <v>60000</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H25" t="s">
+        <v>397</v>
+      </c>
+      <c r="I25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>270</v>
+      </c>
+      <c r="M25" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25">
+        <v>1877</v>
+      </c>
+      <c r="P25" s="2">
+        <v>15000</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I26" s="2">
+        <v>48000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26">
+        <v>1817</v>
+      </c>
+      <c r="P26" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="I27" s="2">
+        <v>15000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27">
+        <v>1838</v>
+      </c>
+      <c r="P27" s="2">
+        <v>6500</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I28" s="2">
+        <v>18000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" t="s">
+        <v>24</v>
+      </c>
+      <c r="N28">
+        <v>1907</v>
+      </c>
+      <c r="P28" s="2">
+        <v>9000</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
+        <v>197</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I29" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" t="s">
+        <v>39</v>
+      </c>
+      <c r="N29">
+        <v>1848</v>
+      </c>
+      <c r="P29" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I30" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" t="s">
+        <v>61</v>
+      </c>
+      <c r="N30">
+        <v>1831</v>
+      </c>
+      <c r="P30" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="H31" t="s">
+        <v>393</v>
+      </c>
+      <c r="I31" s="2">
+        <v>38000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>271</v>
+      </c>
+      <c r="M31" t="s">
+        <v>50</v>
+      </c>
+      <c r="N31">
+        <v>1479</v>
+      </c>
+      <c r="P31" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I32" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" t="s">
+        <v>64</v>
+      </c>
+      <c r="N32">
+        <v>1908</v>
+      </c>
+      <c r="P32" s="2">
+        <v>40000</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I33" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" t="s">
+        <v>66</v>
+      </c>
+      <c r="N33">
+        <v>1582</v>
+      </c>
+      <c r="P33" s="2">
+        <v>25000</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I34" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>67</v>
+      </c>
+      <c r="M34" t="s">
+        <v>39</v>
+      </c>
+      <c r="N34">
+        <v>1789</v>
+      </c>
+      <c r="P34" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>203</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="I35" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35" t="s">
+        <v>39</v>
+      </c>
+      <c r="N35">
+        <v>1851</v>
+      </c>
+      <c r="P35" s="2">
+        <v>33000</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>204</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H36" t="s">
+        <v>388</v>
+      </c>
+      <c r="I36" s="2">
+        <v>23000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>272</v>
+      </c>
+      <c r="M36" t="s">
+        <v>70</v>
+      </c>
+      <c r="N36">
+        <v>1897</v>
+      </c>
+      <c r="P36" s="2">
+        <v>12000</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>71</v>
+      </c>
+      <c r="M37" t="s">
+        <v>73</v>
+      </c>
+      <c r="N37">
+        <v>1901</v>
+      </c>
+      <c r="P37" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>206</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I38" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>74</v>
+      </c>
+      <c r="M38" t="s">
+        <v>39</v>
+      </c>
+      <c r="N38">
+        <v>1867</v>
+      </c>
+      <c r="P38" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I39" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>75</v>
+      </c>
+      <c r="M39" t="s">
+        <v>66</v>
+      </c>
+      <c r="N39">
+        <v>1824</v>
+      </c>
+      <c r="P39" s="2">
+        <v>25000</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I40" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>76</v>
+      </c>
+      <c r="M40" t="s">
+        <v>77</v>
+      </c>
+      <c r="N40">
+        <v>1853</v>
+      </c>
+      <c r="P40" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H41" t="s">
+        <v>355</v>
+      </c>
+      <c r="I41" t="s">
+        <v>79</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M41" t="s">
+        <v>80</v>
+      </c>
+      <c r="N41">
+        <v>1257</v>
+      </c>
+      <c r="P41" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H42" t="s">
+        <v>384</v>
+      </c>
+      <c r="I42" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="M42" t="s">
+        <v>82</v>
+      </c>
+      <c r="N42">
+        <v>2015</v>
+      </c>
+      <c r="P42" s="2">
+        <v>15000</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I43" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="M43" t="s">
+        <v>84</v>
+      </c>
+      <c r="N43">
+        <v>1386</v>
+      </c>
+      <c r="P43" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" t="s">
+        <v>212</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I44" s="2">
+        <v>35000</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="M44" t="s">
+        <v>86</v>
+      </c>
+      <c r="N44">
+        <v>1876</v>
+      </c>
+      <c r="P44" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H45" t="s">
+        <v>347</v>
+      </c>
+      <c r="I45" s="2">
+        <v>3000</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="M45" t="s">
+        <v>50</v>
+      </c>
+      <c r="N45">
+        <v>1810</v>
+      </c>
+      <c r="P45" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>214</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="I46" s="2">
+        <v>25000</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M46" t="s">
+        <v>39</v>
+      </c>
+      <c r="N46">
+        <v>1909</v>
+      </c>
+      <c r="P46" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" t="s">
+        <v>215</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I47" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M47" t="s">
+        <v>66</v>
+      </c>
+      <c r="N47">
+        <v>1829</v>
+      </c>
+      <c r="P47" s="2">
+        <v>16000</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>216</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H48" t="s">
+        <v>379</v>
+      </c>
+      <c r="I48" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="M48" t="s">
+        <v>50</v>
+      </c>
+      <c r="N48">
+        <v>1636</v>
+      </c>
+      <c r="P48" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I49" s="2">
+        <v>3700</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M49" t="s">
+        <v>95</v>
+      </c>
+      <c r="N49">
+        <v>1943</v>
+      </c>
+      <c r="P49" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="H50" t="s">
+        <v>351</v>
+      </c>
+      <c r="I50" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="M50" t="s">
+        <v>97</v>
+      </c>
+      <c r="N50">
+        <v>1911</v>
+      </c>
+      <c r="P50" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" t="s">
+        <v>219</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H51" t="s">
+        <v>370</v>
+      </c>
+      <c r="I51" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="M51" t="s">
+        <v>84</v>
+      </c>
+      <c r="N51">
+        <v>1827</v>
+      </c>
+      <c r="P51" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>220</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I52" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M52" t="s">
+        <v>39</v>
+      </c>
+      <c r="N52">
+        <v>1883</v>
+      </c>
+      <c r="P52" s="2">
+        <v>40000</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>221</v>
+      </c>
+      <c r="C53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I53" s="2">
+        <v>13000</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M53" t="s">
+        <v>101</v>
+      </c>
+      <c r="N53">
+        <v>1873</v>
+      </c>
+      <c r="P53" s="2">
+        <v>7000</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="I54" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M54" t="s">
+        <v>39</v>
+      </c>
+      <c r="N54">
+        <v>1856</v>
+      </c>
+      <c r="P54" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I55" s="2">
+        <v>47000</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M55" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55">
+        <v>1880</v>
+      </c>
+      <c r="P55" s="2">
+        <v>19000</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I56" s="2">
+        <v>55000</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M56" t="s">
+        <v>105</v>
+      </c>
+      <c r="N56">
+        <v>1909</v>
+      </c>
+      <c r="P56" s="2">
+        <v>40000</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>225</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="H57" t="s">
+        <v>371</v>
+      </c>
+      <c r="I57" s="2">
+        <v>35000</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M57" t="s">
+        <v>107</v>
+      </c>
+      <c r="N57">
+        <v>1640</v>
+      </c>
+      <c r="P57" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>226</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H58" t="s">
+        <v>370</v>
+      </c>
+      <c r="I58" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="M58" t="s">
+        <v>84</v>
+      </c>
+      <c r="N58">
+        <v>1472</v>
+      </c>
+      <c r="P58" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
+      <c r="A59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>227</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H59" t="s">
+        <v>369</v>
+      </c>
+      <c r="I59" s="2">
+        <v>26000</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="M59" t="s">
+        <v>50</v>
+      </c>
+      <c r="N59">
+        <v>1833</v>
+      </c>
+      <c r="P59" s="2">
+        <v>14000</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
+      <c r="A60" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" t="s">
+        <v>228</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H60" t="s">
+        <v>368</v>
+      </c>
+      <c r="I60" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="M60" t="s">
+        <v>111</v>
+      </c>
+      <c r="N60">
+        <v>1614</v>
+      </c>
+      <c r="P60" s="2">
+        <v>18000</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" t="s">
+        <v>112</v>
+      </c>
+      <c r="B61" t="s">
+        <v>229</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H61" t="s">
+        <v>367</v>
+      </c>
+      <c r="I61" s="2">
+        <v>17000</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="M61" t="s">
+        <v>113</v>
+      </c>
+      <c r="N61">
+        <v>1559</v>
+      </c>
+      <c r="P61" s="2">
+        <v>9000</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" t="s">
+        <v>230</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I62" s="2">
+        <v>27000</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M62" t="s">
+        <v>115</v>
+      </c>
+      <c r="N62">
+        <v>1833</v>
+      </c>
+      <c r="P62" s="2">
+        <v>18000</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="A63" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" t="s">
+        <v>231</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="H63" t="s">
+        <v>364</v>
+      </c>
+      <c r="I63" s="2">
+        <v>28000</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="M63" t="s">
+        <v>117</v>
+      </c>
+      <c r="N63">
+        <v>1811</v>
+      </c>
+      <c r="P63" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
+      <c r="A64" t="s">
+        <v>118</v>
+      </c>
+      <c r="B64" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H64" t="s">
+        <v>363</v>
+      </c>
+      <c r="I64" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="M64" t="s">
+        <v>119</v>
+      </c>
+      <c r="N64">
+        <v>1477</v>
+      </c>
+      <c r="P64" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
+      <c r="A65" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" t="s">
+        <v>233</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I65" s="2">
+        <v>36000</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M65" t="s">
+        <v>86</v>
+      </c>
+      <c r="N65">
+        <v>1965</v>
+      </c>
+      <c r="P65" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
+      <c r="A66" t="s">
+        <v>121</v>
+      </c>
+      <c r="B66" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="H66" t="s">
+        <v>360</v>
+      </c>
+      <c r="I66" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="M66" t="s">
+        <v>122</v>
+      </c>
+      <c r="N66">
+        <v>1928</v>
+      </c>
+      <c r="P66" s="2">
+        <v>25000</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
+      <c r="A67" t="s">
+        <v>123</v>
+      </c>
+      <c r="B67" t="s">
+        <v>235</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="I67" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M67" t="s">
+        <v>124</v>
+      </c>
+      <c r="N67">
+        <v>1887</v>
+      </c>
+      <c r="P67" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
+      <c r="A68" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" t="s">
+        <v>236</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I68" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="M68" t="s">
+        <v>64</v>
+      </c>
+      <c r="N68">
+        <v>1821</v>
+      </c>
+      <c r="P68" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
+      <c r="A69" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" t="s">
+        <v>237</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I69" s="2">
+        <v>28000</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="M69" t="s">
+        <v>86</v>
+      </c>
+      <c r="N69">
+        <v>1787</v>
+      </c>
+      <c r="P69" s="2">
+        <v>19000</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
+      <c r="A70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" t="s">
+        <v>238</v>
+      </c>
+      <c r="C70" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H70" t="s">
+        <v>355</v>
+      </c>
+      <c r="I70" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="M70" t="s">
+        <v>82</v>
+      </c>
+      <c r="N70">
+        <v>1794</v>
+      </c>
+      <c r="P70">
+        <v>600</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
+      <c r="A71" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71" t="s">
+        <v>239</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H71" t="s">
+        <v>354</v>
+      </c>
+      <c r="I71" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="M71" t="s">
+        <v>129</v>
+      </c>
+      <c r="N71">
+        <v>1817</v>
+      </c>
+      <c r="P71" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17">
+      <c r="A72" t="s">
+        <v>130</v>
+      </c>
+      <c r="B72" t="s">
+        <v>240</v>
+      </c>
+      <c r="C72" t="s">
+        <v>131</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I72" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M72" t="s">
+        <v>133</v>
+      </c>
+      <c r="N72">
+        <v>1972</v>
+      </c>
+      <c r="P72" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" t="s">
+        <v>241</v>
+      </c>
+      <c r="C73" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="H73" t="s">
+        <v>351</v>
+      </c>
+      <c r="I73" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="M73" t="s">
+        <v>97</v>
+      </c>
+      <c r="N73">
+        <v>1898</v>
+      </c>
+      <c r="P73" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17">
+      <c r="A74" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H74" t="s">
+        <v>350</v>
+      </c>
+      <c r="I74" s="2">
+        <v>28000</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="M74" t="s">
+        <v>136</v>
+      </c>
+      <c r="N74">
+        <v>1913</v>
+      </c>
+      <c r="P74" s="2">
+        <v>15000</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17">
+      <c r="A75" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" t="s">
+        <v>243</v>
+      </c>
+      <c r="C75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="I75" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="M75" t="s">
+        <v>101</v>
+      </c>
+      <c r="N75">
+        <v>1912</v>
+      </c>
+      <c r="P75" s="2">
+        <v>4000</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17">
+      <c r="A76" t="s">
+        <v>138</v>
+      </c>
+      <c r="B76" t="s">
+        <v>244</v>
+      </c>
+      <c r="C76" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H76" t="s">
+        <v>347</v>
+      </c>
+      <c r="I76" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="M76" t="s">
+        <v>119</v>
+      </c>
+      <c r="N76">
+        <v>1878</v>
+      </c>
+      <c r="P76" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17">
+      <c r="A77" t="s">
+        <v>139</v>
+      </c>
+      <c r="B77" t="s">
+        <v>245</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H77" t="s">
+        <v>346</v>
+      </c>
+      <c r="I77" s="2">
+        <v>12000</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M77" t="s">
+        <v>50</v>
+      </c>
+      <c r="N77">
+        <v>1853</v>
+      </c>
+      <c r="P77" s="2">
+        <v>6000</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17">
+      <c r="A78" t="s">
+        <v>140</v>
+      </c>
+      <c r="B78" t="s">
+        <v>246</v>
+      </c>
+      <c r="C78" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="I78" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="M78" t="s">
+        <v>39</v>
+      </c>
+      <c r="N78">
+        <v>1869</v>
+      </c>
+      <c r="P78" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17">
+      <c r="A79" t="s">
+        <v>141</v>
+      </c>
+      <c r="B79" t="s">
+        <v>247</v>
+      </c>
+      <c r="C79" t="s">
+        <v>23</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I79" s="2">
+        <v>80000</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M79" t="s">
+        <v>105</v>
+      </c>
+      <c r="N79">
+        <v>1958</v>
+      </c>
+      <c r="P79" s="2">
+        <v>55000</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17">
+      <c r="A80" t="s">
+        <v>142</v>
+      </c>
+      <c r="B80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C80" t="s">
+        <v>23</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I80" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="M80" t="s">
+        <v>143</v>
+      </c>
+      <c r="N80">
+        <v>1766</v>
+      </c>
+      <c r="P80" s="2">
+        <v>35000</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17">
+      <c r="A81" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I81" s="2">
+        <v>35000</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M81" t="s">
+        <v>50</v>
+      </c>
+      <c r="N81">
+        <v>1839</v>
+      </c>
+      <c r="P81" s="2">
+        <v>16000</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82" t="s">
+        <v>145</v>
+      </c>
+      <c r="B82" t="s">
+        <v>250</v>
+      </c>
+      <c r="C82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I82" s="2">
+        <v>14000</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M82" t="s">
+        <v>61</v>
+      </c>
+      <c r="N82">
+        <v>1900</v>
+      </c>
+      <c r="P82" s="2">
+        <v>7000</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17">
+      <c r="A83" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" t="s">
+        <v>251</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="I83" s="2">
+        <v>61000</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="M83" t="s">
+        <v>39</v>
+      </c>
+      <c r="N83">
+        <v>1870</v>
+      </c>
+      <c r="P83" s="2">
+        <v>47000</v>
+      </c>
+      <c r="Q83" s="2">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17">
+      <c r="A84" t="s">
+        <v>147</v>
+      </c>
+      <c r="B84" t="s">
+        <v>252</v>
+      </c>
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I84" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="M84" t="s">
+        <v>77</v>
+      </c>
+      <c r="N84">
+        <v>1850</v>
+      </c>
+      <c r="P84" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q84" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17">
+      <c r="A85" t="s">
+        <v>148</v>
+      </c>
+      <c r="B85" t="s">
+        <v>253</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I85" s="2">
+        <v>20000</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="M85" t="s">
+        <v>70</v>
+      </c>
+      <c r="N85">
+        <v>1871</v>
+      </c>
+      <c r="P85" s="2">
+        <v>12000</v>
+      </c>
+      <c r="Q85" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17">
+      <c r="A86" t="s">
+        <v>149</v>
+      </c>
+      <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="I86" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="M86" t="s">
+        <v>150</v>
+      </c>
+      <c r="N86">
+        <v>1885</v>
+      </c>
+      <c r="P86" s="2">
+        <v>15000</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17">
+      <c r="A87" t="s">
+        <v>151</v>
+      </c>
+      <c r="B87" t="s">
+        <v>255</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I87" s="2">
+        <v>46000</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M87" t="s">
+        <v>39</v>
+      </c>
+      <c r="N87">
+        <v>1855</v>
+      </c>
+      <c r="P87" s="2">
+        <v>40000</v>
+      </c>
+      <c r="Q87" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17">
+      <c r="A88" t="s">
+        <v>152</v>
+      </c>
+      <c r="B88" t="s">
+        <v>256</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I88" s="2">
+        <v>39000</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M88" t="s">
+        <v>39</v>
+      </c>
+      <c r="N88">
+        <v>1905</v>
+      </c>
+      <c r="P88" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q88" s="2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17">
+      <c r="A89" t="s">
+        <v>153</v>
+      </c>
+      <c r="B89" t="s">
+        <v>257</v>
+      </c>
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H89" t="s">
+        <v>332</v>
+      </c>
+      <c r="I89" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M89" t="s">
+        <v>50</v>
+      </c>
+      <c r="N89">
+        <v>1575</v>
+      </c>
+      <c r="P89" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q89" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17">
+      <c r="A90" t="s">
+        <v>154</v>
+      </c>
+      <c r="B90" t="s">
+        <v>258</v>
+      </c>
+      <c r="C90" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I90" s="2">
+        <v>55000</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="M90" t="s">
+        <v>39</v>
+      </c>
+      <c r="N90">
+        <v>1853</v>
+      </c>
+      <c r="P90" s="2">
+        <v>35000</v>
+      </c>
+      <c r="Q90" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17">
+      <c r="A91" t="s">
+        <v>155</v>
+      </c>
+      <c r="B91" t="s">
+        <v>259</v>
+      </c>
+      <c r="C91" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H91" t="s">
+        <v>329</v>
+      </c>
+      <c r="I91" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="M91" t="s">
+        <v>50</v>
+      </c>
+      <c r="N91">
+        <v>1425</v>
+      </c>
+      <c r="P91" s="2">
+        <v>40000</v>
+      </c>
+      <c r="Q91" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17">
+      <c r="A92" t="s">
+        <v>156</v>
+      </c>
+      <c r="B92" t="s">
+        <v>260</v>
+      </c>
+      <c r="C92" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" t="s">
+        <v>157</v>
+      </c>
+      <c r="H92" t="s">
+        <v>157</v>
+      </c>
+      <c r="I92" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M92" t="s">
+        <v>50</v>
+      </c>
+      <c r="N92">
+        <v>1905</v>
+      </c>
+      <c r="P92" s="2">
+        <v>28000</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17">
+      <c r="A93" t="s">
+        <v>158</v>
+      </c>
+      <c r="B93" t="s">
+        <v>261</v>
+      </c>
+      <c r="C93" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="I93" s="2">
+        <v>25000</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M93" t="s">
+        <v>105</v>
+      </c>
+      <c r="N93">
+        <v>1911</v>
+      </c>
+      <c r="P93" s="2">
+        <v>18000</v>
+      </c>
+      <c r="Q93" s="2">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="A94" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" t="s">
+        <v>262</v>
+      </c>
+      <c r="C94" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="H94" t="s">
+        <v>326</v>
+      </c>
+      <c r="I94" s="2">
+        <v>40000</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="M94" t="s">
+        <v>160</v>
+      </c>
+      <c r="N94">
+        <v>1755</v>
+      </c>
+      <c r="P94" s="2">
+        <v>25000</v>
+      </c>
+      <c r="Q94" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17">
+      <c r="A95" t="s">
+        <v>161</v>
+      </c>
+      <c r="B95" t="s">
+        <v>263</v>
+      </c>
+      <c r="C95" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H95" t="s">
+        <v>324</v>
+      </c>
+      <c r="I95" s="2">
+        <v>13000</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M95" t="s">
+        <v>162</v>
+      </c>
+      <c r="N95">
+        <v>1460</v>
+      </c>
+      <c r="P95" s="2">
+        <v>7000</v>
+      </c>
+      <c r="Q95" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17">
+      <c r="A96" t="s">
+        <v>163</v>
+      </c>
+      <c r="B96" t="s">
+        <v>264</v>
+      </c>
+      <c r="C96" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H96" t="s">
+        <v>322</v>
+      </c>
+      <c r="I96" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="M96" t="s">
+        <v>164</v>
+      </c>
+      <c r="N96">
+        <v>1737</v>
+      </c>
+      <c r="P96" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q96" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17">
+      <c r="A97" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97" t="s">
+        <v>265</v>
+      </c>
+      <c r="C97" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H97" t="s">
+        <v>320</v>
+      </c>
+      <c r="I97" s="2">
+        <v>20000</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="M97" t="s">
+        <v>77</v>
+      </c>
+      <c r="N97">
+        <v>1946</v>
+      </c>
+      <c r="P97" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Q97" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17">
+      <c r="A98" t="s">
+        <v>166</v>
+      </c>
+      <c r="B98" t="s">
+        <v>266</v>
+      </c>
+      <c r="C98" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="I98" s="2">
+        <v>20000</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M98" t="s">
+        <v>167</v>
+      </c>
+      <c r="N98">
+        <v>1962</v>
+      </c>
+      <c r="P98" s="2">
+        <v>18000</v>
+      </c>
+      <c r="Q98" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17">
+      <c r="A99" t="s">
+        <v>168</v>
+      </c>
+      <c r="B99" t="s">
+        <v>267</v>
+      </c>
+      <c r="C99" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="I99" s="2">
+        <v>30000</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="M99" t="s">
+        <v>115</v>
+      </c>
+      <c r="N99">
+        <v>1883</v>
+      </c>
+      <c r="P99" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q99" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17">
+      <c r="A100" t="s">
+        <v>169</v>
+      </c>
+      <c r="B100" t="s">
+        <v>268</v>
+      </c>
+      <c r="C100" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I100" s="2">
+        <v>45000</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="M100" t="s">
+        <v>39</v>
+      </c>
+      <c r="N100">
+        <v>1885</v>
+      </c>
+      <c r="P100" s="2">
+        <v>34000</v>
+      </c>
+      <c r="Q100" s="2">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17">
+      <c r="A101" t="s">
+        <v>309</v>
+      </c>
+      <c r="B101" t="s">
+        <v>311</v>
+      </c>
+      <c r="C101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H101" t="s">
+        <v>313</v>
+      </c>
+      <c r="I101" s="2">
+        <v>61000</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="M101" t="s">
+        <v>310</v>
+      </c>
+      <c r="N101">
+        <v>1957</v>
+      </c>
+      <c r="P101" s="2">
+        <v>38000</v>
+      </c>
+      <c r="Q101" s="2">
+        <v>23000</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="R2:R100">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="C2:C999" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"UNIVERSITY,GRANDE_ECOLE,INSTITUTE,ACADEMY,ONLINE,OTHER"</formula1>

--- a/apps/api/data/excel_templates/universities.xlsx
+++ b/apps/api/data/excel_templates/universities.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE590D08-25E7-5243-9729-F216247796EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8543E2-1DAF-BF42-9C34-304B5700B634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="universities" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="415">
   <si>
     <t>name</t>
   </si>
@@ -260,9 +260,6 @@
   </si>
   <si>
     <t>Pierre and Marie Curie University - Paris 6</t>
-  </si>
-  <si>
-    <t>40,000 (for Sorbonne University)</t>
   </si>
   <si>
     <t>Elite university in France. World-renowned university.</t>
@@ -1394,16 +1391,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1720,9 +1718,14 @@
   <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="18" customWidth="1"/>
+    <col min="1" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="18" style="5" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="17" width="18" customWidth="1"/>
+    <col min="12" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18" style="5" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="17" width="18" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1750,7 +1753,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1765,16 +1768,16 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1783,18 +1786,18 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="G2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="I2" s="5">
         <v>20000</v>
       </c>
       <c r="L2" t="s">
@@ -1803,13 +1806,13 @@
       <c r="M2" t="s">
         <v>19</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="5">
         <v>1636</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="5">
         <v>7000</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="5">
         <v>13000</v>
       </c>
     </row>
@@ -1818,18 +1821,18 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="G3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="I3" s="5">
         <v>15000</v>
       </c>
       <c r="L3" t="s">
@@ -1838,13 +1841,13 @@
       <c r="M3" t="s">
         <v>21</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="5">
         <v>1885</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="5">
         <v>7000</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="5">
         <v>8000</v>
       </c>
     </row>
@@ -1853,18 +1856,18 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="G4" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="I4" s="5">
         <v>24000</v>
       </c>
       <c r="L4" t="s">
@@ -1873,13 +1876,13 @@
       <c r="M4" t="s">
         <v>24</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="5">
         <v>1209</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="5">
         <v>12000</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="5">
         <v>12000</v>
       </c>
     </row>
@@ -1888,18 +1891,18 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="G5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="I5" s="5">
         <v>11500</v>
       </c>
       <c r="L5" t="s">
@@ -1908,13 +1911,13 @@
       <c r="M5" t="s">
         <v>26</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="5">
         <v>1861</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="5">
         <v>4500</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="5">
         <v>7000</v>
       </c>
     </row>
@@ -1923,18 +1926,18 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="G6" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="I6" s="5">
         <v>42000</v>
       </c>
       <c r="L6" t="s">
@@ -1943,13 +1946,13 @@
       <c r="M6" t="s">
         <v>28</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>1868</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="5">
         <v>31000</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="5">
         <v>11000</v>
       </c>
     </row>
@@ -1958,18 +1961,18 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="G7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="I7" s="5">
         <v>8000</v>
       </c>
       <c r="L7" t="s">
@@ -1978,13 +1981,13 @@
       <c r="M7" t="s">
         <v>19</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>1746</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="5">
         <v>5300</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="5">
         <v>2700</v>
       </c>
     </row>
@@ -1993,18 +1996,18 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="G8" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I8" s="5">
         <v>24000</v>
       </c>
       <c r="L8" t="s">
@@ -2013,13 +2016,13 @@
       <c r="M8" t="s">
         <v>24</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="5">
         <v>1096</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="5">
         <v>12000</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="5">
         <v>12000</v>
       </c>
     </row>
@@ -2028,18 +2031,18 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="G9" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I9" s="5">
         <v>31000</v>
       </c>
       <c r="L9" t="s">
@@ -2048,13 +2051,13 @@
       <c r="M9" t="s">
         <v>19</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="5">
         <v>1754</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="5">
         <v>8200</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="5">
         <v>22800</v>
       </c>
     </row>
@@ -2063,18 +2066,18 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="G10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I10" s="5">
         <v>2200</v>
       </c>
       <c r="L10" t="s">
@@ -2083,13 +2086,13 @@
       <c r="M10" t="s">
         <v>26</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="5">
         <v>1891</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="5">
         <v>1000</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="5">
         <v>1200</v>
       </c>
     </row>
@@ -2098,18 +2101,18 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="G11" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I11" s="5">
         <v>17000</v>
       </c>
       <c r="L11" t="s">
@@ -2118,13 +2121,13 @@
       <c r="M11" t="s">
         <v>34</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="5">
         <v>1890</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="5">
         <v>6800</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="5">
         <v>10200</v>
       </c>
     </row>
@@ -2133,18 +2136,18 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="G12" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="I12" s="5">
         <v>13000</v>
       </c>
       <c r="L12" t="s">
@@ -2153,13 +2156,13 @@
       <c r="M12" t="s">
         <v>19</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="5">
         <v>1701</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="5">
         <v>6100</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="5">
         <v>6900</v>
       </c>
     </row>
@@ -2168,18 +2171,18 @@
         <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="G13" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I13" s="5">
         <v>45000</v>
       </c>
       <c r="L13" t="s">
@@ -2188,13 +2191,13 @@
       <c r="M13" t="s">
         <v>37</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="5">
         <v>1919</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="5">
         <v>31000</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="5">
         <v>14000</v>
       </c>
     </row>
@@ -2203,18 +2206,18 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="I14" s="2">
+      <c r="G14" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I14" s="5">
         <v>54000</v>
       </c>
       <c r="L14" t="s">
@@ -2223,13 +2226,13 @@
       <c r="M14" t="s">
         <v>39</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="5">
         <v>1861</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="5">
         <v>32000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="5">
         <v>22000</v>
       </c>
     </row>
@@ -2238,18 +2241,18 @@
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="I15" s="2">
+      <c r="G15" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I15" s="5">
         <v>23000</v>
       </c>
       <c r="L15" t="s">
@@ -2258,13 +2261,13 @@
       <c r="M15" t="s">
         <v>19</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="5">
         <v>1865</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="5">
         <v>15000</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="5">
         <v>8000</v>
       </c>
     </row>
@@ -2273,18 +2276,18 @@
         <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="G16" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I16" s="5">
         <v>40000</v>
       </c>
       <c r="L16" t="s">
@@ -2293,13 +2296,13 @@
       <c r="M16" t="s">
         <v>39</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="5">
         <v>1903</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="5">
         <v>30000</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="5">
         <v>10000</v>
       </c>
     </row>
@@ -2308,18 +2311,18 @@
         <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I17" s="2">
+      <c r="G17" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I17" s="5">
         <v>45000</v>
       </c>
       <c r="L17" t="s">
@@ -2328,13 +2331,13 @@
       <c r="M17" t="s">
         <v>24</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="5">
         <v>1826</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="5">
         <v>20000</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="5">
         <v>25000</v>
       </c>
     </row>
@@ -2343,18 +2346,18 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="I18" s="2">
+      <c r="G18" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="I18" s="5">
         <v>25000</v>
       </c>
       <c r="L18" t="s">
@@ -2363,13 +2366,13 @@
       <c r="M18" t="s">
         <v>19</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="5">
         <v>1740</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="5">
         <v>10000</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="5">
         <v>15000</v>
       </c>
     </row>
@@ -2378,18 +2381,18 @@
         <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="I19" s="2">
+      <c r="G19" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I19" s="5">
         <v>24000</v>
       </c>
       <c r="L19" t="s">
@@ -2398,13 +2401,13 @@
       <c r="M19" t="s">
         <v>34</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="5">
         <v>1876</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="5">
         <v>6000</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="5">
         <v>18000</v>
       </c>
     </row>
@@ -2413,33 +2416,33 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>325</v>
+      <c r="G20" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="H20" t="s">
-        <v>369</v>
-      </c>
-      <c r="I20" s="2">
+        <v>368</v>
+      </c>
+      <c r="I20" s="5">
         <v>20000</v>
       </c>
       <c r="L20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M20" t="s">
         <v>46</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="5">
         <v>1855</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="5">
         <v>10000</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="5">
         <v>10000</v>
       </c>
     </row>
@@ -2448,18 +2451,18 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="I21" s="2">
+      <c r="G21" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I21" s="5">
         <v>15000</v>
       </c>
       <c r="L21" t="s">
@@ -2468,13 +2471,13 @@
       <c r="M21" t="s">
         <v>21</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="5">
         <v>1853</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="5">
         <v>8000</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="5">
         <v>7000</v>
       </c>
     </row>
@@ -2483,18 +2486,18 @@
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="I22" s="2">
+      <c r="G22" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I22" s="5">
         <v>3000</v>
       </c>
       <c r="L22" t="s">
@@ -2503,13 +2506,13 @@
       <c r="M22" t="s">
         <v>50</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="5">
         <v>1864</v>
       </c>
-      <c r="P22" t="s">
+      <c r="P22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="5">
         <v>3000</v>
       </c>
     </row>
@@ -2518,18 +2521,18 @@
         <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="I23" s="2">
+      <c r="G23" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I23" s="5">
         <v>21000</v>
       </c>
       <c r="L23" t="s">
@@ -2538,13 +2541,13 @@
       <c r="M23" t="s">
         <v>21</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="5">
         <v>1851</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="5">
         <v>8000</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="5">
         <v>13000</v>
       </c>
     </row>
@@ -2553,18 +2556,18 @@
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="I24" s="2">
+      <c r="G24" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="I24" s="5">
         <v>90000</v>
       </c>
       <c r="L24" t="s">
@@ -2573,13 +2576,13 @@
       <c r="M24" t="s">
         <v>53</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="5">
         <v>1827</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="5">
         <v>60000</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="5">
         <v>30000</v>
       </c>
     </row>
@@ -2588,33 +2591,33 @@
         <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>338</v>
+      <c r="G25" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="H25" t="s">
-        <v>397</v>
-      </c>
-      <c r="I25" s="2">
+        <v>396</v>
+      </c>
+      <c r="I25" s="5">
         <v>30000</v>
       </c>
       <c r="L25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M25" t="s">
         <v>55</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="5">
         <v>1877</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="5">
         <v>15000</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="5">
         <v>15000</v>
       </c>
     </row>
@@ -2623,18 +2626,18 @@
         <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="I26" s="2">
+      <c r="G26" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I26" s="5">
         <v>48000</v>
       </c>
       <c r="L26" t="s">
@@ -2643,13 +2646,13 @@
       <c r="M26" t="s">
         <v>37</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="5">
         <v>1817</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="5">
         <v>30000</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="5">
         <v>18000</v>
       </c>
     </row>
@@ -2658,18 +2661,18 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="I27" s="2">
+      <c r="G27" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I27" s="5">
         <v>15000</v>
       </c>
       <c r="L27" t="s">
@@ -2678,13 +2681,13 @@
       <c r="M27" t="s">
         <v>21</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="5">
         <v>1838</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="5">
         <v>6500</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="5">
         <v>8500</v>
       </c>
     </row>
@@ -2693,18 +2696,18 @@
         <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I28" s="2">
+      <c r="G28" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I28" s="5">
         <v>18000</v>
       </c>
       <c r="L28" t="s">
@@ -2713,13 +2716,13 @@
       <c r="M28" t="s">
         <v>24</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="5">
         <v>1907</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="5">
         <v>9000</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="5">
         <v>9000</v>
       </c>
     </row>
@@ -2728,18 +2731,18 @@
         <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="I29" s="2">
+      <c r="G29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I29" s="5">
         <v>45000</v>
       </c>
       <c r="L29" t="s">
@@ -2748,13 +2751,13 @@
       <c r="M29" t="s">
         <v>39</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="5">
         <v>1848</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="5">
         <v>30000</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="5">
         <v>15000</v>
       </c>
     </row>
@@ -2763,18 +2766,18 @@
         <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I30" s="2">
+      <c r="G30" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I30" s="5">
         <v>60000</v>
       </c>
       <c r="L30" t="s">
@@ -2783,13 +2786,13 @@
       <c r="M30" t="s">
         <v>61</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="5">
         <v>1831</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="5">
         <v>30000</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="5">
         <v>30000</v>
       </c>
     </row>
@@ -2798,33 +2801,33 @@
         <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>361</v>
+      <c r="G31" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="H31" t="s">
-        <v>393</v>
-      </c>
-      <c r="I31" s="2">
+        <v>392</v>
+      </c>
+      <c r="I31" s="5">
         <v>38000</v>
       </c>
       <c r="L31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s">
         <v>50</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="5">
         <v>1479</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="5">
         <v>20000</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="5">
         <v>18000</v>
       </c>
     </row>
@@ -2833,18 +2836,18 @@
         <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="I32" s="2">
+      <c r="G32" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I32" s="5">
         <v>60000</v>
       </c>
       <c r="L32" t="s">
@@ -2853,13 +2856,13 @@
       <c r="M32" t="s">
         <v>64</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="5">
         <v>1908</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="5">
         <v>40000</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="5">
         <v>20000</v>
       </c>
     </row>
@@ -2868,18 +2871,18 @@
         <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C33" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I33" s="2">
+      <c r="G33" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="I33" s="5">
         <v>45000</v>
       </c>
       <c r="L33" t="s">
@@ -2888,13 +2891,13 @@
       <c r="M33" t="s">
         <v>66</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="5">
         <v>1582</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="5">
         <v>25000</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="5">
         <v>20000</v>
       </c>
     </row>
@@ -2903,18 +2906,18 @@
         <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="I34" s="2">
+      <c r="G34" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I34" s="5">
         <v>30000</v>
       </c>
       <c r="L34" t="s">
@@ -2923,13 +2926,13 @@
       <c r="M34" t="s">
         <v>39</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="5">
         <v>1789</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="5">
         <v>20000</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="5">
         <v>10000</v>
       </c>
     </row>
@@ -2938,18 +2941,18 @@
         <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="I35" s="2">
+      <c r="G35" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I35" s="5">
         <v>50000</v>
       </c>
       <c r="L35" t="s">
@@ -2958,13 +2961,13 @@
       <c r="M35" t="s">
         <v>39</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="5">
         <v>1851</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="5">
         <v>33000</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="5">
         <v>17000</v>
       </c>
     </row>
@@ -2973,33 +2976,33 @@
         <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>338</v>
+      <c r="G36" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="H36" t="s">
-        <v>388</v>
-      </c>
-      <c r="I36" s="2">
+        <v>387</v>
+      </c>
+      <c r="I36" s="5">
         <v>23000</v>
       </c>
       <c r="L36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M36" t="s">
         <v>70</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="5">
         <v>1897</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="5">
         <v>12000</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="5">
         <v>11000</v>
       </c>
     </row>
@@ -3008,18 +3011,18 @@
         <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I37" s="2">
+      <c r="G37" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I37" s="5">
         <v>2000</v>
       </c>
       <c r="L37" t="s">
@@ -3028,13 +3031,13 @@
       <c r="M37" t="s">
         <v>73</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="5">
         <v>1901</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="5">
         <v>2000</v>
       </c>
     </row>
@@ -3043,18 +3046,18 @@
         <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="G38" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I38" s="5">
         <v>50000</v>
       </c>
       <c r="L38" t="s">
@@ -3063,13 +3066,13 @@
       <c r="M38" t="s">
         <v>39</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="5">
         <v>1867</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="5">
         <v>30000</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="5">
         <v>20000</v>
       </c>
     </row>
@@ -3078,18 +3081,18 @@
         <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="I39" s="2">
+      <c r="G39" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I39" s="5">
         <v>40000</v>
       </c>
       <c r="L39" t="s">
@@ -3098,13 +3101,13 @@
       <c r="M39" t="s">
         <v>66</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="5">
         <v>1824</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="5">
         <v>25000</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="5">
         <v>15000</v>
       </c>
     </row>
@@ -3113,18 +3116,18 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I40" s="2">
+      <c r="G40" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I40" s="5">
         <v>50000</v>
       </c>
       <c r="L40" t="s">
@@ -3133,13 +3136,13 @@
       <c r="M40" t="s">
         <v>77</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="5">
         <v>1853</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="5">
         <v>30000</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="5">
         <v>20000</v>
       </c>
     </row>
@@ -3148,2133 +3151,2133 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>356</v>
+      <c r="G41" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="H41" t="s">
-        <v>355</v>
-      </c>
-      <c r="I41" t="s">
+        <v>354</v>
+      </c>
+      <c r="I41" s="5">
+        <v>40000</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="M41" t="s">
         <v>79</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="M41" t="s">
-        <v>80</v>
-      </c>
-      <c r="N41">
+      <c r="N41" s="5">
         <v>1257</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="5">
         <v>30000</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H42" t="s">
+        <v>383</v>
+      </c>
+      <c r="I42" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="M42" t="s">
         <v>81</v>
       </c>
-      <c r="B42" t="s">
-        <v>210</v>
-      </c>
-      <c r="C42" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="H42" t="s">
-        <v>384</v>
-      </c>
-      <c r="I42" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="M42" t="s">
-        <v>82</v>
-      </c>
-      <c r="N42">
+      <c r="N42" s="5">
         <v>2015</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="5">
         <v>15000</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I43" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M43" t="s">
         <v>83</v>
       </c>
-      <c r="B43" t="s">
-        <v>211</v>
-      </c>
-      <c r="C43" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="I43" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="M43" t="s">
-        <v>84</v>
-      </c>
-      <c r="N43">
+      <c r="N43" s="5">
         <v>1386</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="5">
         <v>20000</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I44" s="5">
+        <v>35000</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="M44" t="s">
         <v>85</v>
       </c>
-      <c r="B44" t="s">
-        <v>212</v>
-      </c>
-      <c r="C44" t="s">
-        <v>23</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="I44" s="2">
-        <v>35000</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="M44" t="s">
-        <v>86</v>
-      </c>
-      <c r="N44">
+      <c r="N44" s="5">
         <v>1876</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="5">
         <v>30000</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="5">
         <v>5000</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" t="s">
         <v>87</v>
       </c>
-      <c r="B45" t="s">
-        <v>213</v>
-      </c>
-      <c r="C45" t="s">
-        <v>88</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>348</v>
+      <c r="G45" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
-      </c>
-      <c r="I45" s="2">
+        <v>346</v>
+      </c>
+      <c r="I45" s="5">
         <v>3000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>304</v>
+      <c r="L45" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="M45" t="s">
         <v>50</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="5">
         <v>1810</v>
       </c>
-      <c r="P45" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q45" s="2">
+      <c r="P45" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q45" s="5">
         <v>3000</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C46" t="s">
         <v>23</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="I46" s="2">
+      <c r="G46" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="I46" s="5">
         <v>25000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>90</v>
+      <c r="L46" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="M46" t="s">
         <v>39</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="5">
         <v>1909</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="5">
         <v>20000</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="5">
         <v>5000</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I47" s="2">
+      <c r="G47" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I47" s="5">
         <v>30000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>91</v>
+      <c r="L47" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="M47" t="s">
         <v>66</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="5">
         <v>1829</v>
       </c>
-      <c r="P47" s="2">
+      <c r="P47" s="5">
         <v>16000</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47" s="5">
         <v>14000</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C48" t="s">
         <v>23</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>333</v>
+      <c r="G48" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H48" t="s">
-        <v>379</v>
-      </c>
-      <c r="I48" s="2">
+        <v>378</v>
+      </c>
+      <c r="I48" s="5">
         <v>30000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>303</v>
+      <c r="L48" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="M48" t="s">
         <v>50</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="5">
         <v>1636</v>
       </c>
-      <c r="P48" s="2">
+      <c r="P48" s="5">
         <v>20000</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>216</v>
+      </c>
+      <c r="C49" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I49" s="5">
+        <v>3700</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M49" t="s">
+        <v>94</v>
+      </c>
+      <c r="N49" s="5">
+        <v>1943</v>
+      </c>
+      <c r="P49" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B49" t="s">
-        <v>217</v>
-      </c>
-      <c r="C49" t="s">
-        <v>88</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="I49" s="2">
-        <v>3700</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M49" t="s">
-        <v>95</v>
-      </c>
-      <c r="N49">
-        <v>1943</v>
-      </c>
-      <c r="P49" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q49" s="2">
+      <c r="Q49" s="5">
         <v>3700</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" t="s">
+        <v>217</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H50" t="s">
+        <v>350</v>
+      </c>
+      <c r="I50" s="5">
+        <v>50000</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M50" t="s">
         <v>96</v>
       </c>
-      <c r="B50" t="s">
-        <v>218</v>
-      </c>
-      <c r="C50" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H50" t="s">
-        <v>351</v>
-      </c>
-      <c r="I50" s="2">
-        <v>50000</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="M50" t="s">
-        <v>97</v>
-      </c>
-      <c r="N50">
+      <c r="N50" s="5">
         <v>1911</v>
       </c>
-      <c r="P50" s="2">
+      <c r="P50" s="5">
         <v>20000</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50" s="5">
         <v>30000</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C51" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>323</v>
+      <c r="G51" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="H51" t="s">
-        <v>370</v>
-      </c>
-      <c r="I51" s="2">
+        <v>369</v>
+      </c>
+      <c r="I51" s="5">
         <v>40000</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>301</v>
+      <c r="L51" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="M51" t="s">
-        <v>84</v>
-      </c>
-      <c r="N51">
+        <v>83</v>
+      </c>
+      <c r="N51" s="5">
         <v>1827</v>
       </c>
-      <c r="P51" s="2">
+      <c r="P51" s="5">
         <v>20000</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51" s="5">
         <v>20000</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I52" s="2">
+      <c r="G52" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I52" s="5">
         <v>50000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>99</v>
+      <c r="L52" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="M52" t="s">
         <v>39</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="5">
         <v>1883</v>
       </c>
-      <c r="P52" s="2">
+      <c r="P52" s="5">
         <v>40000</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="I53" s="2">
+      <c r="G53" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I53" s="5">
         <v>13000</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="L53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M53" t="s">
         <v>100</v>
       </c>
-      <c r="M53" t="s">
-        <v>101</v>
-      </c>
-      <c r="N53">
+      <c r="N53" s="5">
         <v>1873</v>
       </c>
-      <c r="P53" s="2">
+      <c r="P53" s="5">
         <v>7000</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53" s="5">
         <v>6000</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="I54" s="2">
+      <c r="G54" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="I54" s="5">
         <v>40000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>102</v>
+      <c r="L54" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="M54" t="s">
         <v>39</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="5">
         <v>1856</v>
       </c>
-      <c r="P54" s="2">
+      <c r="P54" s="5">
         <v>30000</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B55" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="I55" s="2">
+      <c r="G55" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I55" s="5">
         <v>47000</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>103</v>
+      <c r="L55" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="M55" t="s">
         <v>21</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="5">
         <v>1880</v>
       </c>
-      <c r="P55" s="2">
+      <c r="P55" s="5">
         <v>19000</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55" s="5">
         <v>28000</v>
       </c>
     </row>
     <row r="56" spans="1:17">
       <c r="A56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" t="s">
+        <v>223</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I56" s="5">
+        <v>55000</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M56" t="s">
         <v>104</v>
       </c>
-      <c r="B56" t="s">
-        <v>224</v>
-      </c>
-      <c r="C56" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="I56" s="2">
-        <v>55000</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="M56" t="s">
-        <v>105</v>
-      </c>
-      <c r="N56">
+      <c r="N56" s="5">
         <v>1909</v>
       </c>
-      <c r="P56" s="2">
+      <c r="P56" s="5">
         <v>40000</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" t="s">
+        <v>224</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="H57" t="s">
+        <v>370</v>
+      </c>
+      <c r="I57" s="5">
+        <v>35000</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M57" t="s">
         <v>106</v>
       </c>
-      <c r="B57" t="s">
-        <v>225</v>
-      </c>
-      <c r="C57" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="H57" t="s">
-        <v>371</v>
-      </c>
-      <c r="I57" s="2">
-        <v>35000</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="M57" t="s">
-        <v>107</v>
-      </c>
-      <c r="N57">
+      <c r="N57" s="5">
         <v>1640</v>
       </c>
-      <c r="P57" s="2">
+      <c r="P57" s="5">
         <v>20000</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="58" spans="1:17">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>323</v>
+      <c r="G58" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="H58" t="s">
-        <v>370</v>
-      </c>
-      <c r="I58" s="2">
+        <v>369</v>
+      </c>
+      <c r="I58" s="5">
         <v>50000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>299</v>
+      <c r="L58" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="M58" t="s">
-        <v>84</v>
-      </c>
-      <c r="N58">
+        <v>83</v>
+      </c>
+      <c r="N58" s="5">
         <v>1472</v>
       </c>
-      <c r="P58" s="2">
+      <c r="P58" s="5">
         <v>30000</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58" s="5">
         <v>20000</v>
       </c>
     </row>
     <row r="59" spans="1:17">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C59" t="s">
         <v>23</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>325</v>
+      <c r="G59" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="H59" t="s">
-        <v>369</v>
-      </c>
-      <c r="I59" s="2">
+        <v>368</v>
+      </c>
+      <c r="I59" s="5">
         <v>26000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>298</v>
+      <c r="L59" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="M59" t="s">
         <v>50</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="5">
         <v>1833</v>
       </c>
-      <c r="P59" s="2">
+      <c r="P59" s="5">
         <v>14000</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59" s="5">
         <v>12000</v>
       </c>
     </row>
     <row r="60" spans="1:17">
       <c r="A60" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" t="s">
+        <v>227</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H60" t="s">
+        <v>367</v>
+      </c>
+      <c r="I60" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="M60" t="s">
         <v>110</v>
       </c>
-      <c r="B60" t="s">
-        <v>228</v>
-      </c>
-      <c r="C60" t="s">
-        <v>23</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H60" t="s">
-        <v>368</v>
-      </c>
-      <c r="I60" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="M60" t="s">
-        <v>111</v>
-      </c>
-      <c r="N60">
+      <c r="N60" s="5">
         <v>1614</v>
       </c>
-      <c r="P60" s="2">
+      <c r="P60" s="5">
         <v>18000</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60" s="5">
         <v>12000</v>
       </c>
     </row>
     <row r="61" spans="1:17">
       <c r="A61" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H61" t="s">
+        <v>366</v>
+      </c>
+      <c r="I61" s="5">
+        <v>17000</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="M61" t="s">
         <v>112</v>
       </c>
-      <c r="B61" t="s">
-        <v>229</v>
-      </c>
-      <c r="C61" t="s">
-        <v>23</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H61" t="s">
-        <v>367</v>
-      </c>
-      <c r="I61" s="2">
-        <v>17000</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="M61" t="s">
-        <v>113</v>
-      </c>
-      <c r="N61">
+      <c r="N61" s="5">
         <v>1559</v>
       </c>
-      <c r="P61" s="2">
+      <c r="P61" s="5">
         <v>9000</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61" s="5">
         <v>8000</v>
       </c>
     </row>
     <row r="62" spans="1:17">
       <c r="A62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B62" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I62" s="5">
+        <v>27000</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M62" t="s">
         <v>114</v>
       </c>
-      <c r="B62" t="s">
-        <v>230</v>
-      </c>
-      <c r="C62" t="s">
-        <v>23</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="I62" s="2">
-        <v>27000</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="M62" t="s">
-        <v>115</v>
-      </c>
-      <c r="N62">
+      <c r="N62" s="5">
         <v>1833</v>
       </c>
-      <c r="P62" s="2">
+      <c r="P62" s="5">
         <v>18000</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62" s="5">
         <v>9000</v>
       </c>
     </row>
     <row r="63" spans="1:17">
       <c r="A63" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H63" t="s">
+        <v>363</v>
+      </c>
+      <c r="I63" s="5">
+        <v>28000</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="M63" t="s">
         <v>116</v>
       </c>
-      <c r="B63" t="s">
-        <v>231</v>
-      </c>
-      <c r="C63" t="s">
-        <v>23</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="H63" t="s">
-        <v>364</v>
-      </c>
-      <c r="I63" s="2">
-        <v>28000</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="M63" t="s">
-        <v>117</v>
-      </c>
-      <c r="N63">
+      <c r="N63" s="5">
         <v>1811</v>
       </c>
-      <c r="P63" s="2">
+      <c r="P63" s="5">
         <v>20000</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="Q63" s="5">
         <v>8000</v>
       </c>
     </row>
     <row r="64" spans="1:17">
       <c r="A64" t="s">
+        <v>117</v>
+      </c>
+      <c r="B64" t="s">
+        <v>231</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H64" t="s">
+        <v>362</v>
+      </c>
+      <c r="I64" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="M64" t="s">
         <v>118</v>
       </c>
-      <c r="B64" t="s">
-        <v>232</v>
-      </c>
-      <c r="C64" t="s">
-        <v>23</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H64" t="s">
-        <v>363</v>
-      </c>
-      <c r="I64" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="M64" t="s">
-        <v>119</v>
-      </c>
-      <c r="N64">
+      <c r="N64" s="5">
         <v>1477</v>
       </c>
-      <c r="P64" s="2">
+      <c r="P64" s="5">
         <v>20000</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="65" spans="1:17">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="I65" s="2">
+      <c r="G65" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I65" s="5">
         <v>36000</v>
       </c>
-      <c r="L65" s="3" t="s">
-        <v>120</v>
+      <c r="L65" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="M65" t="s">
-        <v>86</v>
-      </c>
-      <c r="N65">
+        <v>85</v>
+      </c>
+      <c r="N65" s="5">
         <v>1965</v>
       </c>
-      <c r="P65" s="2">
+      <c r="P65" s="5">
         <v>30000</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q65" s="5">
         <v>6000</v>
       </c>
     </row>
     <row r="66" spans="1:17">
       <c r="A66" t="s">
+        <v>120</v>
+      </c>
+      <c r="B66" t="s">
+        <v>233</v>
+      </c>
+      <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H66" t="s">
+        <v>359</v>
+      </c>
+      <c r="I66" s="5">
+        <v>40000</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="M66" t="s">
         <v>121</v>
       </c>
-      <c r="B66" t="s">
-        <v>234</v>
-      </c>
-      <c r="C66" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="H66" t="s">
-        <v>360</v>
-      </c>
-      <c r="I66" s="2">
-        <v>40000</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="M66" t="s">
-        <v>122</v>
-      </c>
-      <c r="N66">
+      <c r="N66" s="5">
         <v>1928</v>
       </c>
-      <c r="P66" s="2">
+      <c r="P66" s="5">
         <v>25000</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="67" spans="1:17">
       <c r="A67" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I67" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M67" t="s">
         <v>123</v>
       </c>
-      <c r="B67" t="s">
-        <v>235</v>
-      </c>
-      <c r="C67" t="s">
-        <v>23</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="I67" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M67" t="s">
-        <v>124</v>
-      </c>
-      <c r="N67">
+      <c r="N67" s="5">
         <v>1887</v>
       </c>
-      <c r="P67" s="2">
+      <c r="P67" s="5">
         <v>20000</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="68" spans="1:17">
       <c r="A68" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B68" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C68" t="s">
         <v>23</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H68" s="3" t="s">
+      <c r="G68" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="I68" s="2">
+      <c r="H68" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I68" s="5">
         <v>40000</v>
       </c>
-      <c r="L68" s="3" t="s">
-        <v>292</v>
+      <c r="L68" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="M68" t="s">
         <v>64</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="5">
         <v>1821</v>
       </c>
-      <c r="P68" s="2">
+      <c r="P68" s="5">
         <v>30000</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="69" spans="1:17">
       <c r="A69" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B69" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="I69" s="2">
+      <c r="G69" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="I69" s="5">
         <v>28000</v>
       </c>
-      <c r="L69" s="3" t="s">
-        <v>291</v>
+      <c r="L69" s="2" t="s">
+        <v>290</v>
       </c>
       <c r="M69" t="s">
-        <v>86</v>
-      </c>
-      <c r="N69">
+        <v>85</v>
+      </c>
+      <c r="N69" s="5">
         <v>1787</v>
       </c>
-      <c r="P69" s="2">
+      <c r="P69" s="5">
         <v>19000</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69" s="5">
         <v>9000</v>
       </c>
     </row>
     <row r="70" spans="1:17">
       <c r="A70" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>356</v>
+      <c r="G70" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="H70" t="s">
-        <v>355</v>
-      </c>
-      <c r="I70" s="2">
+        <v>354</v>
+      </c>
+      <c r="I70" s="5">
         <v>1800</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>290</v>
+      <c r="L70" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="M70" t="s">
-        <v>82</v>
-      </c>
-      <c r="N70">
+        <v>81</v>
+      </c>
+      <c r="N70" s="5">
         <v>1794</v>
       </c>
-      <c r="P70">
+      <c r="P70" s="5">
         <v>600</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70" s="5">
         <v>1200</v>
       </c>
     </row>
     <row r="71" spans="1:17">
       <c r="A71" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" t="s">
+        <v>238</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H71" t="s">
+        <v>353</v>
+      </c>
+      <c r="I71" s="5">
+        <v>45000</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M71" t="s">
         <v>128</v>
       </c>
-      <c r="B71" t="s">
-        <v>239</v>
-      </c>
-      <c r="C71" t="s">
-        <v>23</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="H71" t="s">
-        <v>354</v>
-      </c>
-      <c r="I71" s="2">
-        <v>45000</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="M71" t="s">
-        <v>129</v>
-      </c>
-      <c r="N71">
+      <c r="N71" s="5">
         <v>1817</v>
       </c>
-      <c r="P71" s="2">
+      <c r="P71" s="5">
         <v>30000</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="72" spans="1:17">
       <c r="A72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
+        <v>239</v>
+      </c>
+      <c r="C72" t="s">
         <v>130</v>
       </c>
-      <c r="B72" t="s">
-        <v>240</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="G72" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I72" s="5">
+        <v>1000</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M72" t="s">
+        <v>132</v>
+      </c>
+      <c r="N72" s="5">
+        <v>1972</v>
+      </c>
+      <c r="P72" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="I72" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="M72" t="s">
-        <v>133</v>
-      </c>
-      <c r="N72">
-        <v>1972</v>
-      </c>
-      <c r="P72" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q72" s="2">
+      <c r="Q72" s="5">
         <v>1000</v>
       </c>
     </row>
     <row r="73" spans="1:17">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B73" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C73" t="s">
         <v>23</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>352</v>
+      <c r="G73" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="H73" t="s">
-        <v>351</v>
-      </c>
-      <c r="I73" s="2">
+        <v>350</v>
+      </c>
+      <c r="I73" s="5">
         <v>45000</v>
       </c>
-      <c r="L73" s="3" t="s">
-        <v>288</v>
+      <c r="L73" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="M73" t="s">
-        <v>97</v>
-      </c>
-      <c r="N73">
+        <v>96</v>
+      </c>
+      <c r="N73" s="5">
         <v>1898</v>
       </c>
-      <c r="P73" s="2">
+      <c r="P73" s="5">
         <v>20000</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73" s="5">
         <v>25000</v>
       </c>
     </row>
     <row r="74" spans="1:17">
       <c r="A74" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" t="s">
+        <v>241</v>
+      </c>
+      <c r="C74" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H74" t="s">
+        <v>349</v>
+      </c>
+      <c r="I74" s="5">
+        <v>28000</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M74" t="s">
         <v>135</v>
       </c>
-      <c r="B74" t="s">
-        <v>242</v>
-      </c>
-      <c r="C74" t="s">
-        <v>23</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H74" t="s">
-        <v>350</v>
-      </c>
-      <c r="I74" s="2">
-        <v>28000</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="M74" t="s">
-        <v>136</v>
-      </c>
-      <c r="N74">
+      <c r="N74" s="5">
         <v>1913</v>
       </c>
-      <c r="P74" s="2">
+      <c r="P74" s="5">
         <v>15000</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="Q74" s="5">
         <v>13000</v>
       </c>
     </row>
     <row r="75" spans="1:17">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B75" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C75" t="s">
         <v>18</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="I75" s="2">
+      <c r="G75" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I75" s="5">
         <v>7000</v>
       </c>
-      <c r="L75" s="3" t="s">
-        <v>137</v>
+      <c r="L75" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="M75" t="s">
-        <v>101</v>
-      </c>
-      <c r="N75">
+        <v>100</v>
+      </c>
+      <c r="N75" s="5">
         <v>1912</v>
       </c>
-      <c r="P75" s="2">
+      <c r="P75" s="5">
         <v>4000</v>
       </c>
-      <c r="Q75" s="2">
+      <c r="Q75" s="5">
         <v>3000</v>
       </c>
     </row>
     <row r="76" spans="1:17">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B76" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>348</v>
+      <c r="G76" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="H76" t="s">
-        <v>347</v>
-      </c>
-      <c r="I76" s="2">
+        <v>346</v>
+      </c>
+      <c r="I76" s="5">
         <v>30000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>286</v>
+      <c r="L76" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="M76" t="s">
-        <v>119</v>
-      </c>
-      <c r="N76">
+        <v>118</v>
+      </c>
+      <c r="N76" s="5">
         <v>1878</v>
       </c>
-      <c r="P76" s="2">
+      <c r="P76" s="5">
         <v>20000</v>
       </c>
-      <c r="Q76" s="2">
+      <c r="Q76" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="77" spans="1:17">
       <c r="A77" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B77" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>325</v>
+      <c r="G77" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="H77" t="s">
-        <v>346</v>
-      </c>
-      <c r="I77" s="2">
+        <v>345</v>
+      </c>
+      <c r="I77" s="5">
         <v>12000</v>
       </c>
-      <c r="L77" s="3" t="s">
-        <v>285</v>
+      <c r="L77" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="M77" t="s">
         <v>50</v>
       </c>
-      <c r="N77">
+      <c r="N77" s="5">
         <v>1853</v>
       </c>
-      <c r="P77" s="2">
+      <c r="P77" s="5">
         <v>6000</v>
       </c>
-      <c r="Q77" s="2">
+      <c r="Q77" s="5">
         <v>6000</v>
       </c>
     </row>
     <row r="78" spans="1:17">
       <c r="A78" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B78" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C78" t="s">
         <v>23</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="I78" s="2">
+      <c r="G78" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="I78" s="5">
         <v>45000</v>
       </c>
-      <c r="L78" s="3" t="s">
-        <v>284</v>
+      <c r="L78" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="M78" t="s">
         <v>39</v>
       </c>
-      <c r="N78">
+      <c r="N78" s="5">
         <v>1869</v>
       </c>
-      <c r="P78" s="2">
+      <c r="P78" s="5">
         <v>30000</v>
       </c>
-      <c r="Q78" s="2">
+      <c r="Q78" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="79" spans="1:17">
       <c r="A79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B79" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C79" t="s">
         <v>23</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I79" s="2">
+      <c r="G79" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I79" s="5">
         <v>80000</v>
       </c>
-      <c r="L79" s="3" t="s">
-        <v>141</v>
+      <c r="L79" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="M79" t="s">
-        <v>105</v>
-      </c>
-      <c r="N79">
+        <v>104</v>
+      </c>
+      <c r="N79" s="5">
         <v>1958</v>
       </c>
-      <c r="P79" s="2">
+      <c r="P79" s="5">
         <v>55000</v>
       </c>
-      <c r="Q79" s="2">
+      <c r="Q79" s="5">
         <v>25000</v>
       </c>
     </row>
     <row r="80" spans="1:17">
       <c r="A80" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" t="s">
+        <v>23</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="I80" s="5">
+        <v>50000</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M80" t="s">
         <v>142</v>
       </c>
-      <c r="B80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C80" t="s">
-        <v>23</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="I80" s="2">
-        <v>50000</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="M80" t="s">
-        <v>143</v>
-      </c>
-      <c r="N80">
+      <c r="N80" s="5">
         <v>1766</v>
       </c>
-      <c r="P80" s="2">
+      <c r="P80" s="5">
         <v>35000</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="81" spans="1:17">
       <c r="A81" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B81" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C81" t="s">
         <v>18</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="I81" s="2">
+      <c r="G81" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I81" s="5">
         <v>35000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>144</v>
+      <c r="L81" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="M81" t="s">
         <v>50</v>
       </c>
-      <c r="N81">
+      <c r="N81" s="5">
         <v>1839</v>
       </c>
-      <c r="P81" s="2">
+      <c r="P81" s="5">
         <v>16000</v>
       </c>
-      <c r="Q81" s="2">
+      <c r="Q81" s="5">
         <v>19000</v>
       </c>
     </row>
     <row r="82" spans="1:17">
       <c r="A82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B82" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C82" t="s">
         <v>18</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="I82" s="2">
+      <c r="G82" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="I82" s="5">
         <v>14000</v>
       </c>
-      <c r="L82" s="3" t="s">
-        <v>145</v>
+      <c r="L82" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="M82" t="s">
         <v>61</v>
       </c>
-      <c r="N82">
+      <c r="N82" s="5">
         <v>1900</v>
       </c>
-      <c r="P82" s="2">
+      <c r="P82" s="5">
         <v>7000</v>
       </c>
-      <c r="Q82" s="2">
+      <c r="Q82" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="83" spans="1:17">
       <c r="A83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B83" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I83" s="2">
+      <c r="G83" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I83" s="5">
         <v>61000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>282</v>
+      <c r="L83" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="M83" t="s">
         <v>39</v>
       </c>
-      <c r="N83">
+      <c r="N83" s="5">
         <v>1870</v>
       </c>
-      <c r="P83" s="2">
+      <c r="P83" s="5">
         <v>47000</v>
       </c>
-      <c r="Q83" s="2">
+      <c r="Q83" s="5">
         <v>14000</v>
       </c>
     </row>
     <row r="84" spans="1:17">
       <c r="A84" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B84" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C84" t="s">
         <v>23</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="I84" s="2">
+      <c r="G84" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I84" s="5">
         <v>45000</v>
       </c>
-      <c r="L84" s="3" t="s">
-        <v>281</v>
+      <c r="L84" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="M84" t="s">
         <v>77</v>
       </c>
-      <c r="N84">
+      <c r="N84" s="5">
         <v>1850</v>
       </c>
-      <c r="P84" s="2">
+      <c r="P84" s="5">
         <v>30000</v>
       </c>
-      <c r="Q84" s="2">
+      <c r="Q84" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="85" spans="1:17">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B85" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H85" s="3" t="s">
+      <c r="G85" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="I85" s="2">
+      <c r="H85" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="I85" s="5">
         <v>20000</v>
       </c>
-      <c r="L85" s="3" t="s">
-        <v>280</v>
+      <c r="L85" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="M85" t="s">
         <v>70</v>
       </c>
-      <c r="N85">
+      <c r="N85" s="5">
         <v>1871</v>
       </c>
-      <c r="P85" s="2">
+      <c r="P85" s="5">
         <v>12000</v>
       </c>
-      <c r="Q85" s="2">
+      <c r="Q85" s="5">
         <v>8000</v>
       </c>
     </row>
     <row r="86" spans="1:17">
       <c r="A86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B86" t="s">
+        <v>253</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I86" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M86" t="s">
         <v>149</v>
       </c>
-      <c r="B86" t="s">
-        <v>254</v>
-      </c>
-      <c r="C86" t="s">
-        <v>23</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="I86" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M86" t="s">
-        <v>150</v>
-      </c>
-      <c r="N86">
+      <c r="N86" s="5">
         <v>1885</v>
       </c>
-      <c r="P86" s="2">
+      <c r="P86" s="5">
         <v>15000</v>
       </c>
-      <c r="Q86" s="2">
+      <c r="Q86" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="87" spans="1:17">
       <c r="A87" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="I87" s="2">
+      <c r="G87" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I87" s="5">
         <v>46000</v>
       </c>
-      <c r="L87" s="3" t="s">
-        <v>279</v>
+      <c r="L87" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="M87" t="s">
         <v>39</v>
       </c>
-      <c r="N87">
+      <c r="N87" s="5">
         <v>1855</v>
       </c>
-      <c r="P87" s="2">
+      <c r="P87" s="5">
         <v>40000</v>
       </c>
-      <c r="Q87" s="2">
+      <c r="Q87" s="5">
         <v>6000</v>
       </c>
     </row>
     <row r="88" spans="1:17">
       <c r="A88" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C88" t="s">
         <v>23</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="I88" s="2">
+      <c r="G88" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I88" s="5">
         <v>39000</v>
       </c>
-      <c r="L88" s="3" t="s">
-        <v>152</v>
+      <c r="L88" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="M88" t="s">
         <v>39</v>
       </c>
-      <c r="N88">
+      <c r="N88" s="5">
         <v>1905</v>
       </c>
-      <c r="P88" s="2">
+      <c r="P88" s="5">
         <v>30000</v>
       </c>
-      <c r="Q88" s="2">
+      <c r="Q88" s="5">
         <v>9000</v>
       </c>
     </row>
     <row r="89" spans="1:17">
       <c r="A89" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B89" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C89" t="s">
         <v>23</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>333</v>
+      <c r="G89" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H89" t="s">
-        <v>332</v>
-      </c>
-      <c r="I89" s="2">
+        <v>331</v>
+      </c>
+      <c r="I89" s="5">
         <v>30000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>278</v>
+      <c r="L89" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="M89" t="s">
         <v>50</v>
       </c>
-      <c r="N89">
+      <c r="N89" s="5">
         <v>1575</v>
       </c>
-      <c r="P89" s="2">
+      <c r="P89" s="5">
         <v>20000</v>
       </c>
-      <c r="Q89" s="2">
+      <c r="Q89" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="90" spans="1:17">
       <c r="A90" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B90" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C90" t="s">
         <v>23</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="I90" s="2">
+      <c r="G90" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="I90" s="5">
         <v>55000</v>
       </c>
-      <c r="L90" s="3" t="s">
-        <v>154</v>
+      <c r="L90" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="M90" t="s">
         <v>39</v>
       </c>
-      <c r="N90">
+      <c r="N90" s="5">
         <v>1853</v>
       </c>
-      <c r="P90" s="2">
+      <c r="P90" s="5">
         <v>35000</v>
       </c>
-      <c r="Q90" s="2">
+      <c r="Q90" s="5">
         <v>20000</v>
       </c>
     </row>
     <row r="91" spans="1:17">
       <c r="A91" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B91" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C91" t="s">
         <v>23</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>330</v>
+      <c r="G91" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="H91" t="s">
-        <v>329</v>
-      </c>
-      <c r="I91" s="2">
+        <v>328</v>
+      </c>
+      <c r="I91" s="5">
         <v>60000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>277</v>
+      <c r="L91" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="M91" t="s">
         <v>50</v>
       </c>
-      <c r="N91">
+      <c r="N91" s="5">
         <v>1425</v>
       </c>
-      <c r="P91" s="2">
+      <c r="P91" s="5">
         <v>40000</v>
       </c>
-      <c r="Q91" s="2">
+      <c r="Q91" s="5">
         <v>20000</v>
       </c>
     </row>
     <row r="92" spans="1:17">
       <c r="A92" t="s">
+        <v>155</v>
+      </c>
+      <c r="B92" t="s">
+        <v>259</v>
+      </c>
+      <c r="C92" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" t="s">
         <v>156</v>
       </c>
-      <c r="B92" t="s">
-        <v>260</v>
-      </c>
-      <c r="C92" t="s">
-        <v>23</v>
-      </c>
-      <c r="G92" t="s">
-        <v>157</v>
-      </c>
       <c r="H92" t="s">
-        <v>157</v>
-      </c>
-      <c r="I92" s="2">
+        <v>156</v>
+      </c>
+      <c r="I92" s="5">
         <v>40000</v>
       </c>
-      <c r="L92" s="3" t="s">
-        <v>156</v>
+      <c r="L92" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="M92" t="s">
         <v>50</v>
       </c>
-      <c r="N92">
+      <c r="N92" s="5">
         <v>1905</v>
       </c>
-      <c r="P92" s="2">
+      <c r="P92" s="5">
         <v>28000</v>
       </c>
-      <c r="Q92" s="2">
+      <c r="Q92" s="5">
         <v>12000</v>
       </c>
     </row>
     <row r="93" spans="1:17">
       <c r="A93" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B93" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C93" t="s">
         <v>23</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="I93" s="2">
+      <c r="G93" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I93" s="5">
         <v>25000</v>
       </c>
-      <c r="L93" s="3" t="s">
-        <v>158</v>
+      <c r="L93" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="M93" t="s">
-        <v>105</v>
-      </c>
-      <c r="N93">
+        <v>104</v>
+      </c>
+      <c r="N93" s="5">
         <v>1911</v>
       </c>
-      <c r="P93" s="2">
+      <c r="P93" s="5">
         <v>18000</v>
       </c>
-      <c r="Q93" s="2">
+      <c r="Q93" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="94" spans="1:17">
       <c r="A94" t="s">
+        <v>158</v>
+      </c>
+      <c r="B94" t="s">
+        <v>261</v>
+      </c>
+      <c r="C94" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="H94" t="s">
+        <v>325</v>
+      </c>
+      <c r="I94" s="5">
+        <v>40000</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M94" t="s">
         <v>159</v>
       </c>
-      <c r="B94" t="s">
-        <v>262</v>
-      </c>
-      <c r="C94" t="s">
-        <v>23</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H94" t="s">
-        <v>326</v>
-      </c>
-      <c r="I94" s="2">
-        <v>40000</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="M94" t="s">
-        <v>160</v>
-      </c>
-      <c r="N94">
+      <c r="N94" s="5">
         <v>1755</v>
       </c>
-      <c r="P94" s="2">
+      <c r="P94" s="5">
         <v>25000</v>
       </c>
-      <c r="Q94" s="2">
+      <c r="Q94" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="95" spans="1:17">
       <c r="A95" t="s">
+        <v>160</v>
+      </c>
+      <c r="B95" t="s">
+        <v>262</v>
+      </c>
+      <c r="C95" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H95" t="s">
+        <v>323</v>
+      </c>
+      <c r="I95" s="5">
+        <v>13000</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M95" t="s">
         <v>161</v>
       </c>
-      <c r="B95" t="s">
-        <v>263</v>
-      </c>
-      <c r="C95" t="s">
-        <v>23</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H95" t="s">
-        <v>324</v>
-      </c>
-      <c r="I95" s="2">
-        <v>13000</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="M95" t="s">
-        <v>162</v>
-      </c>
-      <c r="N95">
+      <c r="N95" s="5">
         <v>1460</v>
       </c>
-      <c r="P95" s="2">
+      <c r="P95" s="5">
         <v>7000</v>
       </c>
-      <c r="Q95" s="2">
+      <c r="Q95" s="5">
         <v>6000</v>
       </c>
     </row>
     <row r="96" spans="1:17">
       <c r="A96" t="s">
+        <v>162</v>
+      </c>
+      <c r="B96" t="s">
+        <v>263</v>
+      </c>
+      <c r="C96" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H96" t="s">
+        <v>321</v>
+      </c>
+      <c r="I96" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="M96" t="s">
         <v>163</v>
       </c>
-      <c r="B96" t="s">
-        <v>264</v>
-      </c>
-      <c r="C96" t="s">
-        <v>23</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H96" t="s">
-        <v>322</v>
-      </c>
-      <c r="I96" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="M96" t="s">
-        <v>164</v>
-      </c>
-      <c r="N96">
+      <c r="N96" s="5">
         <v>1737</v>
       </c>
-      <c r="P96" s="2">
+      <c r="P96" s="5">
         <v>20000</v>
       </c>
-      <c r="Q96" s="2">
+      <c r="Q96" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="97" spans="1:17">
       <c r="A97" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B97" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C97" t="s">
         <v>23</v>
       </c>
-      <c r="G97" s="3" t="s">
-        <v>321</v>
+      <c r="G97" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="H97" t="s">
-        <v>320</v>
-      </c>
-      <c r="I97" s="2">
+        <v>319</v>
+      </c>
+      <c r="I97" s="5">
         <v>20000</v>
       </c>
-      <c r="L97" s="3" t="s">
-        <v>165</v>
+      <c r="L97" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="M97" t="s">
         <v>77</v>
       </c>
-      <c r="N97">
+      <c r="N97" s="5">
         <v>1946</v>
       </c>
-      <c r="P97" s="2">
+      <c r="P97" s="5">
         <v>10000</v>
       </c>
-      <c r="Q97" s="2">
+      <c r="Q97" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="98" spans="1:17">
       <c r="A98" t="s">
+        <v>165</v>
+      </c>
+      <c r="B98" t="s">
+        <v>265</v>
+      </c>
+      <c r="C98" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I98" s="5">
+        <v>20000</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M98" t="s">
         <v>166</v>
       </c>
-      <c r="B98" t="s">
-        <v>266</v>
-      </c>
-      <c r="C98" t="s">
-        <v>23</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="I98" s="2">
-        <v>20000</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M98" t="s">
-        <v>167</v>
-      </c>
-      <c r="N98">
+      <c r="N98" s="5">
         <v>1962</v>
       </c>
-      <c r="P98" s="2">
+      <c r="P98" s="5">
         <v>18000</v>
       </c>
-      <c r="Q98" s="2">
+      <c r="Q98" s="5">
         <v>2000</v>
       </c>
     </row>
     <row r="99" spans="1:17">
       <c r="A99" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B99" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H99" s="3" t="s">
+      <c r="G99" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="I99" s="2">
+      <c r="H99" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I99" s="5">
         <v>30000</v>
       </c>
-      <c r="L99" s="3" t="s">
-        <v>273</v>
+      <c r="L99" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="M99" t="s">
-        <v>115</v>
-      </c>
-      <c r="N99">
+        <v>114</v>
+      </c>
+      <c r="N99" s="5">
         <v>1883</v>
       </c>
-      <c r="P99" s="2">
+      <c r="P99" s="5">
         <v>20000</v>
       </c>
-      <c r="Q99" s="2">
+      <c r="Q99" s="5">
         <v>10000</v>
       </c>
     </row>
     <row r="100" spans="1:17">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B100" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H100" s="3" t="s">
+      <c r="G100" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="I100" s="2">
+      <c r="H100" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I100" s="5">
         <v>45000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>169</v>
+      <c r="L100" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="M100" t="s">
         <v>39</v>
       </c>
-      <c r="N100">
+      <c r="N100" s="5">
         <v>1885</v>
       </c>
-      <c r="P100" s="2">
+      <c r="P100" s="5">
         <v>34000</v>
       </c>
-      <c r="Q100" s="2">
+      <c r="Q100" s="5">
         <v>11000</v>
       </c>
     </row>
     <row r="101" spans="1:17">
       <c r="A101" t="s">
+        <v>308</v>
+      </c>
+      <c r="B101" t="s">
+        <v>310</v>
+      </c>
+      <c r="C101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H101" t="s">
+        <v>312</v>
+      </c>
+      <c r="I101" s="5">
+        <v>61000</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M101" t="s">
         <v>309</v>
       </c>
-      <c r="B101" t="s">
-        <v>311</v>
-      </c>
-      <c r="C101" t="s">
-        <v>23</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="H101" t="s">
-        <v>313</v>
-      </c>
-      <c r="I101" s="2">
-        <v>61000</v>
-      </c>
-      <c r="L101" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="M101" t="s">
-        <v>310</v>
-      </c>
-      <c r="N101">
+      <c r="N101" s="5">
         <v>1957</v>
       </c>
-      <c r="P101" s="2">
+      <c r="P101" s="5">
         <v>38000</v>
       </c>
-      <c r="Q101" s="2">
+      <c r="Q101" s="5">
         <v>23000</v>
       </c>
     </row>

--- a/apps/api/data/excel_templates/universities.xlsx
+++ b/apps/api/data/excel_templates/universities.xlsx
@@ -6118,7 +6118,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:Q1"/>
   <conditionalFormatting sqref="R2:R100">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>

--- a/apps/api/data/excel_templates/universities.xlsx
+++ b/apps/api/data/excel_templates/universities.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -545,7 +545,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:Q1"/>
   <dataValidations count="6">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/universities.xlsx
+++ b/apps/api/data/excel_templates/universities.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -70,6 +70,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -542,6 +545,5517 @@
         <is>
           <t>postgraduates</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Harvard University</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000001</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Cambridge,Massachusetts</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Harvard University</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>1636</v>
+      </c>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Stanford,California</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>1885</v>
+      </c>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>University of Cambridge</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000003</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Cambridge,England</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>University of Cambridge</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Russell Group.</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology (MIT)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000004</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Cambridge,Massachusetts</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>11500</v>
+      </c>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology (MIT)</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Highly selective.</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>1861</v>
+      </c>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Berkeley</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000005</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Berkeley,California</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>42000</v>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Berkeley</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Public Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>1868</v>
+      </c>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n">
+        <v>31000</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Princeton University</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000006</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Princeton,New Jersey</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Princeton University</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>1746</v>
+      </c>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n">
+        <v>5300</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000007</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Oxford,England</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Russell Group.</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>1096</v>
+      </c>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Columbia University</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000008</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>New York City,New York</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>31000</v>
+      </c>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Columbia University</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>1754</v>
+      </c>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n">
+        <v>8200</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>California Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000009</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Pasadena,California</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>2200</v>
+      </c>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>California Institute of Technology</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Highly selective.</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>1891</v>
+      </c>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>University of Chicago</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000010</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Chicago,Illinois</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>17000</v>
+      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>University of Chicago</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>1890</v>
+      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n">
+        <v>6800</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Yale University</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000011</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>New Haven,Connecticut</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Yale University</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>1701</v>
+      </c>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n">
+        <v>6100</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Los Angeles</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000012</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Los Angeles,California</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Los Angeles</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Public Ivy League.</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>1919</v>
+      </c>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n">
+        <v>31000</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000013</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Seattle,Washington</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>54000</v>
+      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>1861</v>
+      </c>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n">
+        <v>32000</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000014</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Ithaca,New York</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>23000</v>
+      </c>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>1865</v>
+      </c>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>University of California, San Diego</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000015</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>San Diego,California</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>University of California, San Diego</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>1903</v>
+      </c>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000016</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>London,England</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Russell Group.</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>1826</v>
+      </c>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>University of Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000017</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Philadelphia,Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>University of Pennsylvania</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>1740</v>
+      </c>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000018</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Baltimore,Maryland</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>1876</v>
+      </c>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Swiss Federal Institute of Technology Zurich</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000019</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Eidgenössische Technische Hochschule Zürich</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>1855</v>
+      </c>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Washington University in St. Louis</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000020</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>St. Louis,Missouri</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Washington University in St. Louis</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>1853</v>
+      </c>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>University of California, San Francisco</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000021</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>San Francisco,California</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>University of California, San Francisco</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>1864</v>
+      </c>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> N/A (UCSF does not offer undergraduate programs)</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Northwestern University</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000022</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Evanston,Illinois</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Northwestern University</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>1851</v>
+      </c>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000023</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Toronto,Ontario</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. U15 Group.</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>1827</v>
+      </c>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000024</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>東京大学</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Imperial university.</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>1877</v>
+      </c>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>University of Michigan-Ann Arbor</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000025</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Ann Arbor,Michigan</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>48000</v>
+      </c>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>University of Michigan-Ann Arbor</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Public Ivy League.</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>1817</v>
+      </c>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Duke University</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000026</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Durham,North Carolina</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Duke University</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>1838</v>
+      </c>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Imperial College London</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000027</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>London,England</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Imperial College London</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. Russell Group.</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>1907</v>
+      </c>
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>University of Wisconsin - Madison</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000028</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Madison,Wisconsin</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>University of Wisconsin - Madison</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>1848</v>
+      </c>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000029</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>New York City,New York</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Highly selective.</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>1831</v>
+      </c>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>University of Copenhagen</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000030</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Københavns Universitet</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>1479</v>
+      </c>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000031</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Vancouver,British Columbia</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. U15 Group.</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>1908</v>
+      </c>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>The University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000032</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Edinburgh,Scotland</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>The University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Russell Group.</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>1582</v>
+      </c>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>University of North Carolina at Chapel Hill</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000033</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Chapel Hill,North Carolina</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>University of North Carolina at Chapel Hill</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>1789</v>
+      </c>
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>University of Minnesota, Twin Cities</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000034</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Minneapolis,Minnesota</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>University of Minnesota, Twin Cities</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>1851</v>
+      </c>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="n">
+        <v>33000</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Kyoto University</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000035</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Kyoto</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>23000</v>
+      </c>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>京都大学</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Imperial university.</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>1897</v>
+      </c>
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Rockefeller University</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000036</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>New York City,New York</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Rockefeller University</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>Focused on Biomedical Sciences</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>1901</v>
+      </c>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> N/A (Rockefeller is a graduate-only institution)</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>University of Illinois at Urbana-Champaign</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000037</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Urbana and Champaign,Illinois</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>University of Illinois at Urbana-Champaign</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>1867</v>
+      </c>
+      <c r="O38" s="6" t="n"/>
+      <c r="P38" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>The University of Manchester</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000038</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Manchester,England</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>The University of Manchester</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Russell Group.</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>1824</v>
+      </c>
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>The University of Melbourne</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000039</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Melbourne,Victoria</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>The University of Melbourne</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Group of Eight (Go8).</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>1853</v>
+      </c>
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Pierre and Marie Curie University - Paris 6</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000040</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Université Pierre-et-Marie-Curie (Paris VI)</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>Elite university in France. World-renowned university.</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>1257</v>
+      </c>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>University of Paris-Sud (Paris 11)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000041</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Orsay</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Université Paris-Sud (Paris XI)</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>Elite university in France</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Heidelberg University</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000042</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Heidelberg,Baden-Württemberg</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Ruprecht-Karls-Universität Heidelberg</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Elite university in Germany.</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>1386</v>
+      </c>
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>University of Colorado at Boulder</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000043</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Boulder,Colorado</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>University of Colorado Boulder</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>Public Ivy League</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>1876</v>
+      </c>
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Karolinska Institute</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000044</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Public Medical University</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Karolinska Institutet</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>1810</v>
+      </c>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> N/A (focuses primarily on graduate programs in medical and life sciences)</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Santa Barbara</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000045</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Santa Barbara,California</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Santa Barbara</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>1909</v>
+      </c>
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000046</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>London,England</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Russell Group.</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>1829</v>
+      </c>
+      <c r="O47" s="6" t="n"/>
+      <c r="P47" s="6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Utrecht University</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000047</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Universiteit Utrecht</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="n">
+        <v>1636</v>
+      </c>
+      <c r="O48" s="6" t="n"/>
+      <c r="P48" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>The University of Texas Southwestern Medical Center at Dallas</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000048</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Public Medical University</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Dallas,Texas</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>3700</v>
+      </c>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>The University of Texas Southwestern Medical Center at Dallas</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>Known for Medical Sciences, Healthcare and Research</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>1943</v>
+      </c>
+      <c r="O49" s="6" t="n"/>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> N/A (medical institution)</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000049</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. C9 League.</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>1911</v>
+      </c>
+      <c r="O50" s="6" t="n"/>
+      <c r="P50" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Technical University Munich</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000050</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>Technische Universität München</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Elite university in Germany.</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>1827</v>
+      </c>
+      <c r="O51" s="6" t="n"/>
+      <c r="P51" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>The University of Texas at Austin</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000051</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Austin,Texas</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>The University of Texas at Austin</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v>1883</v>
+      </c>
+      <c r="O52" s="6" t="n"/>
+      <c r="P52" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Vanderbilt University</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000052</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Nashville,Tennessee</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>Vanderbilt University</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>1873</v>
+      </c>
+      <c r="O53" s="6" t="n"/>
+      <c r="P53" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>University of Maryland, College Park</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000053</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>College Park,Maryland</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>University of Maryland, College Park</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>1856</v>
+      </c>
+      <c r="O54" s="6" t="n"/>
+      <c r="P54" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>University of Southern California</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000054</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Los Angeles,California</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>47000</v>
+      </c>
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>University of Southern California</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>1880</v>
+      </c>
+      <c r="O55" s="6" t="n"/>
+      <c r="P55" s="6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>The University of Queensland</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000055</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Brisbane,Queensland</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>55000</v>
+      </c>
+      <c r="J56" s="6" t="n"/>
+      <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>The University of Queensland</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>Group of Eight (Go8)</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>1909</v>
+      </c>
+      <c r="O56" s="6" t="n"/>
+      <c r="P56" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000056</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>Helsingin yliopisto</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>Known for Medical Sciences, Humanities and Social Sciences</t>
+        </is>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="O57" s="6" t="n"/>
+      <c r="P57" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>University of Munich</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000057</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J58" s="6" t="n"/>
+      <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>Ludwig-Maximilians-Universität München</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Elite university in Germany.</t>
+        </is>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>1472</v>
+      </c>
+      <c r="O58" s="6" t="n"/>
+      <c r="P58" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>University of Zurich</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000058</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>Universität Zürich</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>1833</v>
+      </c>
+      <c r="O59" s="6" t="n"/>
+      <c r="P59" s="6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000059</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J60" s="6" t="n"/>
+      <c r="K60" s="6" t="n"/>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>Rijksuniversiteit Groningen</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>Known for Life Sciences, Arts and Social Sciences</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>1614</v>
+      </c>
+      <c r="O60" s="6" t="n"/>
+      <c r="P60" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>University of Geneva</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000060</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Geneva</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>17000</v>
+      </c>
+      <c r="J61" s="6" t="n"/>
+      <c r="K61" s="6" t="n"/>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>Université de Genève</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>Known for International Relations, Social Sciences and Law</t>
+        </is>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>1559</v>
+      </c>
+      <c r="O61" s="6" t="n"/>
+      <c r="P61" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>University of Bristol</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000061</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Bristol,England</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>27000</v>
+      </c>
+      <c r="J62" s="6" t="n"/>
+      <c r="K62" s="6" t="n"/>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>University of Bristol</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>Russell Group</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="n">
+        <v>1833</v>
+      </c>
+      <c r="O62" s="6" t="n"/>
+      <c r="P62" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>University of Oslo</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000062</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="6" t="n"/>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>Universitetet i Oslo</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>Known for Humanities, Natural Sciences and Social Sciences</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>1811</v>
+      </c>
+      <c r="O63" s="6" t="n"/>
+      <c r="P63" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Uppsala University</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000063</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J64" s="6" t="n"/>
+      <c r="K64" s="6" t="n"/>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>Uppsala universitet</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>Known for Humanities, Life Sciences and Social Sciences</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="n">
+        <v>1477</v>
+      </c>
+      <c r="O64" s="6" t="n"/>
+      <c r="P64" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Irvine</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000064</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Irvine,California</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="J65" s="6" t="n"/>
+      <c r="K65" s="6" t="n"/>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Irvine</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>Public Ivy League</t>
+        </is>
+      </c>
+      <c r="N65" s="6" t="n">
+        <v>1965</v>
+      </c>
+      <c r="O65" s="6" t="n"/>
+      <c r="P65" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000065</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Aarhus</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J66" s="6" t="n"/>
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>Aarhus Universitet</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>Known for Humanities, Business and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>1928</v>
+      </c>
+      <c r="O66" s="6" t="n"/>
+      <c r="P66" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Q66" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>McMaster University</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000066</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Hamilton,Ontario</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>McMaster University</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>U15 Group</t>
+        </is>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>1887</v>
+      </c>
+      <c r="O67" s="6" t="n"/>
+      <c r="P67" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q67" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>McGill University</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000067</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Montreal,Quebec</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J68" s="6" t="n"/>
+      <c r="K68" s="6" t="n"/>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>Université McGill</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. U15 Group.</t>
+        </is>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>1821</v>
+      </c>
+      <c r="O68" s="6" t="n"/>
+      <c r="P68" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q68" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>University of Pittsburgh, Pittsburgh Campus</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000068</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Pittsburgh,Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="J69" s="6" t="n"/>
+      <c r="K69" s="6" t="n"/>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>University of Pittsburgh</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>Public Ivy League</t>
+        </is>
+      </c>
+      <c r="N69" s="6" t="n">
+        <v>1787</v>
+      </c>
+      <c r="O69" s="6" t="n"/>
+      <c r="P69" s="6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q69" s="6" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>École Normale Supérieure - Paris</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000069</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J70" s="6" t="n"/>
+      <c r="K70" s="6" t="n"/>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>École normale supérieure</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>Elite university in France</t>
+        </is>
+      </c>
+      <c r="N70" s="6" t="n">
+        <v>1794</v>
+      </c>
+      <c r="O70" s="6" t="n"/>
+      <c r="P70" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q70" s="6" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Ghent University</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000070</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Ghent</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J71" s="6" t="n"/>
+      <c r="K71" s="6" t="n"/>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>Universiteit Gent</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>Known for Medical Sciences, Engineering and Life Sciences</t>
+        </is>
+      </c>
+      <c r="N71" s="6" t="n">
+        <v>1817</v>
+      </c>
+      <c r="O71" s="6" t="n"/>
+      <c r="P71" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q71" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Mayo Medical School</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000071</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Private Medical School</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Rochester,Minnesota</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J72" s="6" t="n"/>
+      <c r="K72" s="6" t="n"/>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>Mayo Medical School</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>Known for Medical Education and Clinical Research</t>
+        </is>
+      </c>
+      <c r="N72" s="6" t="n">
+        <v>1972</v>
+      </c>
+      <c r="O72" s="6" t="n"/>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> N/A (graduate-only institution)</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000072</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="6" t="n"/>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>World prestigious university. C9 League.</t>
+        </is>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>1898</v>
+      </c>
+      <c r="O73" s="6" t="n"/>
+      <c r="P73" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q73" s="6" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Erasmus University</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000073</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="J74" s="6" t="n"/>
+      <c r="K74" s="6" t="n"/>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>Erasmus Universiteit Rotterdam</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>Known for Social Sciences, Business and Medical Sciences</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>1913</v>
+      </c>
+      <c r="O74" s="6" t="n"/>
+      <c r="P74" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q74" s="6" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Rice University</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000074</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Houston,Texas</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="n"/>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>Rice University</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>Highly selective. Hidden Ivy League.</t>
+        </is>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>1912</v>
+      </c>
+      <c r="O75" s="6" t="n"/>
+      <c r="P75" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q75" s="6" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Stockholm University</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000075</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J76" s="6" t="n"/>
+      <c r="K76" s="6" t="n"/>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>Stockholms universitet</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>Known for Humanities, Life Sciences and Social Sciences</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="n">
+        <v>1878</v>
+      </c>
+      <c r="O76" s="6" t="n"/>
+      <c r="P76" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q76" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Swiss Federal Institute of Technology Lausanne</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000076</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="n"/>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J77" s="6" t="n"/>
+      <c r="K77" s="6" t="n"/>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>École polytechnique fédérale de Lausanne (EPFL)</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N77" s="6" t="n">
+        <v>1853</v>
+      </c>
+      <c r="O77" s="6" t="n"/>
+      <c r="P77" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Q77" s="6" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Purdue University - West Lafayette</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000077</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>West Lafayette,Indiana</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J78" s="6" t="n"/>
+      <c r="K78" s="6" t="n"/>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="n">
+        <v>1869</v>
+      </c>
+      <c r="O78" s="6" t="n"/>
+      <c r="P78" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q78" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Monash University</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000078</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="n"/>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Melbourne,Victoria</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J79" s="6" t="n"/>
+      <c r="K79" s="6" t="n"/>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>Monash University</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>Group of Eight (Go8)</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="n">
+        <v>1958</v>
+      </c>
+      <c r="O79" s="6" t="n"/>
+      <c r="P79" s="6" t="n">
+        <v>55000</v>
+      </c>
+      <c r="Q79" s="6" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Rutgers, The State University of New Jersey - New Brunswick</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000079</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="n"/>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>New Brunswick,New Jersey</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J80" s="6" t="n"/>
+      <c r="K80" s="6" t="n"/>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>Rutgers, The State University of New Jersey–New Brunswick</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public Ivy League
+</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="n">
+        <v>1766</v>
+      </c>
+      <c r="O80" s="6" t="n"/>
+      <c r="P80" s="6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Q80" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Boston University</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000080</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="6" t="n"/>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Boston,Massachusetts</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J81" s="6" t="n"/>
+      <c r="K81" s="6" t="n"/>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>Boston University</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="n">
+        <v>1839</v>
+      </c>
+      <c r="O81" s="6" t="n"/>
+      <c r="P81" s="6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="Q81" s="6" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000081</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Private Research University</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="6" t="n"/>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Pittsburgh,Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J82" s="6" t="n"/>
+      <c r="K82" s="6" t="n"/>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Highly selective.</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>1900</v>
+      </c>
+      <c r="O82" s="6" t="n"/>
+      <c r="P82" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Q82" s="6" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>The Ohio State University - Columbus</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000082</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n"/>
+      <c r="F83" s="6" t="n"/>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Columbus,Ohio</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>61000</v>
+      </c>
+      <c r="J83" s="6" t="n"/>
+      <c r="K83" s="6" t="n"/>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>The Ohio State University</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N83" s="6" t="n">
+        <v>1870</v>
+      </c>
+      <c r="O83" s="6" t="n"/>
+      <c r="P83" s="6" t="n">
+        <v>47000</v>
+      </c>
+      <c r="Q83" s="6" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>University of Sydney</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000083</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n"/>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Sydney,New South Wales</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J84" s="6" t="n"/>
+      <c r="K84" s="6" t="n"/>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>The University of Sydney</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Group of Eight (Go8).</t>
+        </is>
+      </c>
+      <c r="N84" s="6" t="n">
+        <v>1850</v>
+      </c>
+      <c r="O84" s="6" t="n"/>
+      <c r="P84" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q84" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Nagoya University</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000084</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="6" t="n"/>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>Nagoya,Aichi</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J85" s="6" t="n"/>
+      <c r="K85" s="6" t="n"/>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>名古屋大学</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Imperial university.</t>
+        </is>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>1871</v>
+      </c>
+      <c r="O85" s="6" t="n"/>
+      <c r="P85" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q85" s="6" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000085</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="6" t="n"/>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Atlanta,Georgia</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J86" s="6" t="n"/>
+      <c r="K86" s="6" t="n"/>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League, highly selective.</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="n">
+        <v>1885</v>
+      </c>
+      <c r="O86" s="6" t="n"/>
+      <c r="P86" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q86" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Pennsylvania State University - University Park</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000086</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="6" t="n"/>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>University Park,Pennsylvania</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="6" t="n"/>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>The Pennsylvania State University</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N87" s="6" t="n">
+        <v>1855</v>
+      </c>
+      <c r="O87" s="6" t="n"/>
+      <c r="P87" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="Q87" s="6" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Davis</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000087</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="6" t="n"/>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Davis,California</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>39000</v>
+      </c>
+      <c r="J88" s="6" t="n"/>
+      <c r="K88" s="6" t="n"/>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Davis</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N88" s="6" t="n">
+        <v>1905</v>
+      </c>
+      <c r="O88" s="6" t="n"/>
+      <c r="P88" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q88" s="6" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Leiden University</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000088</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="n"/>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Leiden</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J89" s="6" t="n"/>
+      <c r="K89" s="6" t="n"/>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>Universiteit Leiden</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="n">
+        <v>1575</v>
+      </c>
+      <c r="O89" s="6" t="n"/>
+      <c r="P89" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q89" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>University of Florida</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000089</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="6" t="n"/>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Gainesville,Florida</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>55000</v>
+      </c>
+      <c r="J90" s="6" t="n"/>
+      <c r="K90" s="6" t="n"/>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>University of Florida</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="n">
+        <v>1853</v>
+      </c>
+      <c r="O90" s="6" t="n"/>
+      <c r="P90" s="6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Q90" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>KU Leuven</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000090</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="6" t="n"/>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>Leuven</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="J91" s="6" t="n"/>
+      <c r="K91" s="6" t="n"/>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>Katholieke Universiteit Leuven</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N91" s="6" t="n">
+        <v>1425</v>
+      </c>
+      <c r="O91" s="6" t="n"/>
+      <c r="P91" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>National University of Singapore</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000091</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J92" s="6" t="n"/>
+      <c r="K92" s="6" t="n"/>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>National University of Singapore</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university</t>
+        </is>
+      </c>
+      <c r="N92" s="6" t="n">
+        <v>1905</v>
+      </c>
+      <c r="O92" s="6" t="n"/>
+      <c r="P92" s="6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Q92" s="6" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>The University of Western Australia</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000092</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="n"/>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>Perth,Western Australia</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J93" s="6" t="n"/>
+      <c r="K93" s="6" t="n"/>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>The University of Western Australia</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>Group of Eight (Go8)</t>
+        </is>
+      </c>
+      <c r="N93" s="6" t="n">
+        <v>1911</v>
+      </c>
+      <c r="O93" s="6" t="n"/>
+      <c r="P93" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="Q93" s="6" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Moscow State University</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000093</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="6" t="n"/>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J94" s="6" t="n"/>
+      <c r="K94" s="6" t="n"/>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>Московский государственный университет имени М. В. Ломоносова</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Elite university in Russia.</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="n">
+        <v>1755</v>
+      </c>
+      <c r="O94" s="6" t="n"/>
+      <c r="P94" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Q94" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>University of Basel</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000094</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="6" t="n"/>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="J95" s="6" t="n"/>
+      <c r="K95" s="6" t="n"/>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>Universität Basel</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>Known for Medical Sciences, Life Sciences and Humanities</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="n">
+        <v>1460</v>
+      </c>
+      <c r="O95" s="6" t="n"/>
+      <c r="P95" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Q95" s="6" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>University of Göttingen</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000095</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="6" t="n"/>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>Göttingen</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J96" s="6" t="n"/>
+      <c r="K96" s="6" t="n"/>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>Georg-August-Universität Göttingen</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>Elite university in Germany</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="n">
+        <v>1737</v>
+      </c>
+      <c r="O96" s="6" t="n"/>
+      <c r="P96" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q96" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>The Australian National University</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000096</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="6" t="n"/>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Canberra</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J97" s="6" t="n"/>
+      <c r="K97" s="6" t="n"/>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>The Australian National University</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university. Group of Eight (Go8).</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="n">
+        <v>1946</v>
+      </c>
+      <c r="O97" s="6" t="n"/>
+      <c r="P97" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q97" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000097</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>Santa Cruz,California</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J98" s="6" t="n"/>
+      <c r="K98" s="6" t="n"/>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>University of California, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>Known for Social Sciences, Natural Sciences and Arts</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="n">
+        <v>1962</v>
+      </c>
+      <c r="O98" s="6" t="n"/>
+      <c r="P98" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="Q98" s="6" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Cardiff University</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000098</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="6" t="n"/>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>Cardiff,Wales</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J99" s="6" t="n"/>
+      <c r="K99" s="6" t="n"/>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>Prifysgol Caerdydd</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>Russell Group</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="n">
+        <v>1883</v>
+      </c>
+      <c r="O99" s="6" t="n"/>
+      <c r="P99" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q99" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>University of Arizona</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000099</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="6" t="n"/>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>Tucson,Arizona</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J100" s="6" t="n"/>
+      <c r="K100" s="6" t="n"/>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>University of Arizona</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>World-renowned university, public Ivy League</t>
+        </is>
+      </c>
+      <c r="N100" s="6" t="n">
+        <v>1885</v>
+      </c>
+      <c r="O100" s="6" t="n"/>
+      <c r="P100" s="6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="Q100" s="6" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>King Saud University</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>UNI-000100</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>61000</v>
+      </c>
+      <c r="J101" s="6" t="n"/>
+      <c r="K101" s="6" t="n"/>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>جامعة الملك سعود</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>Leading public university in Saudi Arabia. Flagship institution with strong research programs and broad academic offerings.</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="n">
+        <v>1957</v>
+      </c>
+      <c r="O101" s="6" t="n"/>
+      <c r="P101" s="6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q101" s="6" t="n">
+        <v>23000</v>
       </c>
     </row>
   </sheetData>

--- a/apps/api/data/excel_templates/universities.xlsx
+++ b/apps/api/data/excel_templates/universities.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -70,9 +70,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,5513 +545,4913 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>UNI-000001</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Cambridge,Massachusetts</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" t="n">
         <v>20000</v>
       </c>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="N2" t="n">
         <v>1636</v>
       </c>
-      <c r="O2" s="6" t="n"/>
-      <c r="P2" s="6" t="n">
+      <c r="P2" t="n">
         <v>7000</v>
       </c>
-      <c r="Q2" s="6" t="n">
+      <c r="Q2" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>UNI-000002</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Stanford,California</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" t="n">
         <v>15000</v>
       </c>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="N3" t="n">
         <v>1885</v>
       </c>
-      <c r="O3" s="6" t="n"/>
-      <c r="P3" s="6" t="n">
+      <c r="P3" t="n">
         <v>7000</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="Q3" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>University of Cambridge</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>UNI-000003</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Cambridge,England</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" t="n">
         <v>24000</v>
       </c>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>University of Cambridge</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" t="n">
         <v>1209</v>
       </c>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="6" t="n">
+      <c r="P4" t="n">
         <v>12000</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Massachusetts Institute of Technology (MIT)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>UNI-000004</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Cambridge,Massachusetts</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" t="n">
         <v>11500</v>
       </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Massachusetts Institute of Technology (MIT)</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective.</t>
         </is>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" t="n">
         <v>1861</v>
       </c>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="6" t="n">
+      <c r="P5" t="n">
         <v>4500</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>University of California, Berkeley</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>UNI-000005</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Berkeley,California</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" t="n">
         <v>42000</v>
       </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>University of California, Berkeley</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>World prestigious university. Public Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" t="n">
         <v>1868</v>
       </c>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n">
+      <c r="P6" t="n">
         <v>31000</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="Q6" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>UNI-000006</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Princeton,New Jersey</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" t="n">
         <v>8000</v>
       </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" t="n">
         <v>1746</v>
       </c>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n">
+      <c r="P7" t="n">
         <v>5300</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q7" t="n">
         <v>2700</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>University of Oxford</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>UNI-000007</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Oxford,England</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" t="n">
         <v>24000</v>
       </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>University of Oxford</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="N8" t="n">
         <v>1096</v>
       </c>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n">
+      <c r="P8" t="n">
         <v>12000</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="Q8" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Columbia University</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>UNI-000008</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>New York City,New York</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" t="n">
         <v>31000</v>
       </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Columbia University</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" t="n">
         <v>1754</v>
       </c>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n">
+      <c r="P9" t="n">
         <v>8200</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q9" t="n">
         <v>22800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>California Institute of Technology</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>UNI-000009</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Pasadena,California</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" t="n">
         <v>2200</v>
       </c>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>California Institute of Technology</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective.</t>
         </is>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="N10" t="n">
         <v>1891</v>
       </c>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n">
+      <c r="P10" t="n">
         <v>1000</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="Q10" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>University of Chicago</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>UNI-000010</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Chicago,Illinois</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" t="n">
         <v>17000</v>
       </c>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>University of Chicago</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" t="n">
         <v>1890</v>
       </c>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n">
+      <c r="P11" t="n">
         <v>6800</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" t="n">
         <v>10200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>UNI-000011</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>New Haven,Connecticut</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" t="n">
         <v>13000</v>
       </c>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" t="n">
         <v>1701</v>
       </c>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n">
+      <c r="P12" t="n">
         <v>6100</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" t="n">
         <v>6900</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>University of California, Los Angeles</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>UNI-000012</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Los Angeles,California</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" t="n">
         <v>45000</v>
       </c>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>University of California, Los Angeles</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>World prestigious university. Public Ivy League.</t>
         </is>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" t="n">
         <v>1919</v>
       </c>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n">
+      <c r="P13" t="n">
         <v>31000</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>University of Washington</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>UNI-000013</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Seattle,Washington</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" t="n">
         <v>54000</v>
       </c>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>University of Washington</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" t="n">
         <v>1861</v>
       </c>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n">
+      <c r="P14" t="n">
         <v>32000</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Cornell University</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>UNI-000014</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Ithaca,New York</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" t="n">
         <v>23000</v>
       </c>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Cornell University</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" t="n">
         <v>1865</v>
       </c>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n">
+      <c r="P15" t="n">
         <v>15000</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>University of California, San Diego</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>UNI-000015</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>San Diego,California</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" t="n">
         <v>40000</v>
       </c>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>University of California, San Diego</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" t="n">
         <v>1903</v>
       </c>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n">
+      <c r="P16" t="n">
         <v>30000</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>University College London</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>UNI-000016</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>London,England</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" t="n">
         <v>45000</v>
       </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>University College London</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" t="n">
         <v>1826</v>
       </c>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n">
+      <c r="P17" t="n">
         <v>20000</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>University of Pennsylvania</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>UNI-000017</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Philadelphia,Pennsylvania</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" t="n">
         <v>25000</v>
       </c>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>University of Pennsylvania</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" t="n">
         <v>1740</v>
       </c>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n">
+      <c r="P18" t="n">
         <v>10000</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Johns Hopkins University</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>UNI-000018</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Baltimore,Maryland</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" t="n">
         <v>24000</v>
       </c>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Johns Hopkins University</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" t="n">
         <v>1876</v>
       </c>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n">
+      <c r="P19" t="n">
         <v>6000</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Swiss Federal Institute of Technology Zurich</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>UNI-000019</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" t="n">
         <v>20000</v>
       </c>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Eidgenössische Technische Hochschule Zürich</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>World prestigious university</t>
         </is>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" t="n">
         <v>1855</v>
       </c>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n">
+      <c r="P20" t="n">
         <v>10000</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Washington University in St. Louis</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>UNI-000020</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>St. Louis,Missouri</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" t="n">
         <v>15000</v>
       </c>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Washington University in St. Louis</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" t="n">
         <v>1853</v>
       </c>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n">
+      <c r="P21" t="n">
         <v>8000</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>University of California, San Francisco</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>UNI-000021</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>San Francisco,California</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" t="n">
         <v>3000</v>
       </c>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>University of California, San Francisco</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" t="n">
         <v>1864</v>
       </c>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (UCSF does not offer undergraduate programs)</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>UNI-000022</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Evanston,Illinois</t>
         </is>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" t="n">
         <v>21000</v>
       </c>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" t="n">
         <v>1851</v>
       </c>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="6" t="n">
+      <c r="P23" t="n">
         <v>8000</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>University of Toronto</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>UNI-000023</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Toronto,Ontario</t>
         </is>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" t="n">
         <v>90000</v>
       </c>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>University of Toronto</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>World prestigious university. U15 Group.</t>
         </is>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" t="n">
         <v>1827</v>
       </c>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="6" t="n">
+      <c r="P24" t="n">
         <v>60000</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>The University of Tokyo</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>UNI-000024</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" t="n">
         <v>30000</v>
       </c>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>東京大学</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>World prestigious university. Imperial university.</t>
         </is>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" t="n">
         <v>1877</v>
       </c>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="6" t="n">
+      <c r="P25" t="n">
         <v>15000</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>University of Michigan-Ann Arbor</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>UNI-000025</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Ann Arbor,Michigan</t>
         </is>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" t="n">
         <v>48000</v>
       </c>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>University of Michigan-Ann Arbor</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>World prestigious university. Public Ivy League.</t>
         </is>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" t="n">
         <v>1817</v>
       </c>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="6" t="n">
+      <c r="P26" t="n">
         <v>30000</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Duke University</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>UNI-000026</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Durham,North Carolina</t>
         </is>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" t="n">
         <v>15000</v>
       </c>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Duke University</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" t="n">
         <v>1838</v>
       </c>
-      <c r="O27" s="6" t="n"/>
-      <c r="P27" s="6" t="n">
+      <c r="P27" t="n">
         <v>6500</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" t="n">
         <v>8500</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Imperial College London</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>UNI-000027</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>London,England</t>
         </is>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" t="n">
         <v>18000</v>
       </c>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Imperial College London</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" t="n">
         <v>1907</v>
       </c>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="6" t="n">
+      <c r="P28" t="n">
         <v>9000</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>University of Wisconsin - Madison</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>UNI-000028</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Madison,Wisconsin</t>
         </is>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" t="n">
         <v>45000</v>
       </c>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>University of Wisconsin - Madison</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N29" t="n">
         <v>1848</v>
       </c>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="n">
+      <c r="P29" t="n">
         <v>30000</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="Q29" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>New York University</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>UNI-000029</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>New York City,New York</t>
         </is>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" t="n">
         <v>60000</v>
       </c>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>New York University</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective.</t>
         </is>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" t="n">
         <v>1831</v>
       </c>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="6" t="n">
+      <c r="P30" t="n">
         <v>30000</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="Q30" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>University of Copenhagen</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>UNI-000030</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Copenhagen</t>
         </is>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" t="n">
         <v>38000</v>
       </c>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Københavns Universitet</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" t="n">
         <v>1479</v>
       </c>
-      <c r="O31" s="6" t="n"/>
-      <c r="P31" s="6" t="n">
+      <c r="P31" t="n">
         <v>20000</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="Q31" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>University of British Columbia</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>UNI-000031</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Vancouver,British Columbia</t>
         </is>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" t="n">
         <v>60000</v>
       </c>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>University of British Columbia</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>World-renowned university. U15 Group.</t>
         </is>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N32" t="n">
         <v>1908</v>
       </c>
-      <c r="O32" s="6" t="n"/>
-      <c r="P32" s="6" t="n">
+      <c r="P32" t="n">
         <v>40000</v>
       </c>
-      <c r="Q32" s="6" t="n">
+      <c r="Q32" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>The University of Edinburgh</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>UNI-000032</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Edinburgh,Scotland</t>
         </is>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" t="n">
         <v>45000</v>
       </c>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>The University of Edinburgh</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>World-renowned university. Russell Group.</t>
         </is>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" t="n">
         <v>1582</v>
       </c>
-      <c r="O33" s="6" t="n"/>
-      <c r="P33" s="6" t="n">
+      <c r="P33" t="n">
         <v>25000</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="Q33" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>UNI-000033</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Chapel Hill,North Carolina</t>
         </is>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" t="n">
         <v>30000</v>
       </c>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="N34" t="n">
         <v>1789</v>
       </c>
-      <c r="O34" s="6" t="n"/>
-      <c r="P34" s="6" t="n">
+      <c r="P34" t="n">
         <v>20000</v>
       </c>
-      <c r="Q34" s="6" t="n">
+      <c r="Q34" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>UNI-000034</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Minneapolis,Minnesota</t>
         </is>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" t="n">
         <v>50000</v>
       </c>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" t="n">
         <v>1851</v>
       </c>
-      <c r="O35" s="6" t="n"/>
-      <c r="P35" s="6" t="n">
+      <c r="P35" t="n">
         <v>33000</v>
       </c>
-      <c r="Q35" s="6" t="n">
+      <c r="Q35" t="n">
         <v>17000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Kyoto University</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>UNI-000035</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Kyoto</t>
         </is>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" t="n">
         <v>23000</v>
       </c>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>京都大学</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>World-renowned university. Imperial university.</t>
         </is>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" t="n">
         <v>1897</v>
       </c>
-      <c r="O36" s="6" t="n"/>
-      <c r="P36" s="6" t="n">
+      <c r="P36" t="n">
         <v>12000</v>
       </c>
-      <c r="Q36" s="6" t="n">
+      <c r="Q36" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Rockefeller University</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>UNI-000036</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>New York City,New York</t>
         </is>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" t="n">
         <v>2000</v>
       </c>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Rockefeller University</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Focused on Biomedical Sciences</t>
         </is>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" t="n">
         <v>1901</v>
       </c>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="6" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (Rockefeller is a graduate-only institution)</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="n">
+      <c r="Q37" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>University of Illinois at Urbana-Champaign</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>UNI-000037</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Urbana and Champaign,Illinois</t>
         </is>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" t="n">
         <v>50000</v>
       </c>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="6" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>University of Illinois at Urbana-Champaign</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N38" t="n">
         <v>1867</v>
       </c>
-      <c r="O38" s="6" t="n"/>
-      <c r="P38" s="6" t="n">
+      <c r="P38" t="n">
         <v>30000</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="Q38" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>The University of Manchester</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>UNI-000038</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Manchester,England</t>
         </is>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" t="n">
         <v>40000</v>
       </c>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="6" t="n"/>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>The University of Manchester</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>World-renowned university. Russell Group.</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" t="n">
         <v>1824</v>
       </c>
-      <c r="O39" s="6" t="n"/>
-      <c r="P39" s="6" t="n">
+      <c r="P39" t="n">
         <v>25000</v>
       </c>
-      <c r="Q39" s="6" t="n">
+      <c r="Q39" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>The University of Melbourne</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>UNI-000039</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Melbourne,Victoria</t>
         </is>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I40" t="n">
         <v>50000</v>
       </c>
-      <c r="J40" s="6" t="n"/>
-      <c r="K40" s="6" t="n"/>
-      <c r="L40" s="6" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>The University of Melbourne</t>
         </is>
       </c>
-      <c r="M40" s="6" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>World-renowned university. Group of Eight (Go8).</t>
         </is>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" t="n">
         <v>1853</v>
       </c>
-      <c r="O40" s="6" t="n"/>
-      <c r="P40" s="6" t="n">
+      <c r="P40" t="n">
         <v>30000</v>
       </c>
-      <c r="Q40" s="6" t="n">
+      <c r="Q40" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Pierre and Marie Curie University - Paris 6</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>UNI-000040</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" t="n">
         <v>40000</v>
       </c>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="6" t="n"/>
-      <c r="L41" s="6" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Université Pierre-et-Marie-Curie (Paris VI)</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Elite university in France. World-renowned university.</t>
         </is>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" t="n">
         <v>1257</v>
       </c>
-      <c r="O41" s="6" t="n"/>
-      <c r="P41" s="6" t="n">
+      <c r="P41" t="n">
         <v>30000</v>
       </c>
-      <c r="Q41" s="6" t="n">
+      <c r="Q41" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>University of Paris-Sud (Paris 11)</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>UNI-000041</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Orsay</t>
         </is>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" t="n">
         <v>30000</v>
       </c>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Université Paris-Sud (Paris XI)</t>
         </is>
       </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Elite university in France</t>
         </is>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="N42" t="n">
         <v>2015</v>
       </c>
-      <c r="O42" s="6" t="n"/>
-      <c r="P42" s="6" t="n">
+      <c r="P42" t="n">
         <v>15000</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="Q42" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Heidelberg University</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>UNI-000042</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Heidelberg,Baden-Württemberg</t>
         </is>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" t="n">
         <v>30000</v>
       </c>
-      <c r="J43" s="6" t="n"/>
-      <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Ruprecht-Karls-Universität Heidelberg</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Germany.</t>
         </is>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="N43" t="n">
         <v>1386</v>
       </c>
-      <c r="O43" s="6" t="n"/>
-      <c r="P43" s="6" t="n">
+      <c r="P43" t="n">
         <v>20000</v>
       </c>
-      <c r="Q43" s="6" t="n">
+      <c r="Q43" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>University of Colorado at Boulder</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>UNI-000043</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Boulder,Colorado</t>
         </is>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" t="n">
         <v>35000</v>
       </c>
-      <c r="J44" s="6" t="n"/>
-      <c r="K44" s="6" t="n"/>
-      <c r="L44" s="6" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>University of Colorado Boulder</t>
         </is>
       </c>
-      <c r="M44" s="6" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Public Ivy League</t>
         </is>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="N44" t="n">
         <v>1876</v>
       </c>
-      <c r="O44" s="6" t="n"/>
-      <c r="P44" s="6" t="n">
+      <c r="P44" t="n">
         <v>30000</v>
       </c>
-      <c r="Q44" s="6" t="n">
+      <c r="Q44" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Karolinska Institute</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>UNI-000044</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Public Medical University</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Stockholm</t>
         </is>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" t="n">
         <v>3000</v>
       </c>
-      <c r="J45" s="6" t="n"/>
-      <c r="K45" s="6" t="n"/>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Karolinska Institutet</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="N45" t="n">
         <v>1810</v>
       </c>
-      <c r="O45" s="6" t="n"/>
-      <c r="P45" s="6" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (focuses primarily on graduate programs in medical and life sciences)</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="n">
+      <c r="Q45" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>University of California, Santa Barbara</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>UNI-000045</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Santa Barbara,California</t>
         </is>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" t="n">
         <v>25000</v>
       </c>
-      <c r="J46" s="6" t="n"/>
-      <c r="K46" s="6" t="n"/>
-      <c r="L46" s="6" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>University of California, Santa Barbara</t>
         </is>
       </c>
-      <c r="M46" s="6" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N46" s="6" t="n">
+      <c r="N46" t="n">
         <v>1909</v>
       </c>
-      <c r="O46" s="6" t="n"/>
-      <c r="P46" s="6" t="n">
+      <c r="P46" t="n">
         <v>20000</v>
       </c>
-      <c r="Q46" s="6" t="n">
+      <c r="Q46" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>King's College London</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>UNI-000046</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>London,England</t>
         </is>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" t="n">
         <v>30000</v>
       </c>
-      <c r="J47" s="6" t="n"/>
-      <c r="K47" s="6" t="n"/>
-      <c r="L47" s="6" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>King's College London</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>World-renowned university. Russell Group.</t>
         </is>
       </c>
-      <c r="N47" s="6" t="n">
+      <c r="N47" t="n">
         <v>1829</v>
       </c>
-      <c r="O47" s="6" t="n"/>
-      <c r="P47" s="6" t="n">
+      <c r="P47" t="n">
         <v>16000</v>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="Q47" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Utrecht University</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>UNI-000047</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Utrecht</t>
         </is>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" t="n">
         <v>30000</v>
       </c>
-      <c r="J48" s="6" t="n"/>
-      <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Universiteit Utrecht</t>
         </is>
       </c>
-      <c r="M48" s="6" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N48" s="6" t="n">
+      <c r="N48" t="n">
         <v>1636</v>
       </c>
-      <c r="O48" s="6" t="n"/>
-      <c r="P48" s="6" t="n">
+      <c r="P48" t="n">
         <v>20000</v>
       </c>
-      <c r="Q48" s="6" t="n">
+      <c r="Q48" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>The University of Texas Southwestern Medical Center at Dallas</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>UNI-000048</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Public Medical University</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Dallas,Texas</t>
         </is>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" t="n">
         <v>3700</v>
       </c>
-      <c r="J49" s="6" t="n"/>
-      <c r="K49" s="6" t="n"/>
-      <c r="L49" s="6" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>The University of Texas Southwestern Medical Center at Dallas</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Healthcare and Research</t>
         </is>
       </c>
-      <c r="N49" s="6" t="n">
+      <c r="N49" t="n">
         <v>1943</v>
       </c>
-      <c r="O49" s="6" t="n"/>
-      <c r="P49" s="6" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (medical institution)</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="n">
+      <c r="Q49" t="n">
         <v>3700</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Tsinghua University</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>UNI-000049</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" t="n">
         <v>50000</v>
       </c>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="M50" s="6" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>World prestigious university. C9 League.</t>
         </is>
       </c>
-      <c r="N50" s="6" t="n">
+      <c r="N50" t="n">
         <v>1911</v>
       </c>
-      <c r="O50" s="6" t="n"/>
-      <c r="P50" s="6" t="n">
+      <c r="P50" t="n">
         <v>20000</v>
       </c>
-      <c r="Q50" s="6" t="n">
+      <c r="Q50" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Technical University Munich</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>UNI-000050</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I51" t="n">
         <v>40000</v>
       </c>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Technische Universität München</t>
         </is>
       </c>
-      <c r="M51" s="6" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Germany.</t>
         </is>
       </c>
-      <c r="N51" s="6" t="n">
+      <c r="N51" t="n">
         <v>1827</v>
       </c>
-      <c r="O51" s="6" t="n"/>
-      <c r="P51" s="6" t="n">
+      <c r="P51" t="n">
         <v>20000</v>
       </c>
-      <c r="Q51" s="6" t="n">
+      <c r="Q51" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>The University of Texas at Austin</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>UNI-000051</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Austin,Texas</t>
         </is>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I52" t="n">
         <v>50000</v>
       </c>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>The University of Texas at Austin</t>
         </is>
       </c>
-      <c r="M52" s="6" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N52" s="6" t="n">
+      <c r="N52" t="n">
         <v>1883</v>
       </c>
-      <c r="O52" s="6" t="n"/>
-      <c r="P52" s="6" t="n">
+      <c r="P52" t="n">
         <v>40000</v>
       </c>
-      <c r="Q52" s="6" t="n">
+      <c r="Q52" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Vanderbilt University</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>UNI-000052</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Nashville,Tennessee</t>
         </is>
       </c>
-      <c r="I53" s="6" t="n">
+      <c r="I53" t="n">
         <v>13000</v>
       </c>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Vanderbilt University</t>
         </is>
       </c>
-      <c r="M53" s="6" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
+      <c r="N53" t="n">
         <v>1873</v>
       </c>
-      <c r="O53" s="6" t="n"/>
-      <c r="P53" s="6" t="n">
+      <c r="P53" t="n">
         <v>7000</v>
       </c>
-      <c r="Q53" s="6" t="n">
+      <c r="Q53" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>University of Maryland, College Park</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>UNI-000053</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>College Park,Maryland</t>
         </is>
       </c>
-      <c r="I54" s="6" t="n">
+      <c r="I54" t="n">
         <v>40000</v>
       </c>
-      <c r="J54" s="6" t="n"/>
-      <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>University of Maryland, College Park</t>
         </is>
       </c>
-      <c r="M54" s="6" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N54" s="6" t="n">
+      <c r="N54" t="n">
         <v>1856</v>
       </c>
-      <c r="O54" s="6" t="n"/>
-      <c r="P54" s="6" t="n">
+      <c r="P54" t="n">
         <v>30000</v>
       </c>
-      <c r="Q54" s="6" t="n">
+      <c r="Q54" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>University of Southern California</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>UNI-000054</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Los Angeles,California</t>
         </is>
       </c>
-      <c r="I55" s="6" t="n">
+      <c r="I55" t="n">
         <v>47000</v>
       </c>
-      <c r="J55" s="6" t="n"/>
-      <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>University of Southern California</t>
         </is>
       </c>
-      <c r="M55" s="6" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N55" s="6" t="n">
+      <c r="N55" t="n">
         <v>1880</v>
       </c>
-      <c r="O55" s="6" t="n"/>
-      <c r="P55" s="6" t="n">
+      <c r="P55" t="n">
         <v>19000</v>
       </c>
-      <c r="Q55" s="6" t="n">
+      <c r="Q55" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>The University of Queensland</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>UNI-000055</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Brisbane,Queensland</t>
         </is>
       </c>
-      <c r="I56" s="6" t="n">
+      <c r="I56" t="n">
         <v>55000</v>
       </c>
-      <c r="J56" s="6" t="n"/>
-      <c r="K56" s="6" t="n"/>
-      <c r="L56" s="6" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>The University of Queensland</t>
         </is>
       </c>
-      <c r="M56" s="6" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Group of Eight (Go8)</t>
         </is>
       </c>
-      <c r="N56" s="6" t="n">
+      <c r="N56" t="n">
         <v>1909</v>
       </c>
-      <c r="O56" s="6" t="n"/>
-      <c r="P56" s="6" t="n">
+      <c r="P56" t="n">
         <v>40000</v>
       </c>
-      <c r="Q56" s="6" t="n">
+      <c r="Q56" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>University of Helsinki</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>UNI-000056</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Helsinki</t>
         </is>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="I57" t="n">
         <v>35000</v>
       </c>
-      <c r="J57" s="6" t="n"/>
-      <c r="K57" s="6" t="n"/>
-      <c r="L57" s="6" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Helsingin yliopisto</t>
         </is>
       </c>
-      <c r="M57" s="6" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Humanities and Social Sciences</t>
         </is>
       </c>
-      <c r="N57" s="6" t="n">
+      <c r="N57" t="n">
         <v>1640</v>
       </c>
-      <c r="O57" s="6" t="n"/>
-      <c r="P57" s="6" t="n">
+      <c r="P57" t="n">
         <v>20000</v>
       </c>
-      <c r="Q57" s="6" t="n">
+      <c r="Q57" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>University of Munich</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>UNI-000057</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="I58" t="n">
         <v>50000</v>
       </c>
-      <c r="J58" s="6" t="n"/>
-      <c r="K58" s="6" t="n"/>
-      <c r="L58" s="6" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Ludwig-Maximilians-Universität München</t>
         </is>
       </c>
-      <c r="M58" s="6" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Germany.</t>
         </is>
       </c>
-      <c r="N58" s="6" t="n">
+      <c r="N58" t="n">
         <v>1472</v>
       </c>
-      <c r="O58" s="6" t="n"/>
-      <c r="P58" s="6" t="n">
+      <c r="P58" t="n">
         <v>30000</v>
       </c>
-      <c r="Q58" s="6" t="n">
+      <c r="Q58" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>University of Zurich</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>UNI-000058</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="I59" t="n">
         <v>26000</v>
       </c>
-      <c r="J59" s="6" t="n"/>
-      <c r="K59" s="6" t="n"/>
-      <c r="L59" s="6" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Universität Zürich</t>
         </is>
       </c>
-      <c r="M59" s="6" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N59" s="6" t="n">
+      <c r="N59" t="n">
         <v>1833</v>
       </c>
-      <c r="O59" s="6" t="n"/>
-      <c r="P59" s="6" t="n">
+      <c r="P59" t="n">
         <v>14000</v>
       </c>
-      <c r="Q59" s="6" t="n">
+      <c r="Q59" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>University of Groningen</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>UNI-000059</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Groningen</t>
         </is>
       </c>
-      <c r="I60" s="6" t="n">
+      <c r="I60" t="n">
         <v>30000</v>
       </c>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Rijksuniversiteit Groningen</t>
         </is>
       </c>
-      <c r="M60" s="6" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Known for Life Sciences, Arts and Social Sciences</t>
         </is>
       </c>
-      <c r="N60" s="6" t="n">
+      <c r="N60" t="n">
         <v>1614</v>
       </c>
-      <c r="O60" s="6" t="n"/>
-      <c r="P60" s="6" t="n">
+      <c r="P60" t="n">
         <v>18000</v>
       </c>
-      <c r="Q60" s="6" t="n">
+      <c r="Q60" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>University of Geneva</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>UNI-000060</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Geneva</t>
         </is>
       </c>
-      <c r="I61" s="6" t="n">
+      <c r="I61" t="n">
         <v>17000</v>
       </c>
-      <c r="J61" s="6" t="n"/>
-      <c r="K61" s="6" t="n"/>
-      <c r="L61" s="6" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Université de Genève</t>
         </is>
       </c>
-      <c r="M61" s="6" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Known for International Relations, Social Sciences and Law</t>
         </is>
       </c>
-      <c r="N61" s="6" t="n">
+      <c r="N61" t="n">
         <v>1559</v>
       </c>
-      <c r="O61" s="6" t="n"/>
-      <c r="P61" s="6" t="n">
+      <c r="P61" t="n">
         <v>9000</v>
       </c>
-      <c r="Q61" s="6" t="n">
+      <c r="Q61" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>University of Bristol</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>UNI-000061</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Bristol,England</t>
         </is>
       </c>
-      <c r="I62" s="6" t="n">
+      <c r="I62" t="n">
         <v>27000</v>
       </c>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="6" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>University of Bristol</t>
         </is>
       </c>
-      <c r="M62" s="6" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Russell Group</t>
         </is>
       </c>
-      <c r="N62" s="6" t="n">
+      <c r="N62" t="n">
         <v>1833</v>
       </c>
-      <c r="O62" s="6" t="n"/>
-      <c r="P62" s="6" t="n">
+      <c r="P62" t="n">
         <v>18000</v>
       </c>
-      <c r="Q62" s="6" t="n">
+      <c r="Q62" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>University of Oslo</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>UNI-000062</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Oslo</t>
         </is>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I63" t="n">
         <v>28000</v>
       </c>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="6" t="n"/>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Universitetet i Oslo</t>
         </is>
       </c>
-      <c r="M63" s="6" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Known for Humanities, Natural Sciences and Social Sciences</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
+      <c r="N63" t="n">
         <v>1811</v>
       </c>
-      <c r="O63" s="6" t="n"/>
-      <c r="P63" s="6" t="n">
+      <c r="P63" t="n">
         <v>20000</v>
       </c>
-      <c r="Q63" s="6" t="n">
+      <c r="Q63" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Uppsala University</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>UNI-000063</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Uppsala</t>
         </is>
       </c>
-      <c r="I64" s="6" t="n">
+      <c r="I64" t="n">
         <v>30000</v>
       </c>
-      <c r="J64" s="6" t="n"/>
-      <c r="K64" s="6" t="n"/>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Uppsala universitet</t>
         </is>
       </c>
-      <c r="M64" s="6" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Known for Humanities, Life Sciences and Social Sciences</t>
         </is>
       </c>
-      <c r="N64" s="6" t="n">
+      <c r="N64" t="n">
         <v>1477</v>
       </c>
-      <c r="O64" s="6" t="n"/>
-      <c r="P64" s="6" t="n">
+      <c r="P64" t="n">
         <v>20000</v>
       </c>
-      <c r="Q64" s="6" t="n">
+      <c r="Q64" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>University of California, Irvine</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>UNI-000064</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Irvine,California</t>
         </is>
       </c>
-      <c r="I65" s="6" t="n">
+      <c r="I65" t="n">
         <v>36000</v>
       </c>
-      <c r="J65" s="6" t="n"/>
-      <c r="K65" s="6" t="n"/>
-      <c r="L65" s="6" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>University of California, Irvine</t>
         </is>
       </c>
-      <c r="M65" s="6" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Public Ivy League</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
+      <c r="N65" t="n">
         <v>1965</v>
       </c>
-      <c r="O65" s="6" t="n"/>
-      <c r="P65" s="6" t="n">
+      <c r="P65" t="n">
         <v>30000</v>
       </c>
-      <c r="Q65" s="6" t="n">
+      <c r="Q65" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Aarhus University</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>UNI-000065</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="H66" s="6" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Aarhus</t>
         </is>
       </c>
-      <c r="I66" s="6" t="n">
+      <c r="I66" t="n">
         <v>40000</v>
       </c>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Aarhus Universitet</t>
         </is>
       </c>
-      <c r="M66" s="6" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Known for Humanities, Business and Natural Sciences</t>
         </is>
       </c>
-      <c r="N66" s="6" t="n">
+      <c r="N66" t="n">
         <v>1928</v>
       </c>
-      <c r="O66" s="6" t="n"/>
-      <c r="P66" s="6" t="n">
+      <c r="P66" t="n">
         <v>25000</v>
       </c>
-      <c r="Q66" s="6" t="n">
+      <c r="Q66" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>McMaster University</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>UNI-000066</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Hamilton,Ontario</t>
         </is>
       </c>
-      <c r="I67" s="6" t="n">
+      <c r="I67" t="n">
         <v>30000</v>
       </c>
-      <c r="J67" s="6" t="n"/>
-      <c r="K67" s="6" t="n"/>
-      <c r="L67" s="6" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>McMaster University</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>U15 Group</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
+      <c r="N67" t="n">
         <v>1887</v>
       </c>
-      <c r="O67" s="6" t="n"/>
-      <c r="P67" s="6" t="n">
+      <c r="P67" t="n">
         <v>20000</v>
       </c>
-      <c r="Q67" s="6" t="n">
+      <c r="Q67" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>McGill University</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>UNI-000067</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Montreal,Quebec</t>
         </is>
       </c>
-      <c r="I68" s="6" t="n">
+      <c r="I68" t="n">
         <v>40000</v>
       </c>
-      <c r="J68" s="6" t="n"/>
-      <c r="K68" s="6" t="n"/>
-      <c r="L68" s="6" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>Université McGill</t>
         </is>
       </c>
-      <c r="M68" s="6" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>World-renowned university. U15 Group.</t>
         </is>
       </c>
-      <c r="N68" s="6" t="n">
+      <c r="N68" t="n">
         <v>1821</v>
       </c>
-      <c r="O68" s="6" t="n"/>
-      <c r="P68" s="6" t="n">
+      <c r="P68" t="n">
         <v>30000</v>
       </c>
-      <c r="Q68" s="6" t="n">
+      <c r="Q68" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>University of Pittsburgh, Pittsburgh Campus</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>UNI-000068</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Pittsburgh,Pennsylvania</t>
         </is>
       </c>
-      <c r="I69" s="6" t="n">
+      <c r="I69" t="n">
         <v>28000</v>
       </c>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="6" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>University of Pittsburgh</t>
         </is>
       </c>
-      <c r="M69" s="6" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Public Ivy League</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
+      <c r="N69" t="n">
         <v>1787</v>
       </c>
-      <c r="O69" s="6" t="n"/>
-      <c r="P69" s="6" t="n">
+      <c r="P69" t="n">
         <v>19000</v>
       </c>
-      <c r="Q69" s="6" t="n">
+      <c r="Q69" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>École Normale Supérieure - Paris</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>UNI-000069</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I70" s="6" t="n">
+      <c r="I70" t="n">
         <v>1800</v>
       </c>
-      <c r="J70" s="6" t="n"/>
-      <c r="K70" s="6" t="n"/>
-      <c r="L70" s="6" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>École normale supérieure</t>
         </is>
       </c>
-      <c r="M70" s="6" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Elite university in France</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
+      <c r="N70" t="n">
         <v>1794</v>
       </c>
-      <c r="O70" s="6" t="n"/>
-      <c r="P70" s="6" t="n">
+      <c r="P70" t="n">
         <v>600</v>
       </c>
-      <c r="Q70" s="6" t="n">
+      <c r="Q70" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Ghent University</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>UNI-000070</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Ghent</t>
         </is>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="I71" t="n">
         <v>45000</v>
       </c>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="6" t="n"/>
-      <c r="L71" s="6" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>Universiteit Gent</t>
         </is>
       </c>
-      <c r="M71" s="6" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Engineering and Life Sciences</t>
         </is>
       </c>
-      <c r="N71" s="6" t="n">
+      <c r="N71" t="n">
         <v>1817</v>
       </c>
-      <c r="O71" s="6" t="n"/>
-      <c r="P71" s="6" t="n">
+      <c r="P71" t="n">
         <v>30000</v>
       </c>
-      <c r="Q71" s="6" t="n">
+      <c r="Q71" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Mayo Medical School</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>UNI-000071</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Private Medical School</t>
         </is>
       </c>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Rochester,Minnesota</t>
         </is>
       </c>
-      <c r="I72" s="6" t="n">
+      <c r="I72" t="n">
         <v>1000</v>
       </c>
-      <c r="J72" s="6" t="n"/>
-      <c r="K72" s="6" t="n"/>
-      <c r="L72" s="6" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>Mayo Medical School</t>
         </is>
       </c>
-      <c r="M72" s="6" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Known for Medical Education and Clinical Research</t>
         </is>
       </c>
-      <c r="N72" s="6" t="n">
+      <c r="N72" t="n">
         <v>1972</v>
       </c>
-      <c r="O72" s="6" t="n"/>
-      <c r="P72" s="6" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (graduate-only institution)</t>
         </is>
       </c>
-      <c r="Q72" s="6" t="n">
+      <c r="Q72" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Peking University</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>UNI-000072</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="I73" s="6" t="n">
+      <c r="I73" t="n">
         <v>45000</v>
       </c>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="6" t="n"/>
-      <c r="L73" s="6" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="M73" s="6" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>World prestigious university. C9 League.</t>
         </is>
       </c>
-      <c r="N73" s="6" t="n">
+      <c r="N73" t="n">
         <v>1898</v>
       </c>
-      <c r="O73" s="6" t="n"/>
-      <c r="P73" s="6" t="n">
+      <c r="P73" t="n">
         <v>20000</v>
       </c>
-      <c r="Q73" s="6" t="n">
+      <c r="Q73" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Erasmus University</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>UNI-000073</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Rotterdam</t>
         </is>
       </c>
-      <c r="I74" s="6" t="n">
+      <c r="I74" t="n">
         <v>28000</v>
       </c>
-      <c r="J74" s="6" t="n"/>
-      <c r="K74" s="6" t="n"/>
-      <c r="L74" s="6" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>Erasmus Universiteit Rotterdam</t>
         </is>
       </c>
-      <c r="M74" s="6" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Known for Social Sciences, Business and Medical Sciences</t>
         </is>
       </c>
-      <c r="N74" s="6" t="n">
+      <c r="N74" t="n">
         <v>1913</v>
       </c>
-      <c r="O74" s="6" t="n"/>
-      <c r="P74" s="6" t="n">
+      <c r="P74" t="n">
         <v>15000</v>
       </c>
-      <c r="Q74" s="6" t="n">
+      <c r="Q74" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Rice University</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>UNI-000074</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Houston,Texas</t>
         </is>
       </c>
-      <c r="I75" s="6" t="n">
+      <c r="I75" t="n">
         <v>7000</v>
       </c>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="6" t="n"/>
-      <c r="L75" s="6" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Rice University</t>
         </is>
       </c>
-      <c r="M75" s="6" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N75" s="6" t="n">
+      <c r="N75" t="n">
         <v>1912</v>
       </c>
-      <c r="O75" s="6" t="n"/>
-      <c r="P75" s="6" t="n">
+      <c r="P75" t="n">
         <v>4000</v>
       </c>
-      <c r="Q75" s="6" t="n">
+      <c r="Q75" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Stockholm University</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>UNI-000075</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Stockholm</t>
         </is>
       </c>
-      <c r="I76" s="6" t="n">
+      <c r="I76" t="n">
         <v>30000</v>
       </c>
-      <c r="J76" s="6" t="n"/>
-      <c r="K76" s="6" t="n"/>
-      <c r="L76" s="6" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Stockholms universitet</t>
         </is>
       </c>
-      <c r="M76" s="6" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Known for Humanities, Life Sciences and Social Sciences</t>
         </is>
       </c>
-      <c r="N76" s="6" t="n">
+      <c r="N76" t="n">
         <v>1878</v>
       </c>
-      <c r="O76" s="6" t="n"/>
-      <c r="P76" s="6" t="n">
+      <c r="P76" t="n">
         <v>20000</v>
       </c>
-      <c r="Q76" s="6" t="n">
+      <c r="Q76" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Swiss Federal Institute of Technology Lausanne</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>UNI-000076</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="I77" s="6" t="n">
+      <c r="I77" t="n">
         <v>12000</v>
       </c>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="6" t="n"/>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>École polytechnique fédérale de Lausanne (EPFL)</t>
         </is>
       </c>
-      <c r="M77" s="6" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N77" s="6" t="n">
+      <c r="N77" t="n">
         <v>1853</v>
       </c>
-      <c r="O77" s="6" t="n"/>
-      <c r="P77" s="6" t="n">
+      <c r="P77" t="n">
         <v>6000</v>
       </c>
-      <c r="Q77" s="6" t="n">
+      <c r="Q77" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Purdue University - West Lafayette</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>UNI-000077</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>West Lafayette,Indiana</t>
         </is>
       </c>
-      <c r="I78" s="6" t="n">
+      <c r="I78" t="n">
         <v>45000</v>
       </c>
-      <c r="J78" s="6" t="n"/>
-      <c r="K78" s="6" t="n"/>
-      <c r="L78" s="6" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>Purdue University</t>
         </is>
       </c>
-      <c r="M78" s="6" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N78" s="6" t="n">
+      <c r="N78" t="n">
         <v>1869</v>
       </c>
-      <c r="O78" s="6" t="n"/>
-      <c r="P78" s="6" t="n">
+      <c r="P78" t="n">
         <v>30000</v>
       </c>
-      <c r="Q78" s="6" t="n">
+      <c r="Q78" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Monash University</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>UNI-000078</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="6" t="n"/>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Melbourne,Victoria</t>
         </is>
       </c>
-      <c r="I79" s="6" t="n">
+      <c r="I79" t="n">
         <v>80000</v>
       </c>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="6" t="n"/>
-      <c r="L79" s="6" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>Monash University</t>
         </is>
       </c>
-      <c r="M79" s="6" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Group of Eight (Go8)</t>
         </is>
       </c>
-      <c r="N79" s="6" t="n">
+      <c r="N79" t="n">
         <v>1958</v>
       </c>
-      <c r="O79" s="6" t="n"/>
-      <c r="P79" s="6" t="n">
+      <c r="P79" t="n">
         <v>55000</v>
       </c>
-      <c r="Q79" s="6" t="n">
+      <c r="Q79" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Rutgers, The State University of New Jersey - New Brunswick</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>UNI-000079</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>New Brunswick,New Jersey</t>
         </is>
       </c>
-      <c r="I80" s="6" t="n">
+      <c r="I80" t="n">
         <v>50000</v>
       </c>
-      <c r="J80" s="6" t="n"/>
-      <c r="K80" s="6" t="n"/>
-      <c r="L80" s="6" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>Rutgers, The State University of New Jersey–New Brunswick</t>
         </is>
       </c>
-      <c r="M80" s="6" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Public Ivy League
 </t>
         </is>
       </c>
-      <c r="N80" s="6" t="n">
+      <c r="N80" t="n">
         <v>1766</v>
       </c>
-      <c r="O80" s="6" t="n"/>
-      <c r="P80" s="6" t="n">
+      <c r="P80" t="n">
         <v>35000</v>
       </c>
-      <c r="Q80" s="6" t="n">
+      <c r="Q80" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Boston University</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>UNI-000080</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D81" s="6" t="n"/>
-      <c r="E81" s="6" t="n"/>
-      <c r="F81" s="6" t="n"/>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Boston,Massachusetts</t>
         </is>
       </c>
-      <c r="I81" s="6" t="n">
+      <c r="I81" t="n">
         <v>35000</v>
       </c>
-      <c r="J81" s="6" t="n"/>
-      <c r="K81" s="6" t="n"/>
-      <c r="L81" s="6" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>Boston University</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N81" s="6" t="n">
+      <c r="N81" t="n">
         <v>1839</v>
       </c>
-      <c r="O81" s="6" t="n"/>
-      <c r="P81" s="6" t="n">
+      <c r="P81" t="n">
         <v>16000</v>
       </c>
-      <c r="Q81" s="6" t="n">
+      <c r="Q81" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Carnegie Mellon University</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>UNI-000081</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="D82" s="6" t="n"/>
-      <c r="E82" s="6" t="n"/>
-      <c r="F82" s="6" t="n"/>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Pittsburgh,Pennsylvania</t>
         </is>
       </c>
-      <c r="I82" s="6" t="n">
+      <c r="I82" t="n">
         <v>14000</v>
       </c>
-      <c r="J82" s="6" t="n"/>
-      <c r="K82" s="6" t="n"/>
-      <c r="L82" s="6" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>Carnegie Mellon University</t>
         </is>
       </c>
-      <c r="M82" s="6" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective.</t>
         </is>
       </c>
-      <c r="N82" s="6" t="n">
+      <c r="N82" t="n">
         <v>1900</v>
       </c>
-      <c r="O82" s="6" t="n"/>
-      <c r="P82" s="6" t="n">
+      <c r="P82" t="n">
         <v>7000</v>
       </c>
-      <c r="Q82" s="6" t="n">
+      <c r="Q82" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>The Ohio State University - Columbus</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>UNI-000082</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="n"/>
-      <c r="E83" s="6" t="n"/>
-      <c r="F83" s="6" t="n"/>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Columbus,Ohio</t>
         </is>
       </c>
-      <c r="I83" s="6" t="n">
+      <c r="I83" t="n">
         <v>61000</v>
       </c>
-      <c r="J83" s="6" t="n"/>
-      <c r="K83" s="6" t="n"/>
-      <c r="L83" s="6" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>The Ohio State University</t>
         </is>
       </c>
-      <c r="M83" s="6" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N83" s="6" t="n">
+      <c r="N83" t="n">
         <v>1870</v>
       </c>
-      <c r="O83" s="6" t="n"/>
-      <c r="P83" s="6" t="n">
+      <c r="P83" t="n">
         <v>47000</v>
       </c>
-      <c r="Q83" s="6" t="n">
+      <c r="Q83" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>University of Sydney</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>UNI-000083</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="F84" s="6" t="n"/>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Sydney,New South Wales</t>
         </is>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="I84" t="n">
         <v>45000</v>
       </c>
-      <c r="J84" s="6" t="n"/>
-      <c r="K84" s="6" t="n"/>
-      <c r="L84" s="6" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>The University of Sydney</t>
         </is>
       </c>
-      <c r="M84" s="6" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>World-renowned university. Group of Eight (Go8).</t>
         </is>
       </c>
-      <c r="N84" s="6" t="n">
+      <c r="N84" t="n">
         <v>1850</v>
       </c>
-      <c r="O84" s="6" t="n"/>
-      <c r="P84" s="6" t="n">
+      <c r="P84" t="n">
         <v>30000</v>
       </c>
-      <c r="Q84" s="6" t="n">
+      <c r="Q84" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Nagoya University</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>UNI-000084</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Nagoya,Aichi</t>
         </is>
       </c>
-      <c r="I85" s="6" t="n">
+      <c r="I85" t="n">
         <v>20000</v>
       </c>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="6" t="n"/>
-      <c r="L85" s="6" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>名古屋大学</t>
         </is>
       </c>
-      <c r="M85" s="6" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>World-renowned university. Imperial university.</t>
         </is>
       </c>
-      <c r="N85" s="6" t="n">
+      <c r="N85" t="n">
         <v>1871</v>
       </c>
-      <c r="O85" s="6" t="n"/>
-      <c r="P85" s="6" t="n">
+      <c r="P85" t="n">
         <v>12000</v>
       </c>
-      <c r="Q85" s="6" t="n">
+      <c r="Q85" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Georgia Institute of Technology</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>UNI-000085</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Atlanta,Georgia</t>
         </is>
       </c>
-      <c r="I86" s="6" t="n">
+      <c r="I86" t="n">
         <v>30000</v>
       </c>
-      <c r="J86" s="6" t="n"/>
-      <c r="K86" s="6" t="n"/>
-      <c r="L86" s="6" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>Georgia Institute of Technology</t>
         </is>
       </c>
-      <c r="M86" s="6" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N86" s="6" t="n">
+      <c r="N86" t="n">
         <v>1885</v>
       </c>
-      <c r="O86" s="6" t="n"/>
-      <c r="P86" s="6" t="n">
+      <c r="P86" t="n">
         <v>15000</v>
       </c>
-      <c r="Q86" s="6" t="n">
+      <c r="Q86" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Pennsylvania State University - University Park</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>UNI-000086</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>University Park,Pennsylvania</t>
         </is>
       </c>
-      <c r="I87" s="6" t="n">
+      <c r="I87" t="n">
         <v>46000</v>
       </c>
-      <c r="J87" s="6" t="n"/>
-      <c r="K87" s="6" t="n"/>
-      <c r="L87" s="6" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>The Pennsylvania State University</t>
         </is>
       </c>
-      <c r="M87" s="6" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N87" s="6" t="n">
+      <c r="N87" t="n">
         <v>1855</v>
       </c>
-      <c r="O87" s="6" t="n"/>
-      <c r="P87" s="6" t="n">
+      <c r="P87" t="n">
         <v>40000</v>
       </c>
-      <c r="Q87" s="6" t="n">
+      <c r="Q87" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>University of California, Davis</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>UNI-000087</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="n"/>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="6" t="n"/>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Davis,California</t>
         </is>
       </c>
-      <c r="I88" s="6" t="n">
+      <c r="I88" t="n">
         <v>39000</v>
       </c>
-      <c r="J88" s="6" t="n"/>
-      <c r="K88" s="6" t="n"/>
-      <c r="L88" s="6" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>University of California, Davis</t>
         </is>
       </c>
-      <c r="M88" s="6" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N88" s="6" t="n">
+      <c r="N88" t="n">
         <v>1905</v>
       </c>
-      <c r="O88" s="6" t="n"/>
-      <c r="P88" s="6" t="n">
+      <c r="P88" t="n">
         <v>30000</v>
       </c>
-      <c r="Q88" s="6" t="n">
+      <c r="Q88" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Leiden University</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>UNI-000088</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Leiden</t>
         </is>
       </c>
-      <c r="I89" s="6" t="n">
+      <c r="I89" t="n">
         <v>30000</v>
       </c>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="6" t="n"/>
-      <c r="L89" s="6" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>Universiteit Leiden</t>
         </is>
       </c>
-      <c r="M89" s="6" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N89" s="6" t="n">
+      <c r="N89" t="n">
         <v>1575</v>
       </c>
-      <c r="O89" s="6" t="n"/>
-      <c r="P89" s="6" t="n">
+      <c r="P89" t="n">
         <v>20000</v>
       </c>
-      <c r="Q89" s="6" t="n">
+      <c r="Q89" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>University of Florida</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>UNI-000089</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Gainesville,Florida</t>
         </is>
       </c>
-      <c r="I90" s="6" t="n">
+      <c r="I90" t="n">
         <v>55000</v>
       </c>
-      <c r="J90" s="6" t="n"/>
-      <c r="K90" s="6" t="n"/>
-      <c r="L90" s="6" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>University of Florida</t>
         </is>
       </c>
-      <c r="M90" s="6" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N90" s="6" t="n">
+      <c r="N90" t="n">
         <v>1853</v>
       </c>
-      <c r="O90" s="6" t="n"/>
-      <c r="P90" s="6" t="n">
+      <c r="P90" t="n">
         <v>35000</v>
       </c>
-      <c r="Q90" s="6" t="n">
+      <c r="Q90" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>KU Leuven</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>UNI-000090</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="n"/>
-      <c r="E91" s="6" t="n"/>
-      <c r="F91" s="6" t="n"/>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Leuven</t>
         </is>
       </c>
-      <c r="I91" s="6" t="n">
+      <c r="I91" t="n">
         <v>60000</v>
       </c>
-      <c r="J91" s="6" t="n"/>
-      <c r="K91" s="6" t="n"/>
-      <c r="L91" s="6" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>Katholieke Universiteit Leuven</t>
         </is>
       </c>
-      <c r="M91" s="6" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N91" s="6" t="n">
+      <c r="N91" t="n">
         <v>1425</v>
       </c>
-      <c r="O91" s="6" t="n"/>
-      <c r="P91" s="6" t="n">
+      <c r="P91" t="n">
         <v>40000</v>
       </c>
-      <c r="Q91" s="6" t="n">
+      <c r="Q91" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>National University of Singapore</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>UNI-000091</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="I92" s="6" t="n">
+      <c r="I92" t="n">
         <v>40000</v>
       </c>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="6" t="n"/>
-      <c r="L92" s="6" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>National University of Singapore</t>
         </is>
       </c>
-      <c r="M92" s="6" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N92" s="6" t="n">
+      <c r="N92" t="n">
         <v>1905</v>
       </c>
-      <c r="O92" s="6" t="n"/>
-      <c r="P92" s="6" t="n">
+      <c r="P92" t="n">
         <v>28000</v>
       </c>
-      <c r="Q92" s="6" t="n">
+      <c r="Q92" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>The University of Western Australia</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>UNI-000092</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="n"/>
-      <c r="E93" s="6" t="n"/>
-      <c r="F93" s="6" t="n"/>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Perth,Western Australia</t>
         </is>
       </c>
-      <c r="I93" s="6" t="n">
+      <c r="I93" t="n">
         <v>25000</v>
       </c>
-      <c r="J93" s="6" t="n"/>
-      <c r="K93" s="6" t="n"/>
-      <c r="L93" s="6" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>The University of Western Australia</t>
         </is>
       </c>
-      <c r="M93" s="6" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>Group of Eight (Go8)</t>
         </is>
       </c>
-      <c r="N93" s="6" t="n">
+      <c r="N93" t="n">
         <v>1911</v>
       </c>
-      <c r="O93" s="6" t="n"/>
-      <c r="P93" s="6" t="n">
+      <c r="P93" t="n">
         <v>18000</v>
       </c>
-      <c r="Q93" s="6" t="n">
+      <c r="Q93" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Moscow State University</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>UNI-000093</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="6" t="n"/>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Moscow</t>
         </is>
       </c>
-      <c r="I94" s="6" t="n">
+      <c r="I94" t="n">
         <v>40000</v>
       </c>
-      <c r="J94" s="6" t="n"/>
-      <c r="K94" s="6" t="n"/>
-      <c r="L94" s="6" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>Московский государственный университет имени М. В. Ломоносова</t>
         </is>
       </c>
-      <c r="M94" s="6" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Russia.</t>
         </is>
       </c>
-      <c r="N94" s="6" t="n">
+      <c r="N94" t="n">
         <v>1755</v>
       </c>
-      <c r="O94" s="6" t="n"/>
-      <c r="P94" s="6" t="n">
+      <c r="P94" t="n">
         <v>25000</v>
       </c>
-      <c r="Q94" s="6" t="n">
+      <c r="Q94" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>University of Basel</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>UNI-000094</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="6" t="n"/>
-      <c r="F95" s="6" t="n"/>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Basel</t>
         </is>
       </c>
-      <c r="I95" s="6" t="n">
+      <c r="I95" t="n">
         <v>13000</v>
       </c>
-      <c r="J95" s="6" t="n"/>
-      <c r="K95" s="6" t="n"/>
-      <c r="L95" s="6" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>Universität Basel</t>
         </is>
       </c>
-      <c r="M95" s="6" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Life Sciences and Humanities</t>
         </is>
       </c>
-      <c r="N95" s="6" t="n">
+      <c r="N95" t="n">
         <v>1460</v>
       </c>
-      <c r="O95" s="6" t="n"/>
-      <c r="P95" s="6" t="n">
+      <c r="P95" t="n">
         <v>7000</v>
       </c>
-      <c r="Q95" s="6" t="n">
+      <c r="Q95" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>University of Göttingen</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>UNI-000095</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n"/>
-      <c r="F96" s="6" t="n"/>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Göttingen</t>
         </is>
       </c>
-      <c r="I96" s="6" t="n">
+      <c r="I96" t="n">
         <v>30000</v>
       </c>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="6" t="n"/>
-      <c r="L96" s="6" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>Georg-August-Universität Göttingen</t>
         </is>
       </c>
-      <c r="M96" s="6" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>Elite university in Germany</t>
         </is>
       </c>
-      <c r="N96" s="6" t="n">
+      <c r="N96" t="n">
         <v>1737</v>
       </c>
-      <c r="O96" s="6" t="n"/>
-      <c r="P96" s="6" t="n">
+      <c r="P96" t="n">
         <v>20000</v>
       </c>
-      <c r="Q96" s="6" t="n">
+      <c r="Q96" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>The Australian National University</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>UNI-000096</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Canberra</t>
         </is>
       </c>
-      <c r="I97" s="6" t="n">
+      <c r="I97" t="n">
         <v>20000</v>
       </c>
-      <c r="J97" s="6" t="n"/>
-      <c r="K97" s="6" t="n"/>
-      <c r="L97" s="6" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>The Australian National University</t>
         </is>
       </c>
-      <c r="M97" s="6" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>World-renowned university. Group of Eight (Go8).</t>
         </is>
       </c>
-      <c r="N97" s="6" t="n">
+      <c r="N97" t="n">
         <v>1946</v>
       </c>
-      <c r="O97" s="6" t="n"/>
-      <c r="P97" s="6" t="n">
+      <c r="P97" t="n">
         <v>10000</v>
       </c>
-      <c r="Q97" s="6" t="n">
+      <c r="Q97" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>University of California, Santa Cruz</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>UNI-000097</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="6" t="n"/>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H98" s="6" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Santa Cruz,California</t>
         </is>
       </c>
-      <c r="I98" s="6" t="n">
+      <c r="I98" t="n">
         <v>20000</v>
       </c>
-      <c r="J98" s="6" t="n"/>
-      <c r="K98" s="6" t="n"/>
-      <c r="L98" s="6" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>University of California, Santa Cruz</t>
         </is>
       </c>
-      <c r="M98" s="6" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Known for Social Sciences, Natural Sciences and Arts</t>
         </is>
       </c>
-      <c r="N98" s="6" t="n">
+      <c r="N98" t="n">
         <v>1962</v>
       </c>
-      <c r="O98" s="6" t="n"/>
-      <c r="P98" s="6" t="n">
+      <c r="P98" t="n">
         <v>18000</v>
       </c>
-      <c r="Q98" s="6" t="n">
+      <c r="Q98" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Cardiff University</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>UNI-000098</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Cardiff,Wales</t>
         </is>
       </c>
-      <c r="I99" s="6" t="n">
+      <c r="I99" t="n">
         <v>30000</v>
       </c>
-      <c r="J99" s="6" t="n"/>
-      <c r="K99" s="6" t="n"/>
-      <c r="L99" s="6" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>Prifysgol Caerdydd</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>Russell Group</t>
         </is>
       </c>
-      <c r="N99" s="6" t="n">
+      <c r="N99" t="n">
         <v>1883</v>
       </c>
-      <c r="O99" s="6" t="n"/>
-      <c r="P99" s="6" t="n">
+      <c r="P99" t="n">
         <v>20000</v>
       </c>
-      <c r="Q99" s="6" t="n">
+      <c r="Q99" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>University of Arizona</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>UNI-000099</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Tucson,Arizona</t>
         </is>
       </c>
-      <c r="I100" s="6" t="n">
+      <c r="I100" t="n">
         <v>45000</v>
       </c>
-      <c r="J100" s="6" t="n"/>
-      <c r="K100" s="6" t="n"/>
-      <c r="L100" s="6" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>University of Arizona</t>
         </is>
       </c>
-      <c r="M100" s="6" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N100" s="6" t="n">
+      <c r="N100" t="n">
         <v>1885</v>
       </c>
-      <c r="O100" s="6" t="n"/>
-      <c r="P100" s="6" t="n">
+      <c r="P100" t="n">
         <v>34000</v>
       </c>
-      <c r="Q100" s="6" t="n">
+      <c r="Q100" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>King Saud University</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>UNI-000100</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="n"/>
-      <c r="E101" s="6" t="n"/>
-      <c r="F101" s="6" t="n"/>
-      <c r="G101" s="6" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="H101" s="6" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Riyadh</t>
         </is>
       </c>
-      <c r="I101" s="6" t="n">
+      <c r="I101" t="n">
         <v>61000</v>
       </c>
-      <c r="J101" s="6" t="n"/>
-      <c r="K101" s="6" t="n"/>
-      <c r="L101" s="6" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>جامعة الملك سعود</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>Leading public university in Saudi Arabia. Flagship institution with strong research programs and broad academic offerings.</t>
         </is>
       </c>
-      <c r="N101" s="6" t="n">
+      <c r="N101" t="n">
         <v>1957</v>
       </c>
-      <c r="O101" s="6" t="n"/>
-      <c r="P101" s="6" t="n">
+      <c r="P101" t="n">
         <v>38000</v>
       </c>
-      <c r="Q101" s="6" t="n">
+      <c r="Q101" t="n">
         <v>23000</v>
       </c>
     </row>

--- a/apps/api/data/excel_templates/universities.xlsx
+++ b/apps/api/data/excel_templates/universities.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -70,6 +70,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -545,4913 +548,5513 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>UNI-000001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Cambridge,Massachusetts</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="6" t="n">
         <v>1636</v>
       </c>
-      <c r="P2" t="n">
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="6" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>UNI-000002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Stanford,California</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="6" t="n">
         <v>1885</v>
       </c>
-      <c r="P3" t="n">
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="6" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>University of Cambridge</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>UNI-000003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Cambridge,England</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>24000</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>University of Cambridge</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="6" t="n">
         <v>1209</v>
       </c>
-      <c r="P4" t="n">
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="6" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Massachusetts Institute of Technology (MIT)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>UNI-000004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Cambridge,Massachusetts</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="6" t="n">
         <v>11500</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Massachusetts Institute of Technology (MIT)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective.</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="6" t="n">
         <v>1861</v>
       </c>
-      <c r="P5" t="n">
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n">
         <v>4500</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="6" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>University of California, Berkeley</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>UNI-000005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Berkeley,California</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="6" t="n">
         <v>42000</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>University of California, Berkeley</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Public Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="6" t="n">
         <v>1868</v>
       </c>
-      <c r="P6" t="n">
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n">
         <v>31000</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>UNI-000006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Princeton,New Jersey</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="6" t="n">
         <v>1746</v>
       </c>
-      <c r="P7" t="n">
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n">
         <v>5300</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="6" t="n">
         <v>2700</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>University of Oxford</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>UNI-000007</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Oxford,England</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="6" t="n">
         <v>24000</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>University of Oxford</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="6" t="n">
         <v>1096</v>
       </c>
-      <c r="P8" t="n">
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="6" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Columbia University</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>UNI-000008</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>New York City,New York</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="6" t="n">
         <v>31000</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>Columbia University</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="6" t="n">
         <v>1754</v>
       </c>
-      <c r="P9" t="n">
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n">
         <v>8200</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="6" t="n">
         <v>22800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>California Institute of Technology</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>UNI-000009</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Pasadena,California</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="6" t="n">
         <v>2200</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>California Institute of Technology</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective.</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="6" t="n">
         <v>1891</v>
       </c>
-      <c r="P10" t="n">
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="6" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>University of Chicago</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>UNI-000010</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Chicago,Illinois</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="6" t="n">
         <v>17000</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>University of Chicago</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="6" t="n">
         <v>1890</v>
       </c>
-      <c r="P11" t="n">
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n">
         <v>6800</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="6" t="n">
         <v>10200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>UNI-000011</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>New Haven,Connecticut</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="6" t="n">
         <v>13000</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="6" t="n">
         <v>1701</v>
       </c>
-      <c r="P12" t="n">
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n">
         <v>6100</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="6" t="n">
         <v>6900</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>University of California, Los Angeles</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>UNI-000012</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Los Angeles,California</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>University of California, Los Angeles</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Public Ivy League.</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="6" t="n">
         <v>1919</v>
       </c>
-      <c r="P13" t="n">
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n">
         <v>31000</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="6" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>University of Washington</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>UNI-000013</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Seattle,Washington</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="6" t="n">
         <v>54000</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>University of Washington</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="6" t="n">
         <v>1861</v>
       </c>
-      <c r="P14" t="n">
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n">
         <v>32000</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="6" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Cornell University</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>UNI-000014</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Ithaca,New York</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="6" t="n">
         <v>23000</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>Cornell University</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="6" t="n">
         <v>1865</v>
       </c>
-      <c r="P15" t="n">
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="6" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>University of California, San Diego</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>UNI-000015</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>San Diego,California</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>University of California, San Diego</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="6" t="n">
         <v>1903</v>
       </c>
-      <c r="P16" t="n">
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>University College London</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>UNI-000016</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>London,England</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>University College London</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="6" t="n">
         <v>1826</v>
       </c>
-      <c r="P17" t="n">
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="6" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>University of Pennsylvania</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>UNI-000017</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Philadelphia,Pennsylvania</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>University of Pennsylvania</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="6" t="n">
         <v>1740</v>
       </c>
-      <c r="P18" t="n">
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Johns Hopkins University</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>UNI-000018</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Baltimore,Maryland</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="6" t="n">
         <v>24000</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>Johns Hopkins University</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="6" t="n">
         <v>1876</v>
       </c>
-      <c r="P19" t="n">
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="6" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Swiss Federal Institute of Technology Zurich</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>UNI-000019</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>Eidgenössische Technische Hochschule Zürich</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>World prestigious university</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="6" t="n">
         <v>1855</v>
       </c>
-      <c r="P20" t="n">
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Washington University in St. Louis</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>UNI-000020</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>St. Louis,Missouri</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="inlineStr">
         <is>
           <t>Washington University in St. Louis</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="6" t="n">
         <v>1853</v>
       </c>
-      <c r="P21" t="n">
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="6" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>University of California, San Francisco</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>UNI-000021</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>San Francisco,California</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>University of California, San Francisco</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="6" t="n">
         <v>1864</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (UCSF does not offer undergraduate programs)</t>
         </is>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="6" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>UNI-000022</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Evanston,Illinois</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="6" t="n">
         <v>21000</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="6" t="n">
         <v>1851</v>
       </c>
-      <c r="P23" t="n">
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="6" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>University of Toronto</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>UNI-000023</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Toronto,Ontario</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="6" t="n">
         <v>90000</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>University of Toronto</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. U15 Group.</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="6" t="n">
         <v>1827</v>
       </c>
-      <c r="P24" t="n">
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" s="6" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>The University of Tokyo</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>UNI-000024</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>東京大学</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Imperial university.</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="6" t="n">
         <v>1877</v>
       </c>
-      <c r="P25" t="n">
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>University of Michigan-Ann Arbor</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>UNI-000025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Ann Arbor,Michigan</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="6" t="n">
         <v>48000</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>University of Michigan-Ann Arbor</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Public Ivy League.</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="6" t="n">
         <v>1817</v>
       </c>
-      <c r="P26" t="n">
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26" s="6" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Duke University</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>UNI-000026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Durham,North Carolina</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>Duke University</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="6" t="n">
         <v>1838</v>
       </c>
-      <c r="P27" t="n">
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n">
         <v>6500</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27" s="6" t="n">
         <v>8500</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Imperial College London</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>UNI-000027</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>London,England</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>Imperial College London</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. Russell Group.</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="6" t="n">
         <v>1907</v>
       </c>
-      <c r="P28" t="n">
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="6" t="n">
         <v>9000</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" s="6" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>University of Wisconsin - Madison</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>UNI-000028</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Madison,Wisconsin</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="inlineStr">
         <is>
           <t>University of Wisconsin - Madison</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="6" t="n">
         <v>1848</v>
       </c>
-      <c r="P29" t="n">
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>New York University</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>UNI-000029</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>New York City,New York</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>New York University</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective.</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="6" t="n">
         <v>1831</v>
       </c>
-      <c r="P30" t="n">
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="6" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>University of Copenhagen</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>UNI-000030</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Copenhagen</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="6" t="n">
         <v>38000</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Københavns Universitet</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="6" t="n">
         <v>1479</v>
       </c>
-      <c r="P31" t="n">
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="6" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>University of British Columbia</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>UNI-000031</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Vancouver,British Columbia</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>University of British Columbia</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. U15 Group.</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="6" t="n">
         <v>1908</v>
       </c>
-      <c r="P32" t="n">
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>The University of Edinburgh</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>UNI-000032</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Edinburgh,Scotland</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>The University of Edinburgh</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Russell Group.</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="6" t="n">
         <v>1582</v>
       </c>
-      <c r="P33" t="n">
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>UNI-000033</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>Chapel Hill,North Carolina</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="6" t="n">
         <v>1789</v>
       </c>
-      <c r="P34" t="n">
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>UNI-000034</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Minneapolis,Minnesota</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="6" t="n">
         <v>1851</v>
       </c>
-      <c r="P35" t="n">
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="n">
         <v>33000</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35" s="6" t="n">
         <v>17000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Kyoto University</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>UNI-000035</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Kyoto</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="6" t="n">
         <v>23000</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>京都大学</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Imperial university.</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="6" t="n">
         <v>1897</v>
       </c>
-      <c r="P36" t="n">
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36" s="6" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Rockefeller University</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>UNI-000036</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>New York City,New York</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>Rockefeller University</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="6" t="inlineStr">
         <is>
           <t>Focused on Biomedical Sciences</t>
         </is>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="6" t="n">
         <v>1901</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (Rockefeller is a graduate-only institution)</t>
         </is>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" s="6" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>University of Illinois at Urbana-Champaign</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>UNI-000037</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Urbana and Champaign,Illinois</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>University of Illinois at Urbana-Champaign</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="6" t="n">
         <v>1867</v>
       </c>
-      <c r="P38" t="n">
+      <c r="O38" s="6" t="n"/>
+      <c r="P38" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>The University of Manchester</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>UNI-000038</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Manchester,England</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>The University of Manchester</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Russell Group.</t>
         </is>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="6" t="n">
         <v>1824</v>
       </c>
-      <c r="P39" t="n">
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>The University of Melbourne</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>UNI-000039</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Melbourne,Victoria</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>The University of Melbourne</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Group of Eight (Go8).</t>
         </is>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" s="6" t="n">
         <v>1853</v>
       </c>
-      <c r="P40" t="n">
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Pierre and Marie Curie University - Paris 6</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>UNI-000040</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>Université Pierre-et-Marie-Curie (Paris VI)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>Elite university in France. World-renowned university.</t>
         </is>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" s="6" t="n">
         <v>1257</v>
       </c>
-      <c r="P41" t="n">
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>University of Paris-Sud (Paris 11)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>UNI-000041</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Orsay</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>Université Paris-Sud (Paris XI)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>Elite university in France</t>
         </is>
       </c>
-      <c r="N42" t="n">
+      <c r="N42" s="6" t="n">
         <v>2015</v>
       </c>
-      <c r="P42" t="n">
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Heidelberg University</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>UNI-000042</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Heidelberg,Baden-Württemberg</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>Ruprecht-Karls-Universität Heidelberg</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Germany.</t>
         </is>
       </c>
-      <c r="N43" t="n">
+      <c r="N43" s="6" t="n">
         <v>1386</v>
       </c>
-      <c r="P43" t="n">
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>University of Colorado at Boulder</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>UNI-000043</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Boulder,Colorado</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>University of Colorado Boulder</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M44" s="6" t="inlineStr">
         <is>
           <t>Public Ivy League</t>
         </is>
       </c>
-      <c r="N44" t="n">
+      <c r="N44" s="6" t="n">
         <v>1876</v>
       </c>
-      <c r="P44" t="n">
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44" s="6" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Karolinska Institute</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>UNI-000044</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Public Medical University</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>Stockholm</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>Karolinska Institutet</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N45" t="n">
+      <c r="N45" s="6" t="n">
         <v>1810</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (focuses primarily on graduate programs in medical and life sciences)</t>
         </is>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45" s="6" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>University of California, Santa Barbara</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>UNI-000045</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>Santa Barbara,California</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>University of California, Santa Barbara</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N46" t="n">
+      <c r="N46" s="6" t="n">
         <v>1909</v>
       </c>
-      <c r="P46" t="n">
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q46" s="6" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>King's College London</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>UNI-000046</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>London,England</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>King's College London</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Russell Group.</t>
         </is>
       </c>
-      <c r="N47" t="n">
+      <c r="N47" s="6" t="n">
         <v>1829</v>
       </c>
-      <c r="P47" t="n">
+      <c r="O47" s="6" t="n"/>
+      <c r="P47" s="6" t="n">
         <v>16000</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q47" s="6" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Utrecht University</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>UNI-000047</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>Utrecht</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="inlineStr">
         <is>
           <t>Universiteit Utrecht</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N48" t="n">
+      <c r="N48" s="6" t="n">
         <v>1636</v>
       </c>
-      <c r="P48" t="n">
+      <c r="O48" s="6" t="n"/>
+      <c r="P48" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q48" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>The University of Texas Southwestern Medical Center at Dallas</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>UNI-000048</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Public Medical University</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>Dallas,Texas</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="6" t="n">
         <v>3700</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="inlineStr">
         <is>
           <t>The University of Texas Southwestern Medical Center at Dallas</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Healthcare and Research</t>
         </is>
       </c>
-      <c r="N49" t="n">
+      <c r="N49" s="6" t="n">
         <v>1943</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="O49" s="6" t="n"/>
+      <c r="P49" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (medical institution)</t>
         </is>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q49" s="6" t="n">
         <v>3700</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Tsinghua University</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>UNI-000049</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="I50" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. C9 League.</t>
         </is>
       </c>
-      <c r="N50" t="n">
+      <c r="N50" s="6" t="n">
         <v>1911</v>
       </c>
-      <c r="P50" t="n">
+      <c r="O50" s="6" t="n"/>
+      <c r="P50" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q50" s="6" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Technical University Munich</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>UNI-000050</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="inlineStr">
         <is>
           <t>Technische Universität München</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Germany.</t>
         </is>
       </c>
-      <c r="N51" t="n">
+      <c r="N51" s="6" t="n">
         <v>1827</v>
       </c>
-      <c r="P51" t="n">
+      <c r="O51" s="6" t="n"/>
+      <c r="P51" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>The University of Texas at Austin</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>UNI-000051</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Austin,Texas</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="inlineStr">
         <is>
           <t>The University of Texas at Austin</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N52" t="n">
+      <c r="N52" s="6" t="n">
         <v>1883</v>
       </c>
-      <c r="P52" t="n">
+      <c r="O52" s="6" t="n"/>
+      <c r="P52" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q52" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Vanderbilt University</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>UNI-000052</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>Nashville,Tennessee</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="6" t="n">
         <v>13000</v>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="inlineStr">
         <is>
           <t>Vanderbilt University</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" s="6" t="inlineStr">
         <is>
           <t>Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N53" t="n">
+      <c r="N53" s="6" t="n">
         <v>1873</v>
       </c>
-      <c r="P53" t="n">
+      <c r="O53" s="6" t="n"/>
+      <c r="P53" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q53" s="6" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>University of Maryland, College Park</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>UNI-000053</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>College Park,Maryland</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="inlineStr">
         <is>
           <t>University of Maryland, College Park</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M54" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N54" t="n">
+      <c r="N54" s="6" t="n">
         <v>1856</v>
       </c>
-      <c r="P54" t="n">
+      <c r="O54" s="6" t="n"/>
+      <c r="P54" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q54" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>University of Southern California</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>UNI-000054</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Los Angeles,California</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="6" t="n">
         <v>47000</v>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="inlineStr">
         <is>
           <t>University of Southern California</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N55" t="n">
+      <c r="N55" s="6" t="n">
         <v>1880</v>
       </c>
-      <c r="P55" t="n">
+      <c r="O55" s="6" t="n"/>
+      <c r="P55" s="6" t="n">
         <v>19000</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q55" s="6" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>The University of Queensland</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>UNI-000055</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>Brisbane,Queensland</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" s="6" t="n">
         <v>55000</v>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="J56" s="6" t="n"/>
+      <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="inlineStr">
         <is>
           <t>The University of Queensland</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M56" s="6" t="inlineStr">
         <is>
           <t>Group of Eight (Go8)</t>
         </is>
       </c>
-      <c r="N56" t="n">
+      <c r="N56" s="6" t="n">
         <v>1909</v>
       </c>
-      <c r="P56" t="n">
+      <c r="O56" s="6" t="n"/>
+      <c r="P56" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q56" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>University of Helsinki</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>UNI-000056</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>Helsinki</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I57" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="inlineStr">
         <is>
           <t>Helsingin yliopisto</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Humanities and Social Sciences</t>
         </is>
       </c>
-      <c r="N57" t="n">
+      <c r="N57" s="6" t="n">
         <v>1640</v>
       </c>
-      <c r="P57" t="n">
+      <c r="O57" s="6" t="n"/>
+      <c r="P57" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q57" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>University of Munich</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>UNI-000057</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="J58" s="6" t="n"/>
+      <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="inlineStr">
         <is>
           <t>Ludwig-Maximilians-Universität München</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Germany.</t>
         </is>
       </c>
-      <c r="N58" t="n">
+      <c r="N58" s="6" t="n">
         <v>1472</v>
       </c>
-      <c r="P58" t="n">
+      <c r="O58" s="6" t="n"/>
+      <c r="P58" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q58" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>University of Zurich</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>UNI-000058</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" s="6" t="n">
         <v>26000</v>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>Universität Zürich</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N59" t="n">
+      <c r="N59" s="6" t="n">
         <v>1833</v>
       </c>
-      <c r="P59" t="n">
+      <c r="O59" s="6" t="n"/>
+      <c r="P59" s="6" t="n">
         <v>14000</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Q59" s="6" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>University of Groningen</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>UNI-000059</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Groningen</t>
         </is>
       </c>
-      <c r="I60" t="n">
+      <c r="I60" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="J60" s="6" t="n"/>
+      <c r="K60" s="6" t="n"/>
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>Rijksuniversiteit Groningen</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>Known for Life Sciences, Arts and Social Sciences</t>
         </is>
       </c>
-      <c r="N60" t="n">
+      <c r="N60" s="6" t="n">
         <v>1614</v>
       </c>
-      <c r="P60" t="n">
+      <c r="O60" s="6" t="n"/>
+      <c r="P60" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="Q60" s="6" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>University of Geneva</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>UNI-000060</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>Geneva</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="I61" s="6" t="n">
         <v>17000</v>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="J61" s="6" t="n"/>
+      <c r="K61" s="6" t="n"/>
+      <c r="L61" s="6" t="inlineStr">
         <is>
           <t>Université de Genève</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
         <is>
           <t>Known for International Relations, Social Sciences and Law</t>
         </is>
       </c>
-      <c r="N61" t="n">
+      <c r="N61" s="6" t="n">
         <v>1559</v>
       </c>
-      <c r="P61" t="n">
+      <c r="O61" s="6" t="n"/>
+      <c r="P61" s="6" t="n">
         <v>9000</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="Q61" s="6" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>University of Bristol</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>UNI-000061</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>Bristol,England</t>
         </is>
       </c>
-      <c r="I62" t="n">
+      <c r="I62" s="6" t="n">
         <v>27000</v>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="J62" s="6" t="n"/>
+      <c r="K62" s="6" t="n"/>
+      <c r="L62" s="6" t="inlineStr">
         <is>
           <t>University of Bristol</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M62" s="6" t="inlineStr">
         <is>
           <t>Russell Group</t>
         </is>
       </c>
-      <c r="N62" t="n">
+      <c r="N62" s="6" t="n">
         <v>1833</v>
       </c>
-      <c r="P62" t="n">
+      <c r="O62" s="6" t="n"/>
+      <c r="P62" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="Q62" s="6" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>University of Oslo</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>UNI-000062</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>Oslo</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="I63" s="6" t="n">
         <v>28000</v>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="6" t="n"/>
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>Universitetet i Oslo</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
         <is>
           <t>Known for Humanities, Natural Sciences and Social Sciences</t>
         </is>
       </c>
-      <c r="N63" t="n">
+      <c r="N63" s="6" t="n">
         <v>1811</v>
       </c>
-      <c r="P63" t="n">
+      <c r="O63" s="6" t="n"/>
+      <c r="P63" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Q63" s="6" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Uppsala University</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>UNI-000063</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>Uppsala</t>
         </is>
       </c>
-      <c r="I64" t="n">
+      <c r="I64" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="J64" s="6" t="n"/>
+      <c r="K64" s="6" t="n"/>
+      <c r="L64" s="6" t="inlineStr">
         <is>
           <t>Uppsala universitet</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>Known for Humanities, Life Sciences and Social Sciences</t>
         </is>
       </c>
-      <c r="N64" t="n">
+      <c r="N64" s="6" t="n">
         <v>1477</v>
       </c>
-      <c r="P64" t="n">
+      <c r="O64" s="6" t="n"/>
+      <c r="P64" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q64" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>University of California, Irvine</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>UNI-000064</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>Irvine,California</t>
         </is>
       </c>
-      <c r="I65" t="n">
+      <c r="I65" s="6" t="n">
         <v>36000</v>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="J65" s="6" t="n"/>
+      <c r="K65" s="6" t="n"/>
+      <c r="L65" s="6" t="inlineStr">
         <is>
           <t>University of California, Irvine</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>Public Ivy League</t>
         </is>
       </c>
-      <c r="N65" t="n">
+      <c r="N65" s="6" t="n">
         <v>1965</v>
       </c>
-      <c r="P65" t="n">
+      <c r="O65" s="6" t="n"/>
+      <c r="P65" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q65" s="6" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Aarhus University</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>UNI-000065</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>Aarhus</t>
         </is>
       </c>
-      <c r="I66" t="n">
+      <c r="I66" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="J66" s="6" t="n"/>
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>Aarhus Universitet</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M66" s="6" t="inlineStr">
         <is>
           <t>Known for Humanities, Business and Natural Sciences</t>
         </is>
       </c>
-      <c r="N66" t="n">
+      <c r="N66" s="6" t="n">
         <v>1928</v>
       </c>
-      <c r="P66" t="n">
+      <c r="O66" s="6" t="n"/>
+      <c r="P66" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q66" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>McMaster University</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>UNI-000066</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>Hamilton,Ontario</t>
         </is>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="6" t="inlineStr">
         <is>
           <t>McMaster University</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
         <is>
           <t>U15 Group</t>
         </is>
       </c>
-      <c r="N67" t="n">
+      <c r="N67" s="6" t="n">
         <v>1887</v>
       </c>
-      <c r="P67" t="n">
+      <c r="O67" s="6" t="n"/>
+      <c r="P67" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="Q67" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>McGill University</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>UNI-000067</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>Montreal,Quebec</t>
         </is>
       </c>
-      <c r="I68" t="n">
+      <c r="I68" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="J68" s="6" t="n"/>
+      <c r="K68" s="6" t="n"/>
+      <c r="L68" s="6" t="inlineStr">
         <is>
           <t>Université McGill</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. U15 Group.</t>
         </is>
       </c>
-      <c r="N68" t="n">
+      <c r="N68" s="6" t="n">
         <v>1821</v>
       </c>
-      <c r="P68" t="n">
+      <c r="O68" s="6" t="n"/>
+      <c r="P68" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="Q68" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>University of Pittsburgh, Pittsburgh Campus</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>UNI-000068</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>Pittsburgh,Pennsylvania</t>
         </is>
       </c>
-      <c r="I69" t="n">
+      <c r="I69" s="6" t="n">
         <v>28000</v>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="J69" s="6" t="n"/>
+      <c r="K69" s="6" t="n"/>
+      <c r="L69" s="6" t="inlineStr">
         <is>
           <t>University of Pittsburgh</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="M69" s="6" t="inlineStr">
         <is>
           <t>Public Ivy League</t>
         </is>
       </c>
-      <c r="N69" t="n">
+      <c r="N69" s="6" t="n">
         <v>1787</v>
       </c>
-      <c r="P69" t="n">
+      <c r="O69" s="6" t="n"/>
+      <c r="P69" s="6" t="n">
         <v>19000</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="Q69" s="6" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>École Normale Supérieure - Paris</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>UNI-000069</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="I70" s="6" t="n">
         <v>1800</v>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="J70" s="6" t="n"/>
+      <c r="K70" s="6" t="n"/>
+      <c r="L70" s="6" t="inlineStr">
         <is>
           <t>École normale supérieure</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M70" s="6" t="inlineStr">
         <is>
           <t>Elite university in France</t>
         </is>
       </c>
-      <c r="N70" t="n">
+      <c r="N70" s="6" t="n">
         <v>1794</v>
       </c>
-      <c r="P70" t="n">
+      <c r="O70" s="6" t="n"/>
+      <c r="P70" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="Q70" s="6" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Ghent University</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>UNI-000070</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>Ghent</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="I71" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="J71" s="6" t="n"/>
+      <c r="K71" s="6" t="n"/>
+      <c r="L71" s="6" t="inlineStr">
         <is>
           <t>Universiteit Gent</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Engineering and Life Sciences</t>
         </is>
       </c>
-      <c r="N71" t="n">
+      <c r="N71" s="6" t="n">
         <v>1817</v>
       </c>
-      <c r="P71" t="n">
+      <c r="O71" s="6" t="n"/>
+      <c r="P71" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="Q71" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Mayo Medical School</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>UNI-000071</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Private Medical School</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>Rochester,Minnesota</t>
         </is>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="J72" s="6" t="n"/>
+      <c r="K72" s="6" t="n"/>
+      <c r="L72" s="6" t="inlineStr">
         <is>
           <t>Mayo Medical School</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M72" s="6" t="inlineStr">
         <is>
           <t>Known for Medical Education and Clinical Research</t>
         </is>
       </c>
-      <c r="N72" t="n">
+      <c r="N72" s="6" t="n">
         <v>1972</v>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="O72" s="6" t="n"/>
+      <c r="P72" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> N/A (graduate-only institution)</t>
         </is>
       </c>
-      <c r="Q72" t="n">
+      <c r="Q72" s="6" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>Peking University</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>UNI-000072</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="6" t="n"/>
+      <c r="L73" s="6" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M73" s="6" t="inlineStr">
         <is>
           <t>World prestigious university. C9 League.</t>
         </is>
       </c>
-      <c r="N73" t="n">
+      <c r="N73" s="6" t="n">
         <v>1898</v>
       </c>
-      <c r="P73" t="n">
+      <c r="O73" s="6" t="n"/>
+      <c r="P73" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="Q73" s="6" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>Erasmus University</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>UNI-000073</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>Rotterdam</t>
         </is>
       </c>
-      <c r="I74" t="n">
+      <c r="I74" s="6" t="n">
         <v>28000</v>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="J74" s="6" t="n"/>
+      <c r="K74" s="6" t="n"/>
+      <c r="L74" s="6" t="inlineStr">
         <is>
           <t>Erasmus Universiteit Rotterdam</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M74" s="6" t="inlineStr">
         <is>
           <t>Known for Social Sciences, Business and Medical Sciences</t>
         </is>
       </c>
-      <c r="N74" t="n">
+      <c r="N74" s="6" t="n">
         <v>1913</v>
       </c>
-      <c r="P74" t="n">
+      <c r="O74" s="6" t="n"/>
+      <c r="P74" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="Q74" s="6" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Rice University</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>UNI-000074</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>Houston,Texas</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="n"/>
+      <c r="L75" s="6" t="inlineStr">
         <is>
           <t>Rice University</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
         <is>
           <t>Highly selective. Hidden Ivy League.</t>
         </is>
       </c>
-      <c r="N75" t="n">
+      <c r="N75" s="6" t="n">
         <v>1912</v>
       </c>
-      <c r="P75" t="n">
+      <c r="O75" s="6" t="n"/>
+      <c r="P75" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="Q75" s="6" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>Stockholm University</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>UNI-000075</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>Stockholm</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I76" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="J76" s="6" t="n"/>
+      <c r="K76" s="6" t="n"/>
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>Stockholms universitet</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M76" s="6" t="inlineStr">
         <is>
           <t>Known for Humanities, Life Sciences and Social Sciences</t>
         </is>
       </c>
-      <c r="N76" t="n">
+      <c r="N76" s="6" t="n">
         <v>1878</v>
       </c>
-      <c r="P76" t="n">
+      <c r="O76" s="6" t="n"/>
+      <c r="P76" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="Q76" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Swiss Federal Institute of Technology Lausanne</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>UNI-000076</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="n"/>
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="I77" t="n">
+      <c r="I77" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="J77" s="6" t="n"/>
+      <c r="K77" s="6" t="n"/>
+      <c r="L77" s="6" t="inlineStr">
         <is>
           <t>École polytechnique fédérale de Lausanne (EPFL)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N77" t="n">
+      <c r="N77" s="6" t="n">
         <v>1853</v>
       </c>
-      <c r="P77" t="n">
+      <c r="O77" s="6" t="n"/>
+      <c r="P77" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q77" s="6" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>Purdue University - West Lafayette</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>UNI-000077</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>West Lafayette,Indiana</t>
         </is>
       </c>
-      <c r="I78" t="n">
+      <c r="I78" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="J78" s="6" t="n"/>
+      <c r="K78" s="6" t="n"/>
+      <c r="L78" s="6" t="inlineStr">
         <is>
           <t>Purdue University</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M78" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N78" t="n">
+      <c r="N78" s="6" t="n">
         <v>1869</v>
       </c>
-      <c r="P78" t="n">
+      <c r="O78" s="6" t="n"/>
+      <c r="P78" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q78" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Monash University</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>UNI-000078</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="n"/>
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>Melbourne,Victoria</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="I79" s="6" t="n">
         <v>80000</v>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="J79" s="6" t="n"/>
+      <c r="K79" s="6" t="n"/>
+      <c r="L79" s="6" t="inlineStr">
         <is>
           <t>Monash University</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M79" s="6" t="inlineStr">
         <is>
           <t>Group of Eight (Go8)</t>
         </is>
       </c>
-      <c r="N79" t="n">
+      <c r="N79" s="6" t="n">
         <v>1958</v>
       </c>
-      <c r="P79" t="n">
+      <c r="O79" s="6" t="n"/>
+      <c r="P79" s="6" t="n">
         <v>55000</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="Q79" s="6" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>Rutgers, The State University of New Jersey - New Brunswick</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>UNI-000079</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="n"/>
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>New Brunswick,New Jersey</t>
         </is>
       </c>
-      <c r="I80" t="n">
+      <c r="I80" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="J80" s="6" t="n"/>
+      <c r="K80" s="6" t="n"/>
+      <c r="L80" s="6" t="inlineStr">
         <is>
           <t>Rutgers, The State University of New Jersey–New Brunswick</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M80" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Public Ivy League
 </t>
         </is>
       </c>
-      <c r="N80" t="n">
+      <c r="N80" s="6" t="n">
         <v>1766</v>
       </c>
-      <c r="P80" t="n">
+      <c r="O80" s="6" t="n"/>
+      <c r="P80" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="Q80" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Boston University</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>UNI-000080</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="6" t="n"/>
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>Boston,Massachusetts</t>
         </is>
       </c>
-      <c r="I81" t="n">
+      <c r="I81" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="J81" s="6" t="n"/>
+      <c r="K81" s="6" t="n"/>
+      <c r="L81" s="6" t="inlineStr">
         <is>
           <t>Boston University</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M81" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N81" t="n">
+      <c r="N81" s="6" t="n">
         <v>1839</v>
       </c>
-      <c r="P81" t="n">
+      <c r="O81" s="6" t="n"/>
+      <c r="P81" s="6" t="n">
         <v>16000</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="Q81" s="6" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>Carnegie Mellon University</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>UNI-000081</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Private Research University</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="6" t="n"/>
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>Pittsburgh,Pennsylvania</t>
         </is>
       </c>
-      <c r="I82" t="n">
+      <c r="I82" s="6" t="n">
         <v>14000</v>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="J82" s="6" t="n"/>
+      <c r="K82" s="6" t="n"/>
+      <c r="L82" s="6" t="inlineStr">
         <is>
           <t>Carnegie Mellon University</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M82" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Highly selective.</t>
         </is>
       </c>
-      <c r="N82" t="n">
+      <c r="N82" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="P82" t="n">
+      <c r="O82" s="6" t="n"/>
+      <c r="P82" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="Q82" s="6" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>The Ohio State University - Columbus</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>UNI-000082</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n"/>
+      <c r="F83" s="6" t="n"/>
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>Columbus,Ohio</t>
         </is>
       </c>
-      <c r="I83" t="n">
+      <c r="I83" s="6" t="n">
         <v>61000</v>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="J83" s="6" t="n"/>
+      <c r="K83" s="6" t="n"/>
+      <c r="L83" s="6" t="inlineStr">
         <is>
           <t>The Ohio State University</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M83" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N83" t="n">
+      <c r="N83" s="6" t="n">
         <v>1870</v>
       </c>
-      <c r="P83" t="n">
+      <c r="O83" s="6" t="n"/>
+      <c r="P83" s="6" t="n">
         <v>47000</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="Q83" s="6" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>University of Sydney</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>UNI-000083</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n"/>
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>Sydney,New South Wales</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I84" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="J84" s="6" t="n"/>
+      <c r="K84" s="6" t="n"/>
+      <c r="L84" s="6" t="inlineStr">
         <is>
           <t>The University of Sydney</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="M84" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Group of Eight (Go8).</t>
         </is>
       </c>
-      <c r="N84" t="n">
+      <c r="N84" s="6" t="n">
         <v>1850</v>
       </c>
-      <c r="P84" t="n">
+      <c r="O84" s="6" t="n"/>
+      <c r="P84" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q84" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Nagoya University</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>UNI-000084</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="6" t="n"/>
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>Nagoya,Aichi</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="I85" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="J85" s="6" t="n"/>
+      <c r="K85" s="6" t="n"/>
+      <c r="L85" s="6" t="inlineStr">
         <is>
           <t>名古屋大学</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M85" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Imperial university.</t>
         </is>
       </c>
-      <c r="N85" t="n">
+      <c r="N85" s="6" t="n">
         <v>1871</v>
       </c>
-      <c r="P85" t="n">
+      <c r="O85" s="6" t="n"/>
+      <c r="P85" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="Q85" s="6" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>Georgia Institute of Technology</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>UNI-000085</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="6" t="n"/>
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="6" t="inlineStr">
         <is>
           <t>Atlanta,Georgia</t>
         </is>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="J86" s="6" t="n"/>
+      <c r="K86" s="6" t="n"/>
+      <c r="L86" s="6" t="inlineStr">
         <is>
           <t>Georgia Institute of Technology</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M86" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League, highly selective.</t>
         </is>
       </c>
-      <c r="N86" t="n">
+      <c r="N86" s="6" t="n">
         <v>1885</v>
       </c>
-      <c r="P86" t="n">
+      <c r="O86" s="6" t="n"/>
+      <c r="P86" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="Q86" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Pennsylvania State University - University Park</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>UNI-000086</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="6" t="n"/>
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>University Park,Pennsylvania</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="I87" s="6" t="n">
         <v>46000</v>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="6" t="n"/>
+      <c r="L87" s="6" t="inlineStr">
         <is>
           <t>The Pennsylvania State University</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M87" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N87" t="n">
+      <c r="N87" s="6" t="n">
         <v>1855</v>
       </c>
-      <c r="P87" t="n">
+      <c r="O87" s="6" t="n"/>
+      <c r="P87" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="Q87" s="6" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>University of California, Davis</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>UNI-000087</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="6" t="n"/>
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>Davis,California</t>
         </is>
       </c>
-      <c r="I88" t="n">
+      <c r="I88" s="6" t="n">
         <v>39000</v>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="J88" s="6" t="n"/>
+      <c r="K88" s="6" t="n"/>
+      <c r="L88" s="6" t="inlineStr">
         <is>
           <t>University of California, Davis</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="M88" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N88" t="n">
+      <c r="N88" s="6" t="n">
         <v>1905</v>
       </c>
-      <c r="P88" t="n">
+      <c r="O88" s="6" t="n"/>
+      <c r="P88" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="Q88" s="6" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>Leiden University</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>UNI-000088</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="n"/>
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>Leiden</t>
         </is>
       </c>
-      <c r="I89" t="n">
+      <c r="I89" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="J89" s="6" t="n"/>
+      <c r="K89" s="6" t="n"/>
+      <c r="L89" s="6" t="inlineStr">
         <is>
           <t>Universiteit Leiden</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M89" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N89" t="n">
+      <c r="N89" s="6" t="n">
         <v>1575</v>
       </c>
-      <c r="P89" t="n">
+      <c r="O89" s="6" t="n"/>
+      <c r="P89" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="Q89" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>University of Florida</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>UNI-000089</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="6" t="n"/>
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>Gainesville,Florida</t>
         </is>
       </c>
-      <c r="I90" t="n">
+      <c r="I90" s="6" t="n">
         <v>55000</v>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="J90" s="6" t="n"/>
+      <c r="K90" s="6" t="n"/>
+      <c r="L90" s="6" t="inlineStr">
         <is>
           <t>University of Florida</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M90" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N90" t="n">
+      <c r="N90" s="6" t="n">
         <v>1853</v>
       </c>
-      <c r="P90" t="n">
+      <c r="O90" s="6" t="n"/>
+      <c r="P90" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="Q90" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>KU Leuven</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>UNI-000090</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="6" t="n"/>
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>Leuven</t>
         </is>
       </c>
-      <c r="I91" t="n">
+      <c r="I91" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="J91" s="6" t="n"/>
+      <c r="K91" s="6" t="n"/>
+      <c r="L91" s="6" t="inlineStr">
         <is>
           <t>Katholieke Universiteit Leuven</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N91" t="n">
+      <c r="N91" s="6" t="n">
         <v>1425</v>
       </c>
-      <c r="P91" t="n">
+      <c r="O91" s="6" t="n"/>
+      <c r="P91" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="Q91" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>National University of Singapore</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>UNI-000091</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" s="6" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="I92" t="n">
+      <c r="I92" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="J92" s="6" t="n"/>
+      <c r="K92" s="6" t="n"/>
+      <c r="L92" s="6" t="inlineStr">
         <is>
           <t>National University of Singapore</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="M92" s="6" t="inlineStr">
         <is>
           <t>World-renowned university</t>
         </is>
       </c>
-      <c r="N92" t="n">
+      <c r="N92" s="6" t="n">
         <v>1905</v>
       </c>
-      <c r="P92" t="n">
+      <c r="O92" s="6" t="n"/>
+      <c r="P92" s="6" t="n">
         <v>28000</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="Q92" s="6" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>The University of Western Australia</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>UNI-000092</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="n"/>
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>Perth,Western Australia</t>
         </is>
       </c>
-      <c r="I93" t="n">
+      <c r="I93" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="J93" s="6" t="n"/>
+      <c r="K93" s="6" t="n"/>
+      <c r="L93" s="6" t="inlineStr">
         <is>
           <t>The University of Western Australia</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M93" s="6" t="inlineStr">
         <is>
           <t>Group of Eight (Go8)</t>
         </is>
       </c>
-      <c r="N93" t="n">
+      <c r="N93" s="6" t="n">
         <v>1911</v>
       </c>
-      <c r="P93" t="n">
+      <c r="O93" s="6" t="n"/>
+      <c r="P93" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="Q93" s="6" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>Moscow State University</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>UNI-000093</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="6" t="n"/>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>Moscow</t>
         </is>
       </c>
-      <c r="I94" t="n">
+      <c r="I94" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="J94" s="6" t="n"/>
+      <c r="K94" s="6" t="n"/>
+      <c r="L94" s="6" t="inlineStr">
         <is>
           <t>Московский государственный университет имени М. В. Ломоносова</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="M94" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Elite university in Russia.</t>
         </is>
       </c>
-      <c r="N94" t="n">
+      <c r="N94" s="6" t="n">
         <v>1755</v>
       </c>
-      <c r="P94" t="n">
+      <c r="O94" s="6" t="n"/>
+      <c r="P94" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="Q94" s="6" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>University of Basel</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>UNI-000094</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="6" t="n"/>
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>Basel</t>
         </is>
       </c>
-      <c r="I95" t="n">
+      <c r="I95" s="6" t="n">
         <v>13000</v>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="J95" s="6" t="n"/>
+      <c r="K95" s="6" t="n"/>
+      <c r="L95" s="6" t="inlineStr">
         <is>
           <t>Universität Basel</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="M95" s="6" t="inlineStr">
         <is>
           <t>Known for Medical Sciences, Life Sciences and Humanities</t>
         </is>
       </c>
-      <c r="N95" t="n">
+      <c r="N95" s="6" t="n">
         <v>1460</v>
       </c>
-      <c r="P95" t="n">
+      <c r="O95" s="6" t="n"/>
+      <c r="P95" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="Q95" s="6" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>University of Göttingen</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>UNI-000095</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="6" t="n"/>
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>Göttingen</t>
         </is>
       </c>
-      <c r="I96" t="n">
+      <c r="I96" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="J96" s="6" t="n"/>
+      <c r="K96" s="6" t="n"/>
+      <c r="L96" s="6" t="inlineStr">
         <is>
           <t>Georg-August-Universität Göttingen</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="M96" s="6" t="inlineStr">
         <is>
           <t>Elite university in Germany</t>
         </is>
       </c>
-      <c r="N96" t="n">
+      <c r="N96" s="6" t="n">
         <v>1737</v>
       </c>
-      <c r="P96" t="n">
+      <c r="O96" s="6" t="n"/>
+      <c r="P96" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q96" t="n">
+      <c r="Q96" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>The Australian National University</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>UNI-000096</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="6" t="n"/>
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>Canberra</t>
         </is>
       </c>
-      <c r="I97" t="n">
+      <c r="I97" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="J97" s="6" t="n"/>
+      <c r="K97" s="6" t="n"/>
+      <c r="L97" s="6" t="inlineStr">
         <is>
           <t>The Australian National University</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="M97" s="6" t="inlineStr">
         <is>
           <t>World-renowned university. Group of Eight (Go8).</t>
         </is>
       </c>
-      <c r="N97" t="n">
+      <c r="N97" s="6" t="n">
         <v>1946</v>
       </c>
-      <c r="P97" t="n">
+      <c r="O97" s="6" t="n"/>
+      <c r="P97" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="Q97" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>University of California, Santa Cruz</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>UNI-000097</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="6" t="inlineStr">
         <is>
           <t>Santa Cruz,California</t>
         </is>
       </c>
-      <c r="I98" t="n">
+      <c r="I98" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="J98" s="6" t="n"/>
+      <c r="K98" s="6" t="n"/>
+      <c r="L98" s="6" t="inlineStr">
         <is>
           <t>University of California, Santa Cruz</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M98" s="6" t="inlineStr">
         <is>
           <t>Known for Social Sciences, Natural Sciences and Arts</t>
         </is>
       </c>
-      <c r="N98" t="n">
+      <c r="N98" s="6" t="n">
         <v>1962</v>
       </c>
-      <c r="P98" t="n">
+      <c r="O98" s="6" t="n"/>
+      <c r="P98" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="Q98" t="n">
+      <c r="Q98" s="6" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Cardiff University</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>UNI-000098</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="6" t="n"/>
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>Cardiff,Wales</t>
         </is>
       </c>
-      <c r="I99" t="n">
+      <c r="I99" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="J99" s="6" t="n"/>
+      <c r="K99" s="6" t="n"/>
+      <c r="L99" s="6" t="inlineStr">
         <is>
           <t>Prifysgol Caerdydd</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="M99" s="6" t="inlineStr">
         <is>
           <t>Russell Group</t>
         </is>
       </c>
-      <c r="N99" t="n">
+      <c r="N99" s="6" t="n">
         <v>1883</v>
       </c>
-      <c r="P99" t="n">
+      <c r="O99" s="6" t="n"/>
+      <c r="P99" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="Q99" t="n">
+      <c r="Q99" s="6" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>University of Arizona</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>UNI-000099</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="6" t="n"/>
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>Tucson,Arizona</t>
         </is>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="J100" s="6" t="n"/>
+      <c r="K100" s="6" t="n"/>
+      <c r="L100" s="6" t="inlineStr">
         <is>
           <t>University of Arizona</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="M100" s="6" t="inlineStr">
         <is>
           <t>World-renowned university, public Ivy League</t>
         </is>
       </c>
-      <c r="N100" t="n">
+      <c r="N100" s="6" t="n">
         <v>1885</v>
       </c>
-      <c r="P100" t="n">
+      <c r="O100" s="6" t="n"/>
+      <c r="P100" s="6" t="n">
         <v>34000</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q100" s="6" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>King Saud University</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>UNI-000100</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Public Research University</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Public Research University</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+      <c r="G101" s="6" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" s="6" t="inlineStr">
         <is>
           <t>Riyadh</t>
         </is>
       </c>
-      <c r="I101" t="n">
+      <c r="I101" s="6" t="n">
         <v>61000</v>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="J101" s="6" t="n"/>
+      <c r="K101" s="6" t="n"/>
+      <c r="L101" s="6" t="inlineStr">
         <is>
           <t>جامعة الملك سعود</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M101" s="6" t="inlineStr">
         <is>
           <t>Leading public university in Saudi Arabia. Flagship institution with strong research programs and broad academic offerings.</t>
         </is>
       </c>
-      <c r="N101" t="n">
+      <c r="N101" s="6" t="n">
         <v>1957</v>
       </c>
-      <c r="P101" t="n">
+      <c r="O101" s="6" t="n"/>
+      <c r="P101" s="6" t="n">
         <v>38000</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="Q101" s="6" t="n">
         <v>23000</v>
       </c>
     </row>
